--- a/mmrag_evaluation_results.xlsx
+++ b/mmrag_evaluation_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V40"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,65 +476,70 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>OfflineClinicalCorrectness</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>generated_answer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>expected_answer</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>total_iterations</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>retrieval_attempts</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>reasoning_attempts</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>refinement_count</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>evidence_quality</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>response_quality</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>overall_quality</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>evidence_decision</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>response_decision</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>evidence_count</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>modality</t>
         </is>
@@ -567,31 +572,28 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7138341665267944</v>
+        <v>0.7098313570022583</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1]
+- The chest X-ray appears normal. [R1-IMAGE]
 Supporting Evidence:
 - The cardiac silhouette and mediastinum size are within normal limits. [R1]
 - There is no pulmonary edema. [R1]
-- There is no focal consolidation. [R1]
-- A normal chest x-ray does not necessarily rule out all possible conditions or issues. [R1-IMAGE]
+- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R1-IMAGE]
 Next Steps / Recommendations:
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying concerns [R1]. [R1-IMAGE]
-- Clinical correlation recommended [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
+- Further evaluation and diagnostic tests may be needed to rule out all possible conditions or diseases. [Rx]</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
@@ -600,28 +602,31 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q2" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0.9141502499580383</v>
-      </c>
       <c r="R2" t="n">
-        <v>0.7570751249790191</v>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9129494071006774</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.7564747035503387</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U2" t="n">
-        <v>2</v>
-      </c>
-      <c r="V2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>2</v>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -654,60 +659,61 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.605611264705658</v>
+        <v>0.5581897497177124</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Borderline cardiomegaly and enlarged pulmonary arteries detected. [R1]
+- Borderline cardiomegaly detected. [R1]
 Supporting Evidence:
-- Borderline cardiomegaly was observed on the chest X-ray. [R1]
-- Enlarged pulmonary arteries were noted on the chest X-ray. [R1]
-- Clear lungs were observed on the chest X-ray. [R1]
+- The chest X-ray shows borderline cardiomegaly. [R1]
+- Enlarged pulmonary arteries are visible on the X-ray. [R1]
+- Clear lungs are observed on the X-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with the patient's history and symptoms is recommended. [Rx]
-- Further evaluation may be needed depending on the patient's clinical history and symptoms [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+- Clinical correlation with patient's symptoms and medical history is recommended. [Rx]
+- Further evaluation with echocardiogram or other diagnostic tests may be necessary to confirm the diagnosis of borderline cardiomegaly. [Rx]</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
         <v>3</v>
       </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
         <v>0.577</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0.8816833794116974</v>
-      </c>
       <c r="R3" t="n">
-        <v>0.7293416897058487</v>
-      </c>
-      <c r="S3" t="inlineStr">
+        <v>0.8674569249153137</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.7222284624576568</v>
+      </c>
+      <c r="T3" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>2</v>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -740,61 +746,62 @@
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6715929508209229</v>
+        <v>0.5643539428710938</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No signs of cardiomegaly or abnormal cardiac silhouette identified on chest X-ray. [R1], [R2]
+- No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
-- The chest x-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette [R1]. [R2-IMAGE]
-- Well-expanded and clear lungs were observed on the chest X-ray, indicating no acute cardiopulmonary abnormality [R1]. [R1]
-- Mediastinal contour within normal limits was noted on the chest X-ray. [R1]
+- The chest x-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
+- The chest x-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
+- The heart appears to be within normal size and shape in the image. [R1-IMAGE]
+- The absence of cardiomegaly or abnormal cardiac silhouette on chest X-ray is consistent with a normal cardiac silhouette. [R2]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not appear necessary [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="n">
         <v>0.572</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0.9014778852462768</v>
-      </c>
       <c r="R4" t="n">
-        <v>0.7367389426231383</v>
-      </c>
-      <c r="S4" t="inlineStr">
+        <v>0.8693061828613281</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.720653091430664</v>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>2</v>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>2</v>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -827,60 +834,61 @@
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5721495747566223</v>
+        <v>0.7382009029388428</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
+- No signs of pulmonary congestion or edema detected. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any signs of pulmonary congestion or edema [R1]. [R1-IMAGE]
-- The chest x-ray does not show any signs of pulmonary congestion or edema [R1]. [R2-IMAGE]
-- The absence of pulmonary congestion or edema signs on the chest X-ray is consistent with the normal cardiomediastinal silhouette [R1]. [R1]
+- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
+- The chest x-ray does not show any signs of pulmonary congestion or edema. [R2-IMAGE]
+- The cardiomediastinal silhouette is normal in size and contour, which is consistent with no pulmonary congestion or edema. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but not indicated at this time [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+- Clinical correlation recommended to assess for other potential causes of symptoms. [Rx]
+- Further evaluation of the left lung apex for a cavitary lesion is recommended. [Rx]</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
         <v>3</v>
       </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0.8716448724269866</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.7153224362134933</v>
-      </c>
-      <c r="S5" t="inlineStr">
+        <v>0.9214602708816528</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.7402301354408265</v>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>2</v>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -913,31 +921,29 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6840327382087708</v>
+        <v>0.6969091296195984</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No pleural effusion visible on the chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible signs of pleural effusion [R1]. [R2-IMAGE]
-- The cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion [R1]. [R1]
-- There is no pneumothorax or pleural effusion, as stated in the radiologist's impression. [R1]
+- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
+- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
+- The cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion. [R1]
+- There is no pneumothorax or pleural effusion, as stated in the radiologist's report. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely that pleural effusion will be visible on the chest X-ray [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess for other potential causes of symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but based on the current evidence, it is unlikely that pleural effusion will be detected. [Rx]</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
@@ -946,28 +952,31 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>0.604</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0.9052098214626312</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.7546049107313155</v>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9090727388858795</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.7565363694429397</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V6" t="n">
+        <v>2</v>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1000,60 +1009,62 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6916998028755188</v>
+        <v>0.6997577548027039</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No lung consolidation or opacities detected on chest X-ray. [R1], [R1-IMAGE], [R2-IMAGE]
+- No lung consolidation or opacities detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest X-ray shows heart size and mediastinal contour within normal limits. [R1]
-- There is no focal airspace consolidation or suspicious pulmonary opacity. [R1]
-- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE], [R2-IMAGE]
+- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE]
+- The chest X-ray does not show any lung consolidation or opacities. [R2-IMAGE]
+- Heart size and mediastinal contour are within normal limits on the chest X-ray. [R1]
+- Mild degenerative change of the thoracic spine is noted on the chest X-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess for other potential causes of symptoms [R1]. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show lung consolidation or opacities [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+- Clinical correlation recommended to assess for other potential causes of symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show lung consolidation or opacities. [Rx]</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.586</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0.9075099408626556</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.7467549704313278</v>
-      </c>
-      <c r="S7" t="inlineStr">
+        <v>0.9099273264408111</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.7479636632204055</v>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U7" t="n">
-        <v>2</v>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>2</v>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1086,61 +1097,61 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4715036451816559</v>
+        <v>0.4138781428337097</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pneumothorax detected. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R1-IMAGE]
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R2-IMAGE]
-- The lungs are clear [R1]. [R1]
-- No confluent lobar consolidation or pleural effusion. [R1]
+- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
+- The lungs are clear. [R1]
+- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended. [Rx]
-- Follow-up imaging if symptoms persist [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+- Follow-up imaging if symptoms persist. [Rx]</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>0.534</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0.8414510935544968</v>
-      </c>
       <c r="R8" t="n">
-        <v>0.6877255467772484</v>
-      </c>
-      <c r="S8" t="inlineStr">
+        <v>0.8241634428501129</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.6790817214250564</v>
+      </c>
+      <c r="T8" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U8" t="n">
-        <v>2</v>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V8" t="n">
+        <v>2</v>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1173,60 +1184,62 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8294001221656799</v>
+        <v>0.8050918579101562</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No acute cardiopulmonary disease detected. [R1]
+- No significant pathologies detected above threshold. [R1]
 Supporting Evidence:
 - The heart, pulmonary structures, and mediastinum are within normal limits. [R1]
-- No pleural effusion or pneumothorax is present. [R1]
-- No focal air space opacity to suggest a pneumonia is visible. [R1]
+- There is no pleural effusion or pneumothorax. [R1]
+- The chest X-ray shows several key findings, including bilateral pneumothorax, multiple rib fractures, and a left-sided hemopneumothorax. [R1-IMAGE]
+- The chest X-ray also reveals a right-sided pneumothorax with a chest tube in place. [R1-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms and history of mitral valve prolapse. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+- Follow-up imaging if symptoms persist, particularly dyspnea, to rule out any underlying conditions. [Rx]</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="n">
         <v>3</v>
       </c>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
       </c>
       <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
         <v>0.573</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0.9488200366497039</v>
-      </c>
       <c r="R9" t="n">
-        <v>0.7609100183248519</v>
-      </c>
-      <c r="S9" t="inlineStr">
+        <v>0.9415275573730468</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.7572637786865234</v>
+      </c>
+      <c r="T9" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U9" t="n">
-        <v>2</v>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1259,60 +1272,61 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7615203857421875</v>
+        <v>0.6436727643013</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of heart enlargement detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest X-ray does not show any signs of heart enlargement [R1]. [R1-IMAGE]
-- The cardiac silhouette is not enlarged [R1]. [R1]
-- There is no consolidation, pleural effusion or pneumothorax. [R1]
+- The cardiac silhouette is not enlarged on the chest X-ray. [R1]
+- There are no signs of heart enlargement on the frontal and lateral radiographs of the chest. [R2]
+- A chest X-ray is just one diagnostic tool, and further evaluation may be needed to assess the patient's overall cardiovascular health. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging with CT chest with contrast is recommended to further investigate the increased size of density in the left cardiophrenic angle [R1]. [R1].</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+- Clinical correlation recommended to assess the patient's overall cardiovascular health. [Rx]
+- Further evaluation with other diagnostic tools (e.g., echocardiogram, electrocardiogram) may be necessary to rule out other cardiac conditions. [Rx]</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="n">
         <v>3</v>
       </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
       <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
         <v>0.584</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0.9284561157226562</v>
-      </c>
       <c r="R10" t="n">
-        <v>0.7562280578613281</v>
-      </c>
-      <c r="S10" t="inlineStr">
+        <v>0.8931018292903899</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.738550914645195</v>
+      </c>
+      <c r="T10" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V10" t="n">
+        <v>2</v>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1345,62 +1359,62 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5868682861328125</v>
+        <v>0.639173150062561</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
-- The lung fields appear to be clear on the chest X-ray [R1]. [R2-IMAGE]
+- The lung fields appear to be clear on the chest X-ray. [R2-IMAGE]
 Supporting Evidence:
-- The lung fields appear to be clear on the chest x-ray, with no visible signs of abnormalities or opacities in the lung tissue [R1]. [R1-IMAGE]
-- The lung fields appear to be clear on the chest x-ray, with no obvious signs of abnormalities or opacities in the lung fields [R1]. [R2-IMAGE]
-- A clear chest x-ray does not necessarily rule out all possible conditions or issues, and further evaluation and clinical correlation may be needed [R1]. [R1-IMAGE]
-- A clear chest x-ray does not necessarily rule out all possible conditions or issues, and further evaluation and clinical correlation may be needed [R1]. [R2-IMAGE]
+- The lungs are normally inflated without evidence of focal airspace disease, pleural effusion, or pneumothorax. [R1]
+- The lung fields appear to be clear on the chest x-ray, indicating no obvious signs of abnormalities or issues within the lung tissue itself. [R2-IMAGE]
+- A clear chest X-ray does not necessarily rule out all possible conditions or issues, and further evaluation may be needed depending on the patient's clinical history and symptoms. [R1-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns [R1]. [Rx]
-- Further evaluation and follow-up imaging may be necessary if symptoms persist or new concerns arise [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
+- Further evaluation and follow-up imaging may be necessary if symptoms persist or if the patient's clinical history and symptoms suggest underlying conditions. [Rx]</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
         <v>0.596</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0.8760604858398438</v>
-      </c>
       <c r="R11" t="n">
-        <v>0.7360302429199219</v>
-      </c>
-      <c r="S11" t="inlineStr">
+        <v>0.8917519450187683</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.7438759725093842</v>
+      </c>
+      <c r="T11" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>2</v>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V11" t="n">
+        <v>2</v>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1433,12 +1447,13 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7799336314201355</v>
+        <v>0.7783669233322144</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The chest X-ray appears normal. [R1]
@@ -1448,46 +1463,46 @@
 - No pneumothorax or pleural effusion. [R1]
 - No acute osseous findings. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
-- Further evaluation may be needed if symptoms persist [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
+- Further evaluation and tests may still be needed depending on the patient's clinical history and symptoms. [R2]</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
       </c>
       <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.593</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0.9339800894260406</v>
-      </c>
       <c r="R12" t="n">
-        <v>0.7634900447130203</v>
-      </c>
-      <c r="S12" t="inlineStr">
+        <v>0.9335100769996643</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.7632550384998321</v>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U12" t="n">
-        <v>2</v>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V12" t="n">
+        <v>2</v>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1520,15 +1535,16 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8429003953933716</v>
+        <v>0.831372857093811</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No acute abnormality detected. [R1]
+- No significant abnormal findings detected on the chest X-ray. [R1]
 Supporting Evidence:
 - Lungs are clear bilaterally. [R1]
 - Cardiac and mediastinal silhouettes are normal. [R1]
@@ -1536,16 +1552,13 @@
 - No pneumothorax or pleural effusion. [R1]
 - No acute bony abnormality. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out non-imaging related conditions. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to rule out other possible conditions. [Rx]
+- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -1554,28 +1567,31 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
         <v>0.61</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0.9528701186180114</v>
-      </c>
       <c r="R13" t="n">
-        <v>0.7814350593090057</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9494118571281432</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.7797059285640716</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U13" t="n">
-        <v>2</v>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V13" t="n">
+        <v>2</v>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1608,30 +1624,28 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7718997001647949</v>
+        <v>0.9065355658531189</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The cardiac silhouette is within normal limits on the chest radiograph [R1]. [R1]
-- Mediastinal contours are within normal limits on the chest radiograph. [R1]
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
+- The cardiac silhouette is borderline enlarged on the chest radiograph from XXXX, XXXX. [R1]
+- The mediastinal contours are within normal limits on the chest radiograph from XXXX, XXXX. [R1]
+- The chest x-ray does not show any large pleural effusion or pneumothorax. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms [R1]. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not suggest the need for immediate further imaging [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the borderline enlarged cardiac silhouette. [Rx]
+- Follow-up imaging if symptoms persist, such as chest pain. [Rx]</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -1640,28 +1654,31 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
         <v>0.637</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0.9315699100494385</v>
-      </c>
       <c r="R14" t="n">
-        <v>0.7842849550247193</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9719606697559355</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.8044803348779678</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U14" t="n">
-        <v>2</v>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V14" t="n">
+        <v>2</v>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1694,30 +1711,29 @@
         <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.75666743516922</v>
+        <v>0.8714293837547302</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No signs of pulmonary congestion or edema detected on the chest X-ray. [R1], [R1-IMAGE], [R2-IMAGE]
+- No signs of pulmonary congestion or edema detected on the chest X-ray. [R1], [R2]
 Supporting Evidence:
-- Heart size within normal limits, stable mediastinal and hilar contours. [R1]
-- No focal alveolar consolidation, no definite pleural effusion seen. [R1]
+- The chest x-ray shows heart size within normal limits, stable mediastinal and hilar contours. [R1]
+- Mild hyperinflation appears similar to prior, with no focal alveolar consolidation or definite pleural effusion seen. [R1]
+- Scattered chronic appearing irregular interstitial markings are present, but no typical findings of pulmonary edema are observed. [R1]
 - The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE], [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms [R1]. [Rx]
-- Follow-up imaging if symptoms persist, but currently, there is no indication for immediate further imaging [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
+- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not appear necessary. [Rx]</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>1</v>
@@ -1726,28 +1742,31 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0.615</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0.927000230550766</v>
-      </c>
       <c r="R15" t="n">
-        <v>0.7710001152753829</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.961428815126419</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7882144075632095</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>2</v>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1780,61 +1799,61 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5569067001342773</v>
+        <v>0.5959613919258118</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No visible pleural effusion on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
+- No visible signs of pleural effusion on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any visible pleural effusion [R1]. [R1-IMAGE]
-- The chest x-ray does not show any visible signs of pleural effusion [R1]. [R2-IMAGE]
-- The absence of visible pleural effusion in a chest x-ray does not necessarily rule out the presence of fluid accumulation in the pleural space [R1]. [R1-IMAGE]
-- Further diagnostic tests, such as a chest CT scan or ultrasound, may be needed to confirm the presence or absence of pleural effusion [R1]. [R1-IMAGE]
+- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
+- The absence of visible findings on a chest x-ray does not necessarily rule out the presence of pleural effusion or other abnormalities. [R1-IMAGE]
+- Lungs are clear, and no pneumothorax or pleural effusion is detected. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the presence of pleural effusion despite negative chest X-ray findings [R1]. [Rx]
-- Follow-up imaging with a chest CT scan or ultrasound if symptoms persist or worsen [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+- Further diagnostic tests and clinical evaluation may be needed to confirm the absence of pleural effusion or detect any underlying issues. [R1-IMAGE]
+- Clinical correlation recommended to assess the patient's symptoms and medical history. [Rx]</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>3</v>
       </c>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
       </c>
       <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0.576</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0.8670720100402831</v>
-      </c>
       <c r="R16" t="n">
-        <v>0.7215360050201416</v>
-      </c>
-      <c r="S16" t="inlineStr">
+        <v>0.8787884175777435</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.7273942087888717</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V16" t="n">
+        <v>2</v>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1864,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1872,7 +1891,8 @@
       <c r="I17" t="n">
         <v>1</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 No pathologies detected above threshold on the chest X-ray. [R1]
@@ -1881,46 +1901,51 @@
 - The absence of pathologies detected by the algorithm suggests that the chest X-ray is likely normal or shows no significant abnormalities. [R2]
 - However, it is essential to note that the absence of findings on a chest X-ray does not rule out the presence of lung consolidation or opacities, especially if they are mild or not severe enough to be detected by the algorithm. [R3]
 Next Steps / Recommendations:
-- Clinical correlation with the patient's symptoms and medical history is recommended to determine the significance of the normal chest X-ray findings. [Rx]
-- If the patient's symptoms persist or worsen, follow-up imaging may be necessary to rule out any underlying conditions [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+- Clinical correlation with the patient's symptoms and medical history is recommended to determine the next course of action. [Rx]
+- Further imaging or diagnostic testing may be necessary if symptoms persist or worsen, despite a normal chest X-ray. [Rx]
+References:
+[R1] - "DenseNet: Densely Connected Convolutional Networks" by Huang et al., 2017 [1]
+[R2] - "Clinical Applications of Deep Learning in Chest Radiography" by Rajpurkar et al., 2018 [2]
+[R3] - "Radiographic Findings in Acute Respiratory Distress Syndrome" by Goodman et al., 2018 [3]
+Note: The references provided are for general knowledge and may not be directly related to the specific clinical question. However, they are relevant to the topic of chest X-ray interpretation and deep learning algorithms.</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
         <v>3</v>
       </c>
-      <c r="M17" t="n">
-        <v>2</v>
-      </c>
       <c r="N17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
       <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0.7</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S17" t="inlineStr">
+        <v>0.6000000000000001</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4500000000000001</v>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U17" t="n">
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1953,31 +1978,29 @@
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7694137692451477</v>
+        <v>0.7941926717758179</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No signs of pneumothorax detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
+- No signs of pneumothorax detected on the chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R1-IMAGE]
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R2-IMAGE]
-- No focal areas of consolidation or suspicious pulmonary opacities were observed on the chest X-ray [R1]. [R1]
-- Osseous structures, including the ribs, were intact on the chest X-ray. [R1]
+- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
+- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
+- No focal areas of consolidation or suspicious pulmonary opacities were observed on the chest X-ray. [R1]
+- Heart size and osseous structures are within normal limits on the chest X-ray. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but no immediate indication for further imaging at this time [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
-        <v>2</v>
-      </c>
+- Follow-up imaging if symptoms persist, but no immediate indication for further imaging at this time. [Rx]</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
@@ -1986,28 +2009,31 @@
         <v>1</v>
       </c>
       <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0.656</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0.9308241307735443</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.7934120653867722</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9382578015327453</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.7971289007663727</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U18" t="n">
-        <v>2</v>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2040,61 +2066,62 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8533682823181152</v>
+        <v>0.8006788492202759</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No acute cardiopulmonary findings detected. [R1]
+- No significant pathologies detected above threshold. [R1], [R2]
 Supporting Evidence:
 - Heart size within normal limits. [R1]
 - No focal alveolar consolidation, no definite pleural effusion seen. [R1]
 - No typical findings of pulmonary edema. [R1]
 - No pneumothorax. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, as the current findings may not fully explain the patient's presentation [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+- Clinical correlation recommended. [Rx]
+- Insufficient evidence [Rx]</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
         <v>3</v>
       </c>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
       <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
         <v>0.592</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0.9560104846954345</v>
-      </c>
       <c r="R19" t="n">
-        <v>0.7740052423477173</v>
-      </c>
-      <c r="S19" t="inlineStr">
+        <v>0.9402036547660827</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.7661018273830413</v>
+      </c>
+      <c r="T19" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>2</v>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2127,61 +2154,62 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5240681171417236</v>
+        <v>0.5309703946113586</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No heart enlargement detected. [R1], [R2]
+- No heart enlargement detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest X-ray does not show any signs of heart enlargement [R1]. [R2-IMAGE]
-- Heart size is normal on the X-ray findings [R1]. [R1]
-- No signs of heart enlargement were observed on the chest X-ray. [R1], [R2]
+- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
+- Heart size is normal on the X-ray findings. [R1]
+- No signs of heart enlargement were observed on the chest X-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Further diagnostic testing may be necessary if symptoms persist or worsen [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+- Clinical correlation recommended to confirm the absence of heart enlargement. [Rx]
+- Further evaluation with echocardiography or other diagnostic tests may be necessary if symptoms persist. [Rx]</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
         <v>3</v>
       </c>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
         <v>0.589</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0.857220435142517</v>
-      </c>
       <c r="R20" t="n">
-        <v>0.7231102175712585</v>
-      </c>
-      <c r="S20" t="inlineStr">
+        <v>0.8592911183834075</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.7241455591917038</v>
+      </c>
+      <c r="T20" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>2</v>
-      </c>
-      <c r="V20" t="inlineStr">
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2214,61 +2242,63 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6592944860458374</v>
+        <v>0.6538283228874207</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
+- The lung fields appear to be clear on the chest X-ray. [R2-IMAGE]
 Supporting Evidence:
-- The lungs are well expanded and clear [R1]. [R1]
-- The lung fields appear to be clear on the chest X-ray. [R2-IMAGE]
-- There are no focal air space opacities [R1]. [R1]
-- The lung fields appear to be clear on the chest X-ray. [R2-IMAGE]
+- The lungs are well expanded and clear. [R1]
+- There are no focal air space opacities. [R1]
+- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
+- The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns [R1]. [Rx]
-- Further evaluation and testing may be needed to rule out all possible conditions, as a clear chest X-ray does not necessarily rule out all possible conditions [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
+- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0.594</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0.8977883458137512</v>
-      </c>
       <c r="R21" t="n">
-        <v>0.7458941729068755</v>
-      </c>
-      <c r="S21" t="inlineStr">
+        <v>0.8961484968662261</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.745074248433113</v>
+      </c>
+      <c r="T21" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>2</v>
-      </c>
-      <c r="V21" t="inlineStr">
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2301,61 +2331,63 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6545531749725342</v>
+        <v>0.4736593961715698</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1]
+- The chest X-ray appears normal. [R1-IMAGE]
+- The chest X-ray appears normal. [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray shows heart size normal. [R1]
-- Mediastinal silhouettes and pulmonary vascularity are within normal limits. [R1]
-- No focal consolidations or pleural effusions. [R1]
-- No pneumothorax. [R1]
+- The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
+- A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE]
+- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [R1-IMAGE]
+- The chest x-ray appears to be normal, which means that there are no visible abnormalities or signs of disease in the image. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
-- Further evaluation and tests may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray [R1]. [R2].</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
+- Further evaluation and tests may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
         <v>3</v>
       </c>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
       </c>
       <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0.584</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0.8963659524917602</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.74018297624588</v>
-      </c>
-      <c r="S22" t="inlineStr">
+        <v>0.8420978188514709</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.7130489094257355</v>
+      </c>
+      <c r="T22" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>2</v>
-      </c>
-      <c r="V22" t="inlineStr">
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2388,30 +2420,28 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7767394781112671</v>
+        <v>0.8572167754173279</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No acute abnormality detected. [R1]
+- No abnormal findings detected on the chest X-ray. [R1]
 Supporting Evidence:
 - The lungs are clear, and without focal air space opacity. [R1]
 - The cardiomediastinal silhouette is normal in size and contour, and stable. [R1]
-- The chest X-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
+- No pneumothorax or large pleural effusion is visible. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and history [R1]. [Rx]
-- Follow-up imaging if symptoms persist, as a normal chest X-ray does not rule out all possible conditions [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
+- Follow-up imaging if symptoms persist, but currently, the chest X-ray appears normal. [Rx]</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N23" t="n">
         <v>1</v>
@@ -2420,28 +2450,31 @@
         <v>1</v>
       </c>
       <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
         <v>0.601</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0.9330218434333801</v>
-      </c>
       <c r="R23" t="n">
-        <v>0.7670109217166901</v>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9571650326251984</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.7790825163125992</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U23" t="n">
-        <v>2</v>
-      </c>
-      <c r="V23" t="inlineStr">
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>2</v>
+      </c>
+      <c r="W23" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2474,60 +2507,61 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5237517356872559</v>
+        <v>0.6918138265609741</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No evidence of cardiomegaly or abnormal cardiac silhouette on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
+- No signs of cardiomegaly or abnormal cardiac silhouette are seen on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any signs of cardiomegaly [R1]. [R1-IMAGE]
-- The heart appears to be within normal size and shape in the image [R1]. [R1-IMAGE]
-- The chest x-ray does not show any signs of an abnormal cardiac silhouette [R1]. [R2-IMAGE]
+- The heart size appears within normal limits on the chest X-ray. [R1]
+- The lungs are free of focal airspace disease, and no pleural effusion or pneumothorax is seen. [R1]
+- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other potential causes of nausea and vomiting [R1]. [Rx]
-- Further diagnostic evaluation may be necessary if symptoms persist [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+- Clinical correlation recommended to further evaluate the patient's symptoms of nausea and vomiting. [Rx]
+- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not appear necessary. [Rx]</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
         <v>3</v>
       </c>
-      <c r="M24" t="n">
-        <v>2</v>
-      </c>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
       </c>
       <c r="P24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="n">
         <v>0.536</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0.8571255207061768</v>
-      </c>
       <c r="R24" t="n">
-        <v>0.6965627603530884</v>
-      </c>
-      <c r="S24" t="inlineStr">
+        <v>0.9075441479682922</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.7217720739841461</v>
+      </c>
+      <c r="T24" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U24" t="n">
-        <v>2</v>
-      </c>
-      <c r="V24" t="inlineStr">
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>2</v>
+      </c>
+      <c r="W24" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2560,61 +2594,62 @@
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6989673376083374</v>
+        <v>0.6326154470443726</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any signs of pulmonary congestion or edema [R1]. [R1-IMAGE]
-- The chest x-ray does not show any signs of pulmonary congestion or edema [R1]. [R2-IMAGE]
-- Cardiomediastinal silhouette is within normal limits of size and appearance, indicating no acute cardiopulmonary abnormality [R1]. [R1]
-- Lungs are expanded and clear of airspace disease, further supporting the absence of pulmonary congestion or edema. [R1]
+- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
+- The pulmonary vascularity is unremarkable, which is consistent with the absence of pulmonary congestion. [R1]
+- Lungs are expanded and clear of airspace disease, further supporting the absence of pulmonary edema. [R1]
+- The chest x-ray findings are negative for pneumothorax or pleural effusion, which can sometimes be associated with pulmonary congestion or edema. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's symptoms and overall clinical picture. [Rx]
-- Follow-up imaging if symptoms persist or worsen, but currently, no indication for further imaging [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+- Clinical correlation recommended to further evaluate the patient's symptoms of dyspnea. [Rx]
+- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it is unlikely to show signs of pulmonary congestion or edema. [Rx]</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
         <v>3</v>
       </c>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
       </c>
       <c r="P25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="n">
         <v>0.5669999999999999</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0.9096902012825012</v>
-      </c>
       <c r="R25" t="n">
-        <v>0.7383451006412506</v>
-      </c>
-      <c r="S25" t="inlineStr">
+        <v>0.8897846341133118</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.7283923170566559</v>
+      </c>
+      <c r="T25" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U25" t="n">
-        <v>2</v>
-      </c>
-      <c r="V25" t="inlineStr">
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>2</v>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2647,60 +2682,61 @@
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7680481672286987</v>
+        <v>0.644819974899292</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - Pleural effusion is visible on the chest X-ray, with moderate left pleural effusion and small right pleural effusion detected. [R1]
 Supporting Evidence:
-- The chest x-ray shows surgical suture material projecting over the right lung apex, indicating a previous surgical intervention. [R1]
-- The lungs are hyperlucent and hyperinflated, compatible with emphysema, which may be contributing to the pleural effusions. [R1]
-- There is left lower lobe airspace disease identified, which may be secondary to inhalational injury. [R1]
+- The lungs are hyperlucent and hyperinflated compatible with emphysema, which may be contributing to the pleural effusion. [R1]
+- There is moderate left pleural effusion and small right pleural effusion identified on the chest X-ray. [R1]
+- The absence of visible pleural effusion on [R2-IMAGE] and [R1-IMAGE] may be due to the limitations of the imaging modality or the presence of other conditions that mask the effusion. [R2-IMAGE, R1-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to determine the cause of the pleural effusions. [Rx]
-- Follow-up imaging if symptoms persist to assess the resolution of the pleural effusions [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
+- Clinical correlation with patient symptoms and medical history is recommended to determine the cause and significance of the pleural effusion. [Rx]
+- Further imaging or diagnostic testing may be necessary to confirm the presence and extent of the pleural effusion. [Rx]</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
         <v>3</v>
       </c>
-      <c r="M26" t="n">
-        <v>2</v>
-      </c>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
       </c>
       <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
         <v>0.586</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0.9304144501686096</v>
-      </c>
       <c r="R26" t="n">
-        <v>0.7582072250843048</v>
-      </c>
-      <c r="S26" t="inlineStr">
+        <v>0.8934459924697875</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.7397229962348937</v>
+      </c>
+      <c r="T26" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U26" t="n">
-        <v>2</v>
-      </c>
-      <c r="V26" t="inlineStr">
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V26" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2733,60 +2769,62 @@
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5265747308731079</v>
+        <v>0.6798410415649414</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No lung consolidation or opacities detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest X-ray does not show any lung consolidation or opacities [R1]. [R1-IMAGE]
-- The chest X-ray does not show any lung consolidation or opacities [R1]. [R2-IMAGE]
-- The lungs are clear on the chest X-ray [R1]. [R1]
+- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE]
+- The chest X-ray does not show any lung consolidation or opacities. [R2-IMAGE]
+- The lungs are clear on the X-ray. [R1]
+- The cardiac contours are normal, and thoracic spondylosis is present, but these findings are not relevant to the question of lung consolidation or opacities. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist or worsen [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+- Clinical correlation recommended to assess the presence of symptoms or other clinical findings that may be related to thoracic spondylosis. [Rx]
+- No further imaging is recommended at this time, but follow-up imaging may be necessary if symptoms persist or worsen. [Rx]</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
         <v>3</v>
       </c>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
       </c>
       <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0.8579724192619324</v>
-      </c>
       <c r="R27" t="n">
-        <v>0.7104862096309661</v>
-      </c>
-      <c r="S27" t="inlineStr">
+        <v>0.9039523124694824</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.7334761562347412</v>
+      </c>
+      <c r="T27" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" t="inlineStr">
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V27" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2819,61 +2857,62 @@
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6966155767440796</v>
+        <v>0.704419732093811</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pneumothorax detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R1-IMAGE]
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R2-IMAGE]
-- Lungs are overall hyperexpanded with flattening of the diaphragms, which is consistent with chronic lung disease but does not indicate pneumothorax [R1]. [R1]
+- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
+- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
+- Lungs are overall hyperexpanded with flattening of the diaphragms, which is consistent with chronic obstructive pulmonary disease (COPD) but does not indicate pneumothorax. [R1]
 - No focal consolidation, pleural effusions, or pneumothoraces are present on the chest x-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist or worsen [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
+- Clinical correlation with patient symptoms and medical history is recommended. [Rx]
+- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
         <v>3</v>
       </c>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
       </c>
       <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
         <v>0.572</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0.9089846730232238</v>
-      </c>
       <c r="R28" t="n">
-        <v>0.7404923365116118</v>
-      </c>
-      <c r="S28" t="inlineStr">
+        <v>0.9113259196281432</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.7416629598140716</v>
+      </c>
+      <c r="T28" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" t="inlineStr">
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V28" t="n">
+        <v>2</v>
+      </c>
+      <c r="W28" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2906,61 +2945,61 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7954099178314209</v>
+        <v>0.7265353798866272</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Bilateral patchy pulmonary opacities and pulmonary vascular congestion are noted, most consistent with atelectasis/infiltrate. [R1]
+- Cardiomegaly and bilateral pleural effusions are present. [R1-IMAGE]
 Supporting Evidence:
-- Bilateral patchy pulmonary opacities are noted, most consistent with atelectasis/infiltrate. [R1]
-- Pulmonary vascular congestion is again noted. [R1]
-- No large pleural effusions are observed. [R1]
-- No evidence of pneumothorax is noted. [R1]
+- Cardiomegaly, an enlargement of the heart, is noted on the chest X-ray. [R1-IMAGE]
+- Bilateral pleural effusions, abnormal accumulations of fluid in the pleural space surrounding both lungs, are observed. [R1-IMAGE]
+- Pulmonary vascular congestion is also present, suggesting an underlying issue affecting the patient's lungs and heart. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to determine the underlying cause of the pulmonary opacities and vascular congestion. [Rx]
-- Follow-up imaging if symptoms persist to assess for any changes in the patient's condition [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
+- Clinical correlation with the patient's symptoms and history is recommended. [Rx]
+- Follow-up imaging if symptoms persist, as the current findings suggest a potential underlying issue. [Rx]</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
         <v>3</v>
       </c>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
       <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0.9386229753494262</v>
-      </c>
       <c r="R29" t="n">
-        <v>0.7493114876747131</v>
-      </c>
-      <c r="S29" t="inlineStr">
+        <v>0.9179606139659882</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.7389803069829941</v>
+      </c>
+      <c r="T29" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U29" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" t="inlineStr">
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V29" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2993,61 +3032,61 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5036354064941406</v>
+        <v>0.567784309387207</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No heart enlargement detected. [R1], [R2]
+- Insufficient evidence [R1], [R2] to indicate heart enlargement.
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest X-ray does not show any signs of heart enlargement [R1]. [R2-IMAGE]
-- Borderline heart size is reported, but this does not indicate heart enlargement [R1]. [R1]
-- The impression of borderline heart size is not supported by the image analysis. [R1-IMAGE]
+- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
+- No significant pathologies detected above threshold, including heart enlargement. [R2]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the significance of borderline heart size [R1]. [Rx]
-- Follow-up imaging if symptoms persist or if the clinical correlation is inconclusive [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
+- Clinical correlation recommended to further evaluate symptoms of hypoxia. [Rx]
+- Further diagnostic testing, such as echocardiogram or electrocardiogram, may be necessary to assess heart function. [Rx]</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
         <v>3</v>
       </c>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
       </c>
       <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.546</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0.8510906219482421</v>
-      </c>
       <c r="R30" t="n">
-        <v>0.6985453109741211</v>
-      </c>
-      <c r="S30" t="inlineStr">
+        <v>0.8703352928161621</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.7081676464080811</v>
+      </c>
+      <c r="T30" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
-      <c r="V30" t="inlineStr">
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>2</v>
+      </c>
+      <c r="W30" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3080,61 +3119,61 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7140219211578369</v>
+        <v>0.7765252590179443</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
 Supporting Evidence:
-- The chest x-ray shows lungs that are clear without focal consolidation, effusion, or pneumothorax [R1]. [R1]
+- The chest x-ray shows lungs that are clear without focal consolidation, effusion, or pneumothorax. [R1]
 - The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
-- The chest x-ray is negative for pneumoperitoneum [R1]. [R1]
-- The lung fields are grossly unremarkable on the chest x-ray. [R1]
+- Normal heart size and negative for pneumoperitoneum are also noted on the chest x-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying conditions that may not be visible on the x-ray. [Rx]
-- Further evaluation may be needed depending on the patient's clinical history and symptoms [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
+- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
+- Further evaluation may be needed to rule out all possible conditions or issues. [Rx]</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
         <v>3</v>
       </c>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
       </c>
       <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
         <v>0.582</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0.914206576347351</v>
-      </c>
       <c r="R31" t="n">
-        <v>0.7481032881736756</v>
-      </c>
-      <c r="S31" t="inlineStr">
+        <v>0.9329575777053832</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.7574787888526916</v>
+      </c>
+      <c r="T31" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" t="inlineStr">
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V31" t="n">
+        <v>2</v>
+      </c>
+      <c r="W31" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3167,60 +3206,62 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5699558258056641</v>
+        <v>0.5923786759376526</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1-IMAGE], [R2-IMAGE]
+- The chest X-ray appears normal. [R1-IMAGE]
 Supporting Evidence:
-- The chest x-ray shows no visible signs of abnormalities or issues in the image [R1]. [R1-IMAGE]
-- A normal chest x-ray does not necessarily rule out all possible conditions or diseases [R1]. [R1-IMAGE], [R2-IMAGE]
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray [R1]. [R2-IMAGE]
+- The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
+- A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE]
+- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues. [R1-IMAGE]
+- The chest x-ray appears to be normal, which means that there are no visible abnormalities or signs of disease in the image. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray [R1]. [Rx]
-- Further evaluation and tests may still be needed depending on the patient's symptoms and clinical history [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
+- Further evaluation may be needed to rule out all possible conditions or diseases. [Rx]</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
         <v>3</v>
       </c>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
       <c r="P32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q32" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0.8709867477416992</v>
-      </c>
       <c r="R32" t="n">
-        <v>0.7164933738708497</v>
-      </c>
-      <c r="S32" t="inlineStr">
+        <v>0.8777136027812957</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0.7198568013906479</v>
+      </c>
+      <c r="T32" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" t="inlineStr">
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V32" t="n">
+        <v>2</v>
+      </c>
+      <c r="W32" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3253,12 +3294,13 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8247405886650085</v>
+        <v>0.8103905916213989</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No acute abnormality detected. [R1]
@@ -3269,15 +3311,12 @@
 - The lungs are otherwise grossly clear. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
-- Follow-up imaging if symptoms persist, as a normal chest X-ray does not rule out all possible conditions [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
-        <v>2</v>
-      </c>
+- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N33" t="n">
         <v>1</v>
@@ -3286,28 +3325,31 @@
         <v>1</v>
       </c>
       <c r="P33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="n">
         <v>0.611</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0.9474221765995026</v>
-      </c>
       <c r="R33" t="n">
-        <v>0.7792110882997513</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9431171774864197</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0.7770585887432098</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U33" t="n">
-        <v>2</v>
-      </c>
-      <c r="V33" t="inlineStr">
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V33" t="n">
+        <v>2</v>
+      </c>
+      <c r="W33" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3340,60 +3382,61 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6621993184089661</v>
+        <v>0.6666450500488281</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray does not show signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
+- No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- Cardiac and mediastinal contours are within normal limits on the chest X-ray [R1]. [R1]
-- The lungs are clear on the chest X-ray. [R1]
-- Bony structures are intact on the chest X-ray. [R1]
+- Cardiac and mediastinal contours are within normal limits on chest X-ray. [R1]
+- The lungs are clear on chest X-ray. [R1]
+- Bony structures are intact on chest X-ray. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's cardiac status. [Rx]
-- Follow-up imaging if symptoms persist or new cardiac symptoms develop [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+- Follow-up imaging if symptoms persist or new cardiac symptoms develop. [Rx]</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
         <v>3</v>
       </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
       </c>
       <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
         <v>0.599</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0.8986597955226898</v>
-      </c>
       <c r="R34" t="n">
-        <v>0.7488298977613449</v>
-      </c>
-      <c r="S34" t="inlineStr">
+        <v>0.8999935150146484</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.7494967575073241</v>
+      </c>
+      <c r="T34" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U34" t="n">
-        <v>2</v>
-      </c>
-      <c r="V34" t="inlineStr">
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V34" t="n">
+        <v>2</v>
+      </c>
+      <c r="W34" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3431,25 +3474,23 @@
       <c r="I35" t="n">
         <v>1</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any signs of pulmonary congestion or edema [R1]. [R1-IMAGE]
-- The lungs are clear, without evidence of infiltrate [R1]. [R1]
+- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
+- The lungs are clear, without evidence of infiltrate. [R1]
 - The chest x-ray does not show any signs of pulmonary congestion or edema. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms [R1]. [Rx]
-- Follow-up imaging if symptoms persist, but currently, there is no indication for immediate further imaging [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but currently, there is no indication for immediate further imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N35" t="n">
         <v>1</v>
@@ -3458,28 +3499,31 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q35" t="n">
         <v>0.601</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>0.8853358685970306</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>0.7431679342985154</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="T35" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U35" t="n">
-        <v>2</v>
-      </c>
-      <c r="V35" t="inlineStr">
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V35" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3512,30 +3556,29 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6349834203720093</v>
+        <v>0.579179048538208</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No pleural effusion visible on the chest X-ray. [R1], [R2]
 Supporting Evidence:
 - The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest X-ray does not show any visible pleural effusion [R1]. [R2-IMAGE]
-- The absence of focal airspace opacity or pleural effusion is noted in the radiographic findings [R1]. [R1]
+- The chest x-ray does not show any visible signs of pleural effusion. [R2-IMAGE]
+- The findings of the chest X-ray are consistent with no pleural effusion. [R1]
+- The absence of pleural effusion is confirmed by the radiographic examination. [R2]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's symptoms and medical history. [Rx]
-- Further diagnostic testing may be necessary if symptoms persist or worsen [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess the patient's overall condition. [Rx]
+- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N36" t="n">
         <v>1</v>
@@ -3544,28 +3587,31 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q36" t="n">
         <v>0.605</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0.8904950261116027</v>
-      </c>
       <c r="R36" t="n">
-        <v>0.7477475130558013</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8737537145614623</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.7393768572807311</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U36" t="n">
-        <v>2</v>
-      </c>
-      <c r="V36" t="inlineStr">
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V36" t="n">
+        <v>2</v>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3598,30 +3644,28 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.6977760791778564</v>
+        <v>0.7740131020545959</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No lung consolidation or opacities detected on chest X-ray. [R1], [R1-IMAGE], [R2-IMAGE]
+- No lung consolidation or opacities detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
 - The lungs are clear bilaterally, with no evidence of focal consolidation. [R1]
-- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE]
-- The chest X-ray does not show any lung consolidation or opacities [R1]. [R2-IMAGE]
+- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE], [R2-IMAGE]
+- No evidence of pneumothorax or pleural effusion is seen on the chest radiograph. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms [R1]. [Rx]
-- Follow-up imaging if symptoms persist, but currently, no indication for immediate further imaging [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but based on current evidence, no immediate need for further imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N37" t="n">
         <v>1</v>
@@ -3630,28 +3674,31 @@
         <v>1</v>
       </c>
       <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
         <v>0.616</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0.9093328237533569</v>
-      </c>
       <c r="R37" t="n">
-        <v>0.7626664118766784</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9322039306163787</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.7741019653081893</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="U37" t="n">
-        <v>2</v>
-      </c>
-      <c r="V37" t="inlineStr">
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V37" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3684,60 +3731,61 @@
         <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.4395314157009125</v>
+        <v>0.5247206687927246</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pneumothorax detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R1-IMAGE]
-- The chest x-ray does not show any signs of pneumothorax [R1]. [R2-IMAGE]
-- The lungs are otherwise grossly clear, indicating no acute disease [R1]. [R1]
+- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
+- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
+- The lungs are otherwise grossly clear, which is consistent with no pneumothorax. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, pneumothorax is unlikely [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+- Clinical correlation recommended to rule out other causes of hypoxia. [Rx]
+- Further evaluation of the patient's symptoms and medical history is necessary to determine the cause of hypoxia. [Rx]</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
         <v>3</v>
       </c>
-      <c r="M38" t="n">
-        <v>2</v>
-      </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
       </c>
       <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
         <v>0.536</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0.8318594247102737</v>
-      </c>
       <c r="R38" t="n">
-        <v>0.6839297123551369</v>
-      </c>
-      <c r="S38" t="inlineStr">
+        <v>0.8574162006378173</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.6967081003189086</v>
+      </c>
+      <c r="T38" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U38" t="n">
-        <v>2</v>
-      </c>
-      <c r="V38" t="inlineStr">
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V38" t="n">
+        <v>2</v>
+      </c>
+      <c r="W38" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3770,60 +3818,61 @@
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8206111192703247</v>
+        <v>0.8801039457321167</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray shows no acute cardiopulmonary process. [R1]
+- No significant pathologies detected above threshold. [R1]
 Supporting Evidence:
 - Lungs are clear with no pneumothorax or pleural effusion. [R1]
 - The heart and mediastinum are within normal limits. [R1]
 - Bony structures are intact. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further investigate the patient's symptoms of XXXX and shortness of breath. [Rx]
-- Follow-up imaging if symptoms persist, as the widened mediastinum and enlarged cardiac silhouette on the second X-ray may indicate underlying conditions that require further evaluation [R1]. [R2-IMAGE] [R1].</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
+- Follow-up imaging if symptoms persist, as the current findings do not explain the patient's shortness of breath. [Rx]</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="n">
         <v>3</v>
       </c>
-      <c r="M39" t="n">
-        <v>2</v>
-      </c>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
       </c>
       <c r="P39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q39" t="n">
         <v>0.587</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0.9461833357810974</v>
-      </c>
       <c r="R39" t="n">
-        <v>0.7665916678905487</v>
-      </c>
-      <c r="S39" t="inlineStr">
+        <v>0.9640311837196349</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0.7755155918598174</v>
+      </c>
+      <c r="T39" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U39" t="n">
-        <v>2</v>
-      </c>
-      <c r="V39" t="inlineStr">
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V39" t="n">
+        <v>2</v>
+      </c>
+      <c r="W39" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3856,61 +3905,62 @@
         <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.5888468027114868</v>
+        <v>0.5847504734992981</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Insufficient evidence to indicate heart enlargement. [R1-IMAGE], [R2-IMAGE]
+- Insufficient evidence to indicate heart enlargement. [R1], [R2]
 Supporting Evidence:
-- The chest X-ray does not show any signs of heart enlargement [R1]. [R1-IMAGE]
-- The chest X-ray does not show any signs of heart enlargement [R1]. [R2-IMAGE]
-- The heart and mediastinum appear normal on the chest X-ray [R1]. [R1]
+- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
+- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
+- The heart and mediastinum are normal on the chest X-ray. [R1]
 - Both lungs are clear and expanded on the chest X-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate cardiac function. [Rx]
-- Follow-up imaging if symptoms persist or cardiac function is suspected to be abnormal [R1]. [Rx] [R1].</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but based on current evidence, it is not indicated. [Rx]</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
         <v>3</v>
       </c>
-      <c r="M40" t="n">
-        <v>2</v>
-      </c>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
       </c>
       <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0.876654040813446</v>
-      </c>
       <c r="R40" t="n">
-        <v>0.703327020406723</v>
-      </c>
-      <c r="S40" t="inlineStr">
+        <v>0.8754251420497894</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.7027125710248947</v>
+      </c>
+      <c r="T40" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="U40" t="n">
-        <v>2</v>
-      </c>
-      <c r="V40" t="inlineStr">
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V40" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>

--- a/mmrag_evaluation_results.xlsx
+++ b/mmrag_evaluation_results.xlsx
@@ -572,7 +572,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7098313570022583</v>
+        <v>0.7120616436004639</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -588,7 +588,7 @@
 - The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R1-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
-- Further evaluation and diagnostic tests may be needed to rule out all possible conditions or diseases. [Rx]</t>
+- Further evaluation may be needed to rule out all possible conditions or diseases. [Rx]</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -605,13 +605,13 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6</v>
+        <v>0.633</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9129494071006774</v>
+        <v>0.9136184930801391</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7564747035503387</v>
+        <v>0.7733092465400695</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -659,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5581897497177124</v>
+        <v>0.5893280506134033</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -668,22 +668,22 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Borderline cardiomegaly detected. [R1]
+- Borderline cardiomegaly and enlarged pulmonary arteries detected. [R1]
 Supporting Evidence:
-- The chest X-ray shows borderline cardiomegaly. [R1]
-- Enlarged pulmonary arteries are visible on the X-ray. [R1]
-- Clear lungs are observed on the X-ray. [R1]
+- The chest X-ray shows borderline cardiomegaly, which is an indication of possible heart enlargement. [R1]
+- Enlarged pulmonary arteries are visible on the X-ray, which may be related to various conditions such as pulmonary hypertension or heart failure. [R1]
+- The lungs appear clear, which suggests that there is no apparent lung disease. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with patient's symptoms and medical history is recommended. [Rx]
-- Further evaluation with echocardiogram or other diagnostic tests may be necessary to confirm the diagnosis of borderline cardiomegaly. [Rx]</t>
+- Clinical correlation with the patient's history and symptoms is recommended to determine the significance of these findings. [Rx]
+- Further evaluation with echocardiography or other imaging modalities may be necessary to assess the heart function and pulmonary artery pressures. [Rx]</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -692,17 +692,17 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.577</v>
+        <v>0.576</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8674569249153137</v>
+        <v>0.8767984151840209</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7222284624576568</v>
+        <v>0.7263992075920105</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -768,10 +768,10 @@
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -780,17 +780,17 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.572</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="R4" t="n">
         <v>0.8693061828613281</v>
       </c>
       <c r="S4" t="n">
-        <v>0.720653091430664</v>
+        <v>0.716653091430664</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -855,10 +855,10 @@
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -867,17 +867,17 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.531</v>
       </c>
       <c r="R5" t="n">
         <v>0.9214602708816528</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7402301354408265</v>
+        <v>0.7262301354408265</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6969091296195984</v>
+        <v>0.6938239932060242</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -932,13 +932,13 @@
           <t>Diagnosis / Impression:
 - No pleural effusion visible on the chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
+- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
 - The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
 - The cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion. [R1]
 - There is no pneumothorax or pleural effusion, as stated in the radiologist's report. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess for other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current evidence, it is unlikely that pleural effusion will be detected. [Rx]</t>
+- Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely that pleural effusion will be detected. [Rx]</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.604</v>
+        <v>0.644</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9090727388858795</v>
+        <v>0.9081471979618072</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7565363694429397</v>
+        <v>0.7760735989809036</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1043,17 +1043,17 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.586</v>
+        <v>0.599</v>
       </c>
       <c r="R7" t="n">
         <v>0.9099273264408111</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7479636632204055</v>
+        <v>0.7544636632204056</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1118,10 +1118,10 @@
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1130,17 +1130,17 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.534</v>
+        <v>0.468</v>
       </c>
       <c r="R8" t="n">
         <v>0.8241634428501129</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6790817214250564</v>
+        <v>0.6460817214250565</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1184,7 +1184,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8050918579101562</v>
+        <v>0.8091067671775818</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1197,19 +1197,18 @@
 Supporting Evidence:
 - The heart, pulmonary structures, and mediastinum are within normal limits. [R1]
 - There is no pleural effusion or pneumothorax. [R1]
-- The chest X-ray shows several key findings, including bilateral pneumothorax, multiple rib fractures, and a left-sided hemopneumothorax. [R1-IMAGE]
-- The chest X-ray also reveals a right-sided pneumothorax with a chest tube in place. [R1-IMAGE]
+- The chest X-ray shows several key findings, including a right-sided pneumothorax, a left-sided pleural effusion, and an elevated hemidiaphragm. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms and history of mitral valve prolapse. [Rx]
-- Follow-up imaging if symptoms persist, particularly dyspnea, to rule out any underlying conditions. [Rx]</t>
+- Follow-up imaging if symptoms persist, particularly if the patient's condition worsens or new symptoms develop. [Rx]</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1218,17 +1217,17 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.573</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9415275573730468</v>
+        <v>0.9427320301532744</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7572637786865234</v>
+        <v>0.7538660150766372</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1272,7 +1271,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6436727643013</v>
+        <v>0.60411536693573</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1281,22 +1280,21 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No signs of heart enlargement detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
+- No signs of heart enlargement detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
 - The cardiac silhouette is not enlarged on the chest X-ray. [R1]
-- There are no signs of heart enlargement on the frontal and lateral radiographs of the chest. [R2]
-- A chest X-ray is just one diagnostic tool, and further evaluation may be needed to assess the patient's overall cardiovascular health. [R2-IMAGE]
+- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE], [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall cardiovascular health. [Rx]
-- Further evaluation with other diagnostic tools (e.g., echocardiogram, electrocardiogram) may be necessary to rule out other cardiac conditions. [Rx]</t>
+- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but no immediate indication for further imaging based on current chest X-ray findings. [Rx]</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1305,17 +1303,17 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.584</v>
+        <v>0.594</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8931018292903899</v>
+        <v>0.8812346100807189</v>
       </c>
       <c r="S10" t="n">
-        <v>0.738550914645195</v>
+        <v>0.7376173050403594</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1359,7 +1357,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.639173150062561</v>
+        <v>0.6518317461013794</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1372,19 +1370,19 @@
 - The lung fields appear to be clear on the chest X-ray. [R2-IMAGE]
 Supporting Evidence:
 - The lungs are normally inflated without evidence of focal airspace disease, pleural effusion, or pneumothorax. [R1]
-- The lung fields appear to be clear on the chest x-ray, indicating no obvious signs of abnormalities or issues within the lung tissue itself. [R2-IMAGE]
-- A clear chest X-ray does not necessarily rule out all possible conditions or issues, and further evaluation may be needed depending on the patient's clinical history and symptoms. [R1-IMAGE]
+- The lung fields appear to be clear on the chest x-ray, with no obvious signs of abnormalities or opacities in the lung fields. [R2-IMAGE]
+- A clear chest x-ray is generally a positive finding, indicating healthy lung function. [R1-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
-- Further evaluation and follow-up imaging may be necessary if symptoms persist or if the patient's clinical history and symptoms suggest underlying conditions. [Rx]</t>
+- Clinical correlation recommended to rule out all possible conditions or issues, as a clear chest x-ray does not necessarily rule out all possible lung conditions. [Rx]
+- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1393,17 +1391,17 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.596</v>
+        <v>0.622</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8917519450187683</v>
+        <v>0.8955495238304138</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7438759725093842</v>
+        <v>0.7587747619152069</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1447,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7783669233322144</v>
+        <v>0.7782972455024719</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1463,16 +1461,16 @@
 - No pneumothorax or pleural effusion. [R1]
 - No acute osseous findings. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
-- Further evaluation and tests may still be needed depending on the patient's clinical history and symptoms. [R2]</t>
+- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
+- Further evaluation may be needed if symptoms persist. [Rx]</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1481,17 +1479,17 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.593</v>
+        <v>0.617</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9335100769996643</v>
+        <v>0.9334891736507416</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7632550384998321</v>
+        <v>0.7752445868253708</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1535,7 +1533,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.831372857093811</v>
+        <v>0.8339194059371948</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -1544,7 +1542,7 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No significant abnormal findings detected on the chest X-ray. [R1]
+- No abnormal findings detected on the chest X-ray. [R1]
 Supporting Evidence:
 - Lungs are clear bilaterally. [R1]
 - Cardiac and mediastinal silhouettes are normal. [R1]
@@ -1552,8 +1550,8 @@
 - No pneumothorax or pleural effusion. [R1]
 - No acute bony abnormality. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other possible conditions. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
+- Clinical correlation recommended to rule out conditions not visible on chest X-ray. [Rx]
+- Follow-up imaging if symptoms persist or clinical history suggests underlying condition. [Rx]</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1570,13 +1568,13 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.61</v>
+        <v>0.659</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9494118571281432</v>
+        <v>0.9501758217811584</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7797059285640716</v>
+        <v>0.8045879108905792</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1624,7 +1622,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9065355658531189</v>
+        <v>0.8963230848312378</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1635,12 +1633,13 @@
           <t>Diagnosis / Impression:
 - The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The cardiac silhouette is borderline enlarged on the chest radiograph from XXXX, XXXX. [R1]
+- The cardiac silhouette is borderline enlarged on the chest radiograph from XXXX, XXXX, but this is not consistent with the image findings. [R1]
 - The mediastinal contours are within normal limits on the chest radiograph from XXXX, XXXX. [R1]
 - The chest x-ray does not show any large pleural effusion or pneumothorax. [R1]
+- The heart appears to be within normal size and shape in the image. [R1-IMAGE], [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the borderline enlarged cardiac silhouette. [Rx]
-- Follow-up imaging if symptoms persist, such as chest pain. [Rx]</t>
+- Follow-up imaging if symptoms persist, but the current chest X-ray does not show any signs of cardiomegaly or abnormal cardiac silhouette. [Rx]</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1657,13 +1656,13 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.637</v>
+        <v>0.726</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9719606697559355</v>
+        <v>0.9688969254493713</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8044803348779678</v>
+        <v>0.8474484627246857</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1745,13 +1744,13 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.615</v>
+        <v>0.67</v>
       </c>
       <c r="R15" t="n">
         <v>0.961428815126419</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7882144075632095</v>
+        <v>0.8157144075632095</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1799,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5959613919258118</v>
+        <v>0.5888155698776245</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
@@ -1808,22 +1807,22 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No visible signs of pleural effusion on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
+- Insufficient evidence to determine the presence of pleural effusion on the chest X-ray. [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The absence of visible findings on a chest x-ray does not necessarily rule out the presence of pleural effusion or other abnormalities. [R1-IMAGE]
-- Lungs are clear, and no pneumothorax or pleural effusion is detected. [R1]
+- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
+- The lungs are clear, which may suggest the absence of pleural effusion. [R1]
+- However, the absence of pleural effusion on a chest X-ray does not rule out its presence, as it may be small or not visible on a standard X-ray. [R1]
 Next Steps / Recommendations:
-- Further diagnostic tests and clinical evaluation may be needed to confirm the absence of pleural effusion or detect any underlying issues. [R1-IMAGE]
-- Clinical correlation recommended to assess the patient's symptoms and medical history. [Rx]</t>
+- Clinical correlation recommended to assess symptoms and medical history. [Rx]
+- Further imaging or diagnostic tests may be necessary to confirm or rule out pleural effusion. [Rx]</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1832,17 +1831,17 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.576</v>
+        <v>0.573</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8787884175777435</v>
+        <v>0.8766446709632874</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7273942087888717</v>
+        <v>0.7248223354816437</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -1906,8 +1905,8 @@
 References:
 [R1] - "DenseNet: Densely Connected Convolutional Networks" by Huang et al., 2017 [1]
 [R2] - "Clinical Applications of Deep Learning in Chest Radiography" by Rajpurkar et al., 2018 [2]
-[R3] - "Radiographic Findings in Acute Respiratory Distress Syndrome" by Goodman et al., 2018 [3]
-Note: The references provided are for general knowledge and may not be directly related to the specific clinical question. However, they are relevant to the topic of chest X-ray interpretation and deep learning algorithms.</t>
+[R3] - "Radiographic Findings in Community-Acquired Pneumonia" by Metlay et al., 1997 [3]
+Note: The references provided are for general knowledge and may not be directly related to the specific case. They are used to support the reasoning and provide context for the clinical decision-making process.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1924,13 +1923,13 @@
         <v>2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0.6000000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4500000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2012,13 +2011,13 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.656</v>
+        <v>0.774</v>
       </c>
       <c r="R18" t="n">
         <v>0.9382578015327453</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7971289007663727</v>
+        <v>0.8561289007663726</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2066,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8006788492202759</v>
+        <v>0.8251439332962036</v>
       </c>
       <c r="I19" t="n">
         <v>1</v>
@@ -2083,15 +2082,15 @@
 - No pneumothorax. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended. [Rx]
-- Insufficient evidence [Rx]</t>
+- Follow-up imaging if symptoms persist. [Rx]</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -2100,17 +2099,17 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.592</v>
+        <v>0.612</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9402036547660827</v>
+        <v>0.9475431799888611</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7661018273830413</v>
+        <v>0.7797715899944305</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2154,7 +2153,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5309703946113586</v>
+        <v>0.5294567346572876</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -2163,23 +2162,22 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No heart enlargement detected on chest X-ray. [R1], [R2]
+- Insufficient evidence to confirm or rule out heart enlargement. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
 - The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
-- Heart size is normal on the X-ray findings. [R1]
-- No signs of heart enlargement were observed on the chest X-ray. [R1]
+- However, a chest X-ray may not always provide a definitive diagnosis for heart enlargement. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to confirm the absence of heart enlargement. [Rx]
-- Further evaluation with echocardiography or other diagnostic tests may be necessary if symptoms persist. [Rx]</t>
+- Further evaluation and additional tests, such as an echocardiogram or cardiac MRI, may be necessary to assess the patient's heart function and determine if there is any underlying issue. [R2-IMAGE]
+- Clinical correlation with the patient's medical history and symptoms is recommended. [Rx]</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -2188,17 +2186,17 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.589</v>
+        <v>0.605</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8592911183834075</v>
+        <v>0.8588370203971862</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7241455591917038</v>
+        <v>0.7319185101985931</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2242,7 +2240,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6538283228874207</v>
+        <v>0.6593811511993408</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -2260,15 +2258,15 @@
 - The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
-- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
+- Further evaluation may be needed if symptoms persist. [Rx]</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -2277,17 +2275,17 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.594</v>
+        <v>0.619</v>
       </c>
       <c r="R21" t="n">
-        <v>0.8961484968662261</v>
+        <v>0.8978143453598022</v>
       </c>
       <c r="S21" t="n">
-        <v>0.745074248433113</v>
+        <v>0.7584071726799011</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2331,7 +2329,7 @@
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4736593961715698</v>
+        <v>0.4659932851791382</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -2346,18 +2344,18 @@
 - The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
 - A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE]
 - Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [R1-IMAGE]
-- The chest x-ray appears to be normal, which means that there are no visible abnormalities or signs of disease in the image. [R2-IMAGE]
+- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
-- Further evaluation and tests may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]</t>
+- Further evaluation may be needed to determine the cause of the patient's confusion. [Rx]</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -2366,17 +2364,17 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.584</v>
+        <v>0.593</v>
       </c>
       <c r="R22" t="n">
-        <v>0.8420978188514709</v>
+        <v>0.8397979855537414</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7130489094257355</v>
+        <v>0.7163989927768707</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2420,7 +2418,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8572167754173279</v>
+        <v>0.8626533150672913</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -2429,14 +2427,14 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No abnormal findings detected on the chest X-ray. [R1]
+- No significant abnormal findings detected on the chest X-ray. [R1]
 Supporting Evidence:
 - The lungs are clear, and without focal air space opacity. [R1]
 - The cardiomediastinal silhouette is normal in size and contour, and stable. [R1]
 - No pneumothorax or large pleural effusion is visible. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
-- Follow-up imaging if symptoms persist, but currently, the chest X-ray appears normal. [Rx]</t>
+- Clinical correlation recommended to assess the patient's symptoms and history. [Rx]
+- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2453,13 +2451,13 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.601</v>
+        <v>0.637</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9571650326251984</v>
+        <v>0.9587959945201874</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7790825163125992</v>
+        <v>0.7978979972600937</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2507,7 +2505,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6918138265609741</v>
+        <v>0.6126664876937866</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -2518,20 +2516,20 @@
           <t>Diagnosis / Impression:
 - No signs of cardiomegaly or abnormal cardiac silhouette are seen on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The heart size appears within normal limits on the chest X-ray. [R1]
-- The lungs are free of focal airspace disease, and no pleural effusion or pneumothorax is seen. [R1]
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
+- The heart size appears within normal limits on the chest X-ray. [R1-IMAGE]
+- The chest X-ray does not show any signs of cardiomegaly. [R2-IMAGE]
+- The lungs are free of focal airspace disease, which suggests that there are no other significant abnormalities that could be contributing to the patient's symptoms. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms of nausea and vomiting. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not appear necessary. [Rx]</t>
+- Clinical correlation with the patient's symptoms and medical history is recommended. [Rx]
+- Further evaluation with other diagnostic tests or imaging modalities may be necessary if the patient's symptoms persist or worsen. [Rx]</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2540,17 +2538,17 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.536</v>
+        <v>0.473</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9075441479682922</v>
+        <v>0.883799946308136</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7217720739841461</v>
+        <v>0.678399973154068</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2616,10 +2614,10 @@
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2628,17 +2626,17 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="R25" t="n">
         <v>0.8897846341133118</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7283923170566559</v>
+        <v>0.7198923170566559</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -2679,10 +2677,10 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="H26" t="n">
-        <v>0.644819974899292</v>
+        <v>0.659261167049408</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -2691,22 +2689,22 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Pleural effusion is visible on the chest X-ray, with moderate left pleural effusion and small right pleural effusion detected. [R1]
+- Pleural effusion is visible on the chest X-ray, with moderate left pleural effusion and small right pleural effusion identified. [R1]
 Supporting Evidence:
 - The lungs are hyperlucent and hyperinflated compatible with emphysema, which may be contributing to the pleural effusion. [R1]
-- There is moderate left pleural effusion and small right pleural effusion identified on the chest X-ray. [R1]
-- The absence of visible pleural effusion on [R2-IMAGE] and [R1-IMAGE] may be due to the limitations of the imaging modality or the presence of other conditions that mask the effusion. [R2-IMAGE, R1-IMAGE]
+- There is moderate left pleural effusion and small right pleural effusion, as indicated by the comparison of PA and lateral chest X-rays. [R1]
+- The presence of pleural effusion is further supported by the pathology detection results, with high confidence in the detection of pleural effusion in both R1 and R2. [R1, R2] [R1]
 Next Steps / Recommendations:
-- Clinical correlation with patient symptoms and medical history is recommended to determine the cause and significance of the pleural effusion. [Rx]
-- Further imaging or diagnostic testing may be necessary to confirm the presence and extent of the pleural effusion. [Rx]</t>
+- Clinical correlation with patient symptoms and medical history is recommended to determine the cause of the pleural effusion. [Rx]
+- Follow-up imaging may be necessary to monitor the progression of the pleural effusion and to assess the effectiveness of any treatment. [Rx]</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2715,17 +2713,17 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.586</v>
+        <v>0.599</v>
       </c>
       <c r="R26" t="n">
-        <v>0.8934459924697875</v>
+        <v>0.8309783501148224</v>
       </c>
       <c r="S26" t="n">
-        <v>0.7397229962348937</v>
+        <v>0.7149891750574111</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -2791,10 +2789,10 @@
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2803,17 +2801,17 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.541</v>
       </c>
       <c r="R27" t="n">
         <v>0.9039523124694824</v>
       </c>
       <c r="S27" t="n">
-        <v>0.7334761562347412</v>
+        <v>0.7224761562347413</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -2879,10 +2877,10 @@
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2891,17 +2889,17 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.572</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="R28" t="n">
         <v>0.9113259196281432</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7416629598140716</v>
+        <v>0.7371629598140716</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -2945,7 +2943,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7265353798866272</v>
+        <v>0.7952942848205566</v>
       </c>
       <c r="I29" t="n">
         <v>1</v>
@@ -2954,22 +2952,22 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Cardiomegaly and bilateral pleural effusions are present. [R1-IMAGE]
+- Bilateral patchy pulmonary opacities and pleural effusions are noted on chest X-ray. [R1]
 Supporting Evidence:
-- Cardiomegaly, an enlargement of the heart, is noted on the chest X-ray. [R1-IMAGE]
-- Bilateral pleural effusions, abnormal accumulations of fluid in the pleural space surrounding both lungs, are observed. [R1-IMAGE]
-- Pulmonary vascular congestion is also present, suggesting an underlying issue affecting the patient's lungs and heart. [R2-IMAGE]
+- Bilateral patchy pulmonary opacities are observed, indicating areas of increased density or cloudiness in the lung tissue. [R1]
+- Pleural effusions are detected on the chest X-ray, suggesting fluid accumulation in both sides of the lungs. [R1]
+- Pulmonary vascular congestion is also noted, indicating possible fluid overload or heart failure. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with the patient's symptoms and history is recommended. [Rx]
-- Follow-up imaging if symptoms persist, as the current findings suggest a potential underlying issue. [Rx]</t>
+- Clinical correlation with patient symptoms and medical history is recommended to determine the cause of the findings. [Rx]
+- Further evaluation and consultation with a healthcare professional are necessary to develop an appropriate treatment plan. [Rx]</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -2978,17 +2976,17 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.533</v>
       </c>
       <c r="R29" t="n">
-        <v>0.9179606139659882</v>
+        <v>0.9385882854461669</v>
       </c>
       <c r="S29" t="n">
-        <v>0.7389803069829941</v>
+        <v>0.7357941427230834</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3032,7 +3030,7 @@
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.567784309387207</v>
+        <v>0.4797349870204926</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -3041,22 +3039,23 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Insufficient evidence [R1], [R2] to indicate heart enlargement.
+- Insufficient evidence [R1], [R2] to confirm or rule out heart enlargement.
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
-- No significant pathologies detected above threshold, including heart enlargement. [R2]
+- The chest X-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
+- The comparison X-ray does not show any signs of heart enlargement. [R2]
+- The second chest X-ray also does not show any signs of heart enlargement. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate symptoms of hypoxia. [Rx]
-- Further diagnostic testing, such as echocardiogram or electrocardiogram, may be necessary to assess heart function. [Rx]</t>
+- Clinical correlation recommended to further evaluate symptoms and medical history. [Rx]
+- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -3065,17 +3064,17 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.546</v>
+        <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>0.8703352928161621</v>
+        <v>0.8439204961061477</v>
       </c>
       <c r="S30" t="n">
-        <v>0.7081676464080811</v>
+        <v>0.6719602480530739</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3119,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7765252590179443</v>
+        <v>0.6954623460769653</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -3131,19 +3130,20 @@
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
 Supporting Evidence:
 - The chest x-ray shows lungs that are clear without focal consolidation, effusion, or pneumothorax. [R1]
-- The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
-- Normal heart size and negative for pneumoperitoneum are also noted on the chest x-ray. [R1]
+- The chest x-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
+- The lung fields are clear and there are no signs of infection, fluid accumulation, or other issues in the image. [R1-IMAGE]
+- The chest x-ray shows clear lung fields. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
-- Further evaluation may be needed to rule out all possible conditions or issues. [Rx]</t>
+- Further evaluation may be needed to assess the patient's overall health and identify any underlying conditions that may not be visible on the x-ray. [R1-IMAGE]</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -3152,17 +3152,17 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.582</v>
+        <v>0.588</v>
       </c>
       <c r="R31" t="n">
-        <v>0.9329575777053832</v>
+        <v>0.9086387038230895</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7574787888526916</v>
+        <v>0.7483193519115448</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3206,7 +3206,7 @@
         <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5923786759376526</v>
+        <v>0.5901783108711243</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -3219,19 +3219,19 @@
 Supporting Evidence:
 - The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
 - A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE]
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues. [R1-IMAGE]
-- The chest x-ray appears to be normal, which means that there are no visible abnormalities or signs of disease in the image. [R2-IMAGE]
+- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [R1-IMAGE]
+- The chest x-ray appears to be normal, with no visible signs of abnormalities or issues in the lungs, heart, or surrounding structures. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
-- Further evaluation may be needed to rule out all possible conditions or diseases. [Rx]</t>
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
+- Further evaluation and tests may be needed depending on the patient's symptoms and clinical history. [R2-IMAGE]</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -3240,17 +3240,17 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.537</v>
       </c>
       <c r="R32" t="n">
-        <v>0.8777136027812957</v>
+        <v>0.8770534932613372</v>
       </c>
       <c r="S32" t="n">
-        <v>0.7198568013906479</v>
+        <v>0.7070267466306686</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3294,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8103905916213989</v>
+        <v>0.6743566989898682</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -3305,13 +3305,13 @@
           <t>Diagnosis / Impression:
 - No acute abnormality detected. [R1]
 Supporting Evidence:
-- The heart is normal in size. [R1]
-- The mediastinum is unremarkable. [R1]
-- Mild blunting of right costophrenic angle. [R1]
+- The chest X-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
+- Mild blunting of right costophrenic angle is noted, but its clinical significance is unclear. [R1]
 - The lungs are otherwise grossly clear. [R1]
+- The chest X-ray is normal, with no apparent signs of lung disease or other issues. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
+- Clinical correlation recommended to determine the significance of mild blunting of right costophrenic angle. [Rx]
+- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -3328,13 +3328,13 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.611</v>
+        <v>0.662</v>
       </c>
       <c r="R33" t="n">
-        <v>0.9431171774864197</v>
+        <v>0.9023070096969604</v>
       </c>
       <c r="S33" t="n">
-        <v>0.7770585887432098</v>
+        <v>0.7821535048484802</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6666450500488281</v>
+        <v>0.650692880153656</v>
       </c>
       <c r="I34" t="n">
         <v>1</v>
@@ -3393,9 +3393,10 @@
           <t>Diagnosis / Impression:
 - No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- Cardiac and mediastinal contours are within normal limits on chest X-ray. [R1]
-- The lungs are clear on chest X-ray. [R1]
-- Bony structures are intact on chest X-ray. [R1]
+- Cardiac and mediastinal contours are within normal limits on the chest X-ray. [R1]
+- The lungs are clear on the chest X-ray. [R1]
+- Bony structures are intact on the chest X-ray. [R1]
+- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's cardiac status. [Rx]
 - Follow-up imaging if symptoms persist or new cardiac symptoms develop. [Rx]</t>
@@ -3403,10 +3404,10 @@
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -3415,17 +3416,17 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.599</v>
+        <v>0.632</v>
       </c>
       <c r="R34" t="n">
-        <v>0.8999935150146484</v>
+        <v>0.8952078640460968</v>
       </c>
       <c r="S34" t="n">
-        <v>0.7494967575073241</v>
+        <v>0.7636039320230483</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -3502,13 +3503,13 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.601</v>
+        <v>0.636</v>
       </c>
       <c r="R35" t="n">
         <v>0.8853358685970306</v>
       </c>
       <c r="S35" t="n">
-        <v>0.7431679342985154</v>
+        <v>0.7606679342985153</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3556,7 +3557,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.579179048538208</v>
+        <v>0.6230317354202271</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -3565,15 +3566,14 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No pleural effusion visible on the chest X-ray. [R1], [R2]
+- No pleural effusion visible on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
 - The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible signs of pleural effusion. [R2-IMAGE]
-- The findings of the chest X-ray are consistent with no pleural effusion. [R1]
-- The absence of pleural effusion is confirmed by the radiographic examination. [R2]
+- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
+- The absence of focal airspace opacity or pleural effusion is noted on the chest X-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall condition. [Rx]
-- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
+- Clinical correlation recommended to rule out other causes of respiratory symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but pleural effusion is not visible on the current chest X-ray. [Rx]</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -3590,13 +3590,13 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.605</v>
+        <v>0.646</v>
       </c>
       <c r="R36" t="n">
-        <v>0.8737537145614623</v>
+        <v>0.8869095206260681</v>
       </c>
       <c r="S36" t="n">
-        <v>0.7393768572807311</v>
+        <v>0.7664547603130341</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7740131020545959</v>
+        <v>0.7451775074005127</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -3655,12 +3655,13 @@
           <t>Diagnosis / Impression:
 - No lung consolidation or opacities detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The lungs are clear bilaterally, with no evidence of focal consolidation. [R1]
-- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE], [R2-IMAGE]
-- No evidence of pneumothorax or pleural effusion is seen on the chest radiograph. [R1]
+- The chest x-ray does not show any lung consolidation or opacities. [R1-IMAGE]
+- The chest X-ray does not show any lung consolidation or opacities. [R2-IMAGE]
+- The lungs are clear bilaterally, with no evidence of focal consolidation, pneumothorax, or pleural effusion. [R1]
+- The lungs are clear bilaterally, with no evidence of focal consolidation, pneumothorax, or pleural effusion. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, no immediate need for further imaging. [Rx]</t>
+- Follow-up imaging if symptoms persist, but currently, no indication for further imaging. [Rx]</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -3677,13 +3678,13 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.616</v>
+        <v>0.672</v>
       </c>
       <c r="R37" t="n">
-        <v>0.9322039306163787</v>
+        <v>0.9235532522201537</v>
       </c>
       <c r="S37" t="n">
-        <v>0.7741019653081893</v>
+        <v>0.7977766261100769</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -3752,10 +3753,10 @@
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -3764,17 +3765,17 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.536</v>
+        <v>0.475</v>
       </c>
       <c r="R38" t="n">
         <v>0.8574162006378173</v>
       </c>
       <c r="S38" t="n">
-        <v>0.6967081003189086</v>
+        <v>0.6662081003189086</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -3815,10 +3816,10 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8801039457321167</v>
+        <v>0.766639232635498</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -3827,22 +3828,22 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No significant pathologies detected above threshold. [R1]
+- The chest X-ray shows clear lungs with no pneumothorax or pleural effusion, but further evaluation is needed due to conflicting findings. [R1]
 Supporting Evidence:
 - Lungs are clear with no pneumothorax or pleural effusion. [R1]
 - The heart and mediastinum are within normal limits. [R1]
-- Bony structures are intact. [R1]
+- However, there are conflicting findings of pleural effusions and pneumothorax on other X-rays. [R1-IMAGE, R2-IMAGE] [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, as the current findings do not explain the patient's shortness of breath. [Rx]</t>
+- Clinical correlation and further evaluation are needed to determine the cause and significance of the conflicting findings. [Rx]
+- Follow-up imaging if symptoms persist, taking into account the conflicting findings from previous X-rays. [Rx]</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -3851,17 +3852,17 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.587</v>
+        <v>0.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0.9640311837196349</v>
+        <v>0.8631917697906494</v>
       </c>
       <c r="S39" t="n">
-        <v>0.7755155918598174</v>
+        <v>0.7315958848953247</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -3927,10 +3928,10 @@
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3939,17 +3940,17 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.53</v>
+        <v>0.458</v>
       </c>
       <c r="R40" t="n">
         <v>0.8754251420497894</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7027125710248947</v>
+        <v>0.6667125710248947</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">

--- a/mmrag_evaluation_results.xlsx
+++ b/mmrag_evaluation_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:X40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,80 +466,85 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>GroundednessSource</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>ClinicalCorrectness</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Completeness</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>OfflineClinicalCorrectness</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>generated_answer</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>expected_answer</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>total_iterations</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>retrieval_attempts</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>reasoning_attempts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>refinement_count</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>evidence_quality</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>response_quality</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>overall_quality</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>evidence_decision</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>response_decision</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>evidence_count</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>modality</t>
         </is>
@@ -569,16 +574,21 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.7120616436004639</v>
       </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The chest X-ray appears normal. [R1-IMAGE]
@@ -591,12 +601,9 @@
 - Further evaluation may be needed to rule out all possible conditions or diseases. [Rx]</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -605,28 +612,31 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>0.633</v>
       </c>
-      <c r="R2" t="n">
-        <v>0.9136184930801391</v>
-      </c>
       <c r="S2" t="n">
-        <v>0.7733092465400695</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7636184930801392</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.6983092465400695</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V2" t="n">
-        <v>2</v>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W2" t="n">
+        <v>2</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -658,32 +668,34 @@
       <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.5893280506134033</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+        <v>0.5643822550773621</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Borderline cardiomegaly and enlarged pulmonary arteries detected. [R1]
+- Borderline cardiomegaly and enlarged pulmonary arteries are noted on the chest X-ray. [R1]
 Supporting Evidence:
-- The chest X-ray shows borderline cardiomegaly, which is an indication of possible heart enlargement. [R1]
-- Enlarged pulmonary arteries are visible on the X-ray, which may be related to various conditions such as pulmonary hypertension or heart failure. [R1]
-- The lungs appear clear, which suggests that there is no apparent lung disease. [R1]
+- The chest X-ray shows borderline cardiomegaly, which may indicate mild cardiac enlargement. [R1]
+- Enlarged pulmonary arteries are visible on the X-ray, which could be related to various conditions such as pulmonary hypertension or chronic lung disease. [R1]
+- The lungs appear clear on the X-ray, which suggests that there is no obvious lung disease or infection present. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with the patient's history and symptoms is recommended to determine the significance of these findings. [Rx]
-- Further evaluation with echocardiography or other imaging modalities may be necessary to assess the heart function and pulmonary artery pressures. [Rx]</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation with the patient's medical history and symptoms is recommended to further evaluate the significance of the borderline cardiomegaly and enlarged pulmonary arteries. [Rx]
+- Further diagnostic testing, such as an echocardiogram or pulmonary function tests, may be necessary to determine the underlying cause of the abnormal findings on the chest X-ray. [Rx]</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -692,28 +704,31 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>0.576</v>
       </c>
-      <c r="R3" t="n">
-        <v>0.8767984151840209</v>
-      </c>
       <c r="S3" t="n">
-        <v>0.7263992075920105</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8693146765232086</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.7226573382616043</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V3" t="n">
-        <v>2</v>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -743,22 +758,27 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.5643539428710938</v>
       </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
 - The chest x-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
-- The chest x-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
+- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
 - The heart appears to be within normal size and shape in the image. [R1-IMAGE]
 - The absence of cardiomegaly or abnormal cardiac silhouette on chest X-ray is consistent with a normal cardiac silhouette. [R2]
 Next Steps / Recommendations:
@@ -766,12 +786,9 @@
 - Follow-up imaging if symptoms persist or worsen. [Rx]</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>2</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -780,28 +797,31 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
+        <v>2</v>
+      </c>
+      <c r="R4" t="n">
         <v>0.5639999999999999</v>
       </c>
-      <c r="R4" t="n">
-        <v>0.8693061828613281</v>
-      </c>
       <c r="S4" t="n">
-        <v>0.716653091430664</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.5581061828613281</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.561053091430664</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>2</v>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>2</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -831,16 +851,21 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.7382009029388428</v>
       </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pulmonary congestion or edema detected. [R1-IMAGE], [R2-IMAGE]
@@ -853,12 +878,9 @@
 - Further evaluation of the left lung apex for a cavitary lesion is recommended. [Rx]</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -867,28 +889,31 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
         <v>0.531</v>
       </c>
-      <c r="R5" t="n">
-        <v>0.9214602708816528</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.7262301354408265</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8546602708816529</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.6928301354408264</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V5" t="n">
-        <v>2</v>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -918,35 +943,37 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6938239932060242</v>
+        <v>0.778</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+        <v>0.6857281923294067</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No pleural effusion visible on the chest X-ray. [R1], [R2]
 Supporting Evidence:
 - The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
+- The chest X-ray does not show any visible pleural effusion. [R2-IMAGE]
 - The cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion. [R1]
-- There is no pneumothorax or pleural effusion, as stated in the radiologist's report. [R1]
+- There is no pneumothorax or pleural effusion, as stated in the radiology report. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely that pleural effusion will be detected. [Rx]</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>2</v>
-      </c>
+- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show pleural effusion. [Rx]</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -955,28 +982,31 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.644</v>
       </c>
-      <c r="R6" t="n">
-        <v>0.9081471979618072</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.7760735989809036</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.816918457698822</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.7304592288494109</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V6" t="n">
-        <v>2</v>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1006,16 +1036,21 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.6997577548027039</v>
       </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No lung consolidation or opacities detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
@@ -1029,12 +1064,9 @@
 - Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show lung consolidation or opacities. [Rx]</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1043,28 +1075,31 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
         <v>0.599</v>
       </c>
-      <c r="R7" t="n">
-        <v>0.9099273264408111</v>
-      </c>
       <c r="S7" t="n">
-        <v>0.7544636632204056</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8099273264408112</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.7044636632204055</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>2</v>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W7" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1094,16 +1129,21 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.4138781428337097</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pneumothorax detected. [R1-IMAGE], [R2-IMAGE]
@@ -1116,12 +1156,9 @@
 - Follow-up imaging if symptoms persist. [Rx]</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>2</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1130,28 +1167,31 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
+        <v>2</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.468</v>
       </c>
-      <c r="R8" t="n">
-        <v>0.8241634428501129</v>
-      </c>
       <c r="S8" t="n">
-        <v>0.6460817214250565</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.6909634428501129</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.5794817214250565</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V8" t="n">
-        <v>2</v>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1183,32 +1223,34 @@
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="n">
-        <v>0.8091067671775818</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+        <v>0.8089767098426819</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No significant pathologies detected above threshold. [R1]
 Supporting Evidence:
 - The heart, pulmonary structures, and mediastinum are within normal limits. [R1]
-- There is no pleural effusion or pneumothorax. [R1]
-- The chest X-ray shows several key findings, including a right-sided pneumothorax, a left-sided pleural effusion, and an elevated hemidiaphragm. [R2-IMAGE]
+- No pleural effusion or pneumothorax is present. [R1]
+- No focal air space opacity to suggest a pneumonia. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms and history of mitral valve prolapse. [Rx]
-- Follow-up imaging if symptoms persist, particularly if the patient's condition worsens or new symptoms develop. [Rx]</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="n">
-        <v>2</v>
-      </c>
+- Follow-up imaging if symptoms persist, but based on the current evidence, no immediate indication for further imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1217,28 +1259,31 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R9" t="n">
         <v>0.5649999999999999</v>
       </c>
-      <c r="R9" t="n">
-        <v>0.9427320301532744</v>
-      </c>
       <c r="S9" t="n">
-        <v>0.7538660150766372</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9426930129528045</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.7538465064764022</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1270,14 +1315,19 @@
       <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>0.60411536693573</v>
       </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of heart enlargement detected on chest X-ray. [R1], [R2]
@@ -1289,12 +1339,9 @@
 - Follow-up imaging if symptoms persist, but no immediate indication for further imaging based on current chest X-ray findings. [Rx]</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -1303,28 +1350,31 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
+        <v>1</v>
+      </c>
+      <c r="R10" t="n">
         <v>0.594</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>0.8812346100807189</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>0.7376173050403594</v>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V10" t="n">
-        <v>2</v>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W10" t="n">
+        <v>2</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1356,33 +1406,34 @@
       <c r="G11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.6518317461013794</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+        <v>0.6806971430778503</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
-- The lung fields appear to be clear on the chest X-ray. [R2-IMAGE]
 Supporting Evidence:
 - The lungs are normally inflated without evidence of focal airspace disease, pleural effusion, or pneumothorax. [R1]
-- The lung fields appear to be clear on the chest x-ray, with no obvious signs of abnormalities or opacities in the lung fields. [R2-IMAGE]
-- A clear chest x-ray is generally a positive finding, indicating healthy lung function. [R1-IMAGE]
+- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
+- The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out all possible conditions or issues, as a clear chest x-ray does not necessarily rule out all possible lung conditions. [Rx]
+- Clinical correlation recommended to assess the patient's overall health and identify any potential underlying concerns. [Rx]
 - Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>2</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1391,28 +1442,31 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.622</v>
       </c>
-      <c r="R11" t="n">
-        <v>0.8955495238304138</v>
-      </c>
       <c r="S11" t="n">
-        <v>0.7587747619152069</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9042091429233551</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.7631045714616775</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W11" t="n">
+        <v>2</v>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1442,16 +1496,21 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>0.7782972455024719</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The chest X-ray appears normal. [R1]
@@ -1465,12 +1524,9 @@
 - Further evaluation may be needed if symptoms persist. [Rx]</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
+      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -1479,28 +1535,31 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
         <v>0.617</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.9334891736507416</v>
-      </c>
       <c r="S12" t="n">
-        <v>0.7752445868253708</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8134891736507415</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.7152445868253707</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V12" t="n">
-        <v>2</v>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W12" t="n">
+        <v>2</v>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1530,19 +1589,24 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.8339194059371948</v>
+        <v>0.75</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
+        <v>0.820636510848999</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No abnormal findings detected on the chest X-ray. [R1]
+- No significant abnormal findings detected on the chest X-ray. [R1]
 Supporting Evidence:
 - Lungs are clear bilaterally. [R1]
 - Cardiac and mediastinal silhouettes are normal. [R1]
@@ -1551,15 +1615,12 @@
 - No acute bony abnormality. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to rule out conditions not visible on chest X-ray. [Rx]
-- Follow-up imaging if symptoms persist or clinical history suggests underlying condition. [Rx]</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>2</v>
-      </c>
+- Follow-up imaging if symptoms persist or clinical history suggests underlying pathology. [Rx]</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
         <v>1</v>
@@ -1568,28 +1629,31 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.659</v>
       </c>
-      <c r="R13" t="n">
-        <v>0.9501758217811584</v>
-      </c>
       <c r="S13" t="n">
-        <v>0.8045879108905792</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8461909532546998</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.7525954766273499</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1619,35 +1683,37 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.8963230848312378</v>
+        <v>0.429</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
+        <v>0.8997962474822998</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The cardiac silhouette is borderline enlarged on the chest radiograph from XXXX, XXXX, but this is not consistent with the image findings. [R1]
-- The mediastinal contours are within normal limits on the chest radiograph from XXXX, XXXX. [R1]
-- The chest x-ray does not show any large pleural effusion or pneumothorax. [R1]
-- The heart appears to be within normal size and shape in the image. [R1-IMAGE], [R2-IMAGE]
+- The cardiac silhouette is borderline enlarged on the chest radiograph. [R1]
+- Mediastinal contours are within normal limits on the chest radiograph. [R1]
+- The chest X-ray does not show any large pleural effusion or pneumothorax. [R1]
+- The heart appears to be within normal size and shape on the image. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the borderline enlarged cardiac silhouette. [Rx]
-- Follow-up imaging if symptoms persist, but the current chest X-ray does not show any signs of cardiomegaly or abnormal cardiac silhouette. [Rx]</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
+- Follow-up imaging if symptoms persist, considering the borderline enlarged cardiac silhouette. [Rx]</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
@@ -1656,28 +1722,31 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
+        <v>1</v>
+      </c>
+      <c r="R14" t="n">
         <v>0.726</v>
       </c>
-      <c r="R14" t="n">
-        <v>0.9688969254493713</v>
-      </c>
       <c r="S14" t="n">
-        <v>0.8474484627246857</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.74153887424469</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.733769437122345</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1707,35 +1776,36 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.8714293837547302</v>
+        <v>0.714</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
+        <v>0.7411871552467346</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pulmonary congestion or edema detected on the chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest x-ray shows heart size within normal limits, stable mediastinal and hilar contours. [R1]
-- Mild hyperinflation appears similar to prior, with no focal alveolar consolidation or definite pleural effusion seen. [R1]
-- Scattered chronic appearing irregular interstitial markings are present, but no typical findings of pulmonary edema are observed. [R1]
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE], [R2-IMAGE]
+- The chest x-ray shows no focal alveolar consolidation, no definite pleural effusion seen. [R1]
+- No typical findings of pulmonary edema are present on the chest x-ray. [R1]
+- The chest x-ray does not show any signs of pulmonary congestion or edema. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not appear necessary. [Rx]</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to determine the overall health status of the patient. [Rx]
+- Further evaluation by a healthcare professional is necessary to assess the patient's condition. [Rx]</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
         <v>1</v>
@@ -1744,28 +1814,31 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.67</v>
       </c>
-      <c r="R15" t="n">
-        <v>0.961428815126419</v>
-      </c>
       <c r="S15" t="n">
-        <v>0.8157144075632095</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8079561465740204</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.7389780732870102</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V15" t="n">
-        <v>2</v>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1795,34 +1868,37 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.5888155698776245</v>
+        <v>0.8</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
+        <v>0.7225977778434753</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Insufficient evidence to determine the presence of pleural effusion on the chest X-ray. [R2-IMAGE]
+- No pleural effusion visible on the chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
-- The lungs are clear, which may suggest the absence of pleural effusion. [R1]
-- However, the absence of pleural effusion on a chest X-ray does not rule out its presence, as it may be small or not visible on a standard X-ray. [R1]
+- The chest X-ray does not show any visible pleural effusion. [R1-IMAGE]
+- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
+- Cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion. [R1]
+- Lungs are clear, further supporting the absence of pleural effusion. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess symptoms and medical history. [Rx]
-- Further imaging or diagnostic tests may be necessary to confirm or rule out pleural effusion. [Rx]</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess the cause of dyspnea. [Rx]
+- Follow-up imaging if symptoms persist, but pleural effusion is unlikely given the current findings. [Rx]</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
         <v>1</v>
@@ -1831,28 +1907,31 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.573</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.8766446709632874</v>
-      </c>
       <c r="S16" t="n">
-        <v>0.7248223354816437</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8367793333530427</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.7048896666765213</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V16" t="n">
-        <v>2</v>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1869,86 +1948,34 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-No pathologies detected above threshold on the chest X-ray. [R1]
-Supporting Evidence:
-- The DenseNet CNN algorithm used for pathology detection did not identify any abnormalities above the set threshold. [R1]
-- The absence of pathologies detected by the algorithm suggests that the chest X-ray is likely normal or shows no significant abnormalities. [R2]
-- However, it is essential to note that the absence of findings on a chest X-ray does not rule out the presence of lung consolidation or opacities, especially if they are mild or not severe enough to be detected by the algorithm. [R3]
-Next Steps / Recommendations:
-- Clinical correlation with the patient's symptoms and medical history is recommended to determine the next course of action. [Rx]
-- Further imaging or diagnostic testing may be necessary if symptoms persist or worsen, despite a normal chest X-ray. [Rx]
-References:
-[R1] - "DenseNet: Densely Connected Convolutional Networks" by Huang et al., 2017 [1]
-[R2] - "Clinical Applications of Deep Learning in Chest Radiography" by Rajpurkar et al., 2018 [2]
-[R3] - "Radiographic Findings in Community-Acquired Pneumonia" by Metlay et al., 1997 [3]
-Note: The references provided are for general knowledge and may not be directly related to the specific case. They are used to support the reasoning and provide context for the clinical decision-making process.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="n">
-        <v>3</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.6000000000000001</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>RETRY</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>XRAY</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>unsupported operand type(s) for *: 'NoneType' and 'float'</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1976,14 +2003,19 @@
       <c r="G18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>0.7941926717758179</v>
       </c>
-      <c r="I18" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pneumothorax detected on the chest X-ray. [R1], [R2]
@@ -1997,12 +2029,9 @@
 - Follow-up imaging if symptoms persist, but no immediate indication for further imaging at this time. [Rx]</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>2</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -2011,28 +2040,31 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
+        <v>1</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.774</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>0.9382578015327453</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>0.8561289007663726</v>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V18" t="n">
-        <v>2</v>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W18" t="n">
+        <v>2</v>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2062,35 +2094,37 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.8251439332962036</v>
+        <v>0.267</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
+        <v>0.6915655136108398</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No significant pathologies detected above threshold. [R1], [R2]
+- The chest X-ray shows several key findings, including cardiomegaly, bilateral pleural effusions, right-sided pneumothorax, left-sided pneumothorax, bilateral rib fractures, right-sided hemopneumothorax, and left-sided pneumomediastinum. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- Heart size within normal limits. [R1]
-- No focal alveolar consolidation, no definite pleural effusion seen. [R1]
-- No typical findings of pulmonary edema. [R1]
-- No pneumothorax. [R1]
+- Cardiomegaly, which is an enlargement of the heart, is visible on the chest X-ray. [R1-IMAGE]
+- Bilateral pleural effusions, which are abnormal accumulations of fluid in the pleural space surrounding both lungs, are present. [R1-IMAGE]
+- Right-sided pneumothorax, which is a collapsed lung on the right side, is visible on the chest X-ray. [R1-IMAGE]
+- Left-sided pneumothorax, which is a collection of air or gas in the pleural space causing the lung to collapse, is present. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended. [Rx]
-- Follow-up imaging if symptoms persist. [Rx]</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation with the patient's symptoms and medical history is recommended to determine the cause of the observed abnormalities. [Rx]
+- Follow-up imaging may be necessary if the patient's symptoms persist or worsen. [Rx]</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" t="n">
         <v>1</v>
@@ -2099,28 +2133,31 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
+        <v>2</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.612</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.9475431799888611</v>
-      </c>
       <c r="S19" t="n">
-        <v>0.7797715899944305</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.614269654083252</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.6131348270416259</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V19" t="n">
-        <v>2</v>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2150,34 +2187,37 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.5294567346572876</v>
+        <v>0.75</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
+        <v>0.5309703946113586</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Insufficient evidence to confirm or rule out heart enlargement. [R1-IMAGE], [R2-IMAGE]
+- No heart enlargement detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
 - The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
-- However, a chest X-ray may not always provide a definitive diagnosis for heart enlargement. [R2-IMAGE]
+- Heart size is normal on the X-ray findings. [R1]
+- No signs of heart enlargement were observed on the chest X-ray. [R1]
 Next Steps / Recommendations:
-- Further evaluation and additional tests, such as an echocardiogram or cardiac MRI, may be necessary to assess the patient's heart function and determine if there is any underlying issue. [R2-IMAGE]
-- Clinical correlation with the patient's medical history and symptoms is recommended. [Rx]</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to confirm the absence of heart enlargement. [Rx]
+- Further evaluation with echocardiography or other diagnostic tests may be necessary if symptoms persist. [Rx]</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
@@ -2186,28 +2226,31 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
+        <v>1</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.605</v>
       </c>
-      <c r="R20" t="n">
-        <v>0.8588370203971862</v>
-      </c>
       <c r="S20" t="n">
-        <v>0.7319185101985931</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7592911183834077</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.6821455591917038</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V20" t="n">
-        <v>2</v>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W20" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2239,14 +2282,19 @@
       <c r="G21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.6593811511993408</v>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+        <v>0.6488034725189209</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
@@ -2257,16 +2305,13 @@
 - The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
 - The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
-- Further evaluation may be needed if symptoms persist. [Rx]</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to determine the patient's overall health status and identify any potential underlying concerns. [Rx]
+- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
@@ -2275,28 +2320,31 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.619</v>
       </c>
-      <c r="R21" t="n">
-        <v>0.8978143453598022</v>
-      </c>
       <c r="S21" t="n">
-        <v>0.7584071726799011</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8946410417556763</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.7568205208778381</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V21" t="n">
-        <v>2</v>
-      </c>
-      <c r="W21" t="inlineStr">
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W21" t="n">
+        <v>2</v>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2326,36 +2374,36 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.4659932851791382</v>
+        <v>0.667</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
+        <v>0.493852436542511</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The chest X-ray appears normal. [R1-IMAGE]
-- The chest X-ray appears normal. [R2-IMAGE]
 Supporting Evidence:
 - The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
 - A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE]
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [R1-IMAGE]
-- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R2-IMAGE]
+- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
-- Further evaluation may be needed to determine the cause of the patient's confusion. [Rx]</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues. [Rx]
+- Further evaluation and tests may be needed depending on the patient's symptoms and clinical history. [Rx]</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
         <v>1</v>
@@ -2364,28 +2412,31 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
+        <v>1</v>
+      </c>
+      <c r="R22" t="n">
         <v>0.593</v>
       </c>
-      <c r="R22" t="n">
-        <v>0.8397979855537414</v>
-      </c>
       <c r="S22" t="n">
-        <v>0.7163989927768707</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7149557309627532</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.6539778654813766</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V22" t="n">
-        <v>2</v>
-      </c>
-      <c r="W22" t="inlineStr">
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W22" t="n">
+        <v>2</v>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2415,34 +2466,36 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.8626533150672913</v>
+        <v>0.667</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
+        <v>0.76126629114151</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No significant abnormal findings detected on the chest X-ray. [R1]
+- No abnormal findings detected on the chest X-ray. [R1]
 Supporting Evidence:
 - The lungs are clear, and without focal air space opacity. [R1]
 - The cardiomediastinal silhouette is normal in size and contour, and stable. [R1]
-- No pneumothorax or large pleural effusion is visible. [R1]
+- The chest X-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's symptoms and history. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
+- Follow-up imaging if symptoms persist, but currently, there is no indication for further imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
         <v>1</v>
@@ -2451,28 +2504,31 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
         <v>0.637</v>
       </c>
-      <c r="R23" t="n">
-        <v>0.9587959945201874</v>
-      </c>
       <c r="S23" t="n">
-        <v>0.7978979972600937</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7951798873424529</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.7160899436712265</v>
       </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V23" t="n">
-        <v>2</v>
-      </c>
-      <c r="W23" t="inlineStr">
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W23" t="n">
+        <v>2</v>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2502,34 +2558,38 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.6126664876937866</v>
+        <v>0.75</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
+        <v>0.632602334022522</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No signs of cardiomegaly or abnormal cardiac silhouette are seen on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
+- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
+- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
 Supporting Evidence:
-- The heart size appears within normal limits on the chest X-ray. [R1-IMAGE]
-- The chest X-ray does not show any signs of cardiomegaly. [R2-IMAGE]
-- The lungs are free of focal airspace disease, which suggests that there are no other significant abnormalities that could be contributing to the patient's symptoms. [R1]
+- The heart size appears within normal limits on the chest x-ray. [R1]
+- The lungs are free of focal airspace disease, indicating no acute abnormality. [R1]
+- The chest x-ray does not show any signs of pleural effusion or pneumothorax. [R1]
+- The pulmonary vascularity appears within normal limits on the chest x-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with the patient's symptoms and medical history is recommended. [Rx]
-- Further evaluation with other diagnostic tests or imaging modalities may be necessary if the patient's symptoms persist or worsen. [Rx]</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but based on the current chest X-ray, no immediate indication for further imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -2538,28 +2598,31 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
+        <v>1</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.473</v>
       </c>
-      <c r="R24" t="n">
-        <v>0.883799946308136</v>
-      </c>
       <c r="S24" t="n">
-        <v>0.678399973154068</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7897807002067567</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.6313903501033784</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V24" t="n">
-        <v>2</v>
-      </c>
-      <c r="W24" t="inlineStr">
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W24" t="n">
+        <v>2</v>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2589,35 +2652,37 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.6326154470443726</v>
+        <v>0.714</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+        <v>0.7096673250198364</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
 - The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
-- The pulmonary vascularity is unremarkable, which is consistent with the absence of pulmonary congestion. [R1]
-- Lungs are expanded and clear of airspace disease, further supporting the absence of pulmonary edema. [R1]
-- The chest x-ray findings are negative for pneumothorax or pleural effusion, which can sometimes be associated with pulmonary congestion or edema. [R1]
+- The lungs appear to be clear and free of any significant fluid accumulation or other abnormalities in the image. [R2-IMAGE]
+- Cardiomediastinal silhouette is within normal limits of size and appearance, indicating no signs of pulmonary congestion. [R1]
+- Pulmonary vascularity is unremarkable, which is consistent with the absence of pulmonary congestion or edema. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms of dyspnea. [Rx]
 - Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it is unlikely to show signs of pulmonary congestion or edema. [Rx]</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="n">
-        <v>2</v>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>1</v>
@@ -2626,28 +2691,31 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
+        <v>1</v>
+      </c>
+      <c r="R25" t="n">
         <v>0.55</v>
       </c>
-      <c r="R25" t="n">
-        <v>0.8897846341133118</v>
-      </c>
       <c r="S25" t="n">
-        <v>0.7198923170566559</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7985001975059509</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.6742500987529755</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V25" t="n">
-        <v>2</v>
-      </c>
-      <c r="W25" t="inlineStr">
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W25" t="n">
+        <v>2</v>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2677,34 +2745,36 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.659261167049408</v>
+        <v>0.462</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
+        <v>0.6392327547073364</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Pleural effusion is visible on the chest X-ray, with moderate left pleural effusion and small right pleural effusion identified. [R1]
+- Pleural effusion is visible on the chest X-ray. [R1]
 Supporting Evidence:
-- The lungs are hyperlucent and hyperinflated compatible with emphysema, which may be contributing to the pleural effusion. [R1]
-- There is moderate left pleural effusion and small right pleural effusion, as indicated by the comparison of PA and lateral chest X-rays. [R1]
-- The presence of pleural effusion is further supported by the pathology detection results, with high confidence in the detection of pleural effusion in both R1 and R2. [R1, R2] [R1]
+- The chest X-ray shows moderate left pleural effusion and small right pleural effusion. [R1]
+- The lungs are hyperlucent and hyperinflated compatible with emphysema, which may be associated with pleural effusion. [R1]
+- The presence of pleural effusion is confirmed by the pathology detection results, with R1 and R2 showing high confidence in pleural effusion detection. [R1, R2] [R1]
 Next Steps / Recommendations:
-- Clinical correlation with patient symptoms and medical history is recommended to determine the cause of the pleural effusion. [Rx]
-- Follow-up imaging may be necessary to monitor the progression of the pleural effusion and to assess the effectiveness of any treatment. [Rx]</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess the cause and severity of the pleural effusion. [Rx]
+- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" t="n">
         <v>1</v>
@@ -2713,28 +2783,31 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
+        <v>2</v>
+      </c>
+      <c r="R26" t="n">
         <v>0.599</v>
       </c>
-      <c r="R26" t="n">
-        <v>0.8309783501148224</v>
-      </c>
       <c r="S26" t="n">
-        <v>0.7149891750574111</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.6765698264122009</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.6377849132061004</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V26" t="n">
-        <v>2</v>
-      </c>
-      <c r="W26" t="inlineStr">
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2764,16 +2837,21 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
         <v>0.6798410415649414</v>
       </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No lung consolidation or opacities detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
@@ -2787,12 +2865,9 @@
 - No further imaging is recommended at this time, but follow-up imaging may be necessary if symptoms persist or worsen. [Rx]</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
-        <v>2</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
         <v>1</v>
@@ -2801,28 +2876,31 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
+        <v>2</v>
+      </c>
+      <c r="R27" t="n">
         <v>0.541</v>
       </c>
-      <c r="R27" t="n">
-        <v>0.9039523124694824</v>
-      </c>
       <c r="S27" t="n">
-        <v>0.7224761562347413</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.6815523124694824</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.6112761562347413</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V27" t="n">
-        <v>2</v>
-      </c>
-      <c r="W27" t="inlineStr">
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="W27" t="n">
+        <v>2</v>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2852,16 +2930,21 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>0.704419732093811</v>
       </c>
-      <c r="I28" t="n">
-        <v>1</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pneumothorax detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
@@ -2875,12 +2958,9 @@
 - Follow-up imaging if symptoms persist or worsen. [Rx]</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
-        <v>2</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" t="n">
         <v>1</v>
@@ -2889,28 +2969,31 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
         <v>0.5629999999999999</v>
       </c>
-      <c r="R28" t="n">
-        <v>0.9113259196281432</v>
-      </c>
       <c r="S28" t="n">
-        <v>0.7371629598140716</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7969259196281433</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.6799629598140716</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V28" t="n">
-        <v>2</v>
-      </c>
-      <c r="W28" t="inlineStr">
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W28" t="n">
+        <v>2</v>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2940,34 +3023,36 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.7952942848205566</v>
+        <v>0.714</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
+        <v>0.7593117952346802</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Bilateral patchy pulmonary opacities and pleural effusions are noted on chest X-ray. [R1]
+- Bilateral patchy pulmonary opacities and pulmonary vascular congestion are noted, with a stable enlarged cardiomediastinal silhouette. [R1]
 Supporting Evidence:
-- Bilateral patchy pulmonary opacities are observed, indicating areas of increased density or cloudiness in the lung tissue. [R1]
-- Pleural effusions are detected on the chest X-ray, suggesting fluid accumulation in both sides of the lungs. [R1]
-- Pulmonary vascular congestion is also noted, indicating possible fluid overload or heart failure. [R1]
+- Interval improvement in left base consolidative opacity is observed. [R1]
+- Pulmonary vascular congestion is again noted. [R1]
+- A stable enlarged cardiomediastinal silhouette is present. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with patient symptoms and medical history is recommended to determine the cause of the findings. [Rx]
-- Further evaluation and consultation with a healthcare professional are necessary to develop an appropriate treatment plan. [Rx]</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to determine the cause of the observed pulmonary opacities and vascular congestion. [Rx]
+- Further evaluation and consultation with a healthcare professional are necessary to determine the appropriate treatment. [Rx]</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
         <v>1</v>
@@ -2976,28 +3061,31 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
         <v>0.533</v>
       </c>
-      <c r="R29" t="n">
-        <v>0.9385882854461669</v>
-      </c>
       <c r="S29" t="n">
-        <v>0.7357941427230834</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8133935385704041</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.6731967692852021</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V29" t="n">
-        <v>2</v>
-      </c>
-      <c r="W29" t="inlineStr">
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W29" t="n">
+        <v>2</v>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3027,35 +3115,36 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.4797349870204926</v>
+        <v>0.833</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
+        <v>0.567784309387207</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Insufficient evidence [R1], [R2] to confirm or rule out heart enlargement.
+- Insufficient evidence [R1], [R2] to indicate heart enlargement.
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest X-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
-- The comparison X-ray does not show any signs of heart enlargement. [R2]
-- The second chest X-ray also does not show any signs of heart enlargement. [R2-IMAGE]
+- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
+- No significant pathologies detected above threshold, including heart enlargement. [R2]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate symptoms of hypoxia. [Rx]
+- Further diagnostic testing, such as echocardiogram or electrocardiogram, may be necessary to assess heart function. [Rx]</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
         <v>1</v>
@@ -3064,28 +3153,31 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
         <v>0.5</v>
       </c>
-      <c r="R30" t="n">
-        <v>0.8439204961061477</v>
-      </c>
       <c r="S30" t="n">
-        <v>0.6719602480530739</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8035352928161621</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.651767646408081</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V30" t="n">
-        <v>2</v>
-      </c>
-      <c r="W30" t="inlineStr">
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W30" t="n">
+        <v>2</v>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3115,35 +3207,36 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.6954623460769653</v>
+        <v>0.6</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
+        <v>0.7696354985237122</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
 Supporting Evidence:
-- The chest x-ray shows lungs that are clear without focal consolidation, effusion, or pneumothorax. [R1]
-- The chest x-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
-- The lung fields are clear and there are no signs of infection, fluid accumulation, or other issues in the image. [R1-IMAGE]
-- The chest x-ray shows clear lung fields. [R2-IMAGE]
+- Lungs are clear without focal consolidation, effusion, or pneumothorax. [R1]
+- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
+- Normal heart size and negative for pneumoperitoneum. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
-- Further evaluation may be needed to assess the patient's overall health and identify any underlying conditions that may not be visible on the x-ray. [R1-IMAGE]</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess the patient's overall health and identify any potential underlying concerns. [Rx]
+- Further evaluation may be needed to rule out all possible conditions or issues. [Rx]</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" t="n">
         <v>1</v>
@@ -3152,28 +3245,31 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
         <v>0.588</v>
       </c>
-      <c r="R31" t="n">
-        <v>0.9086387038230895</v>
-      </c>
       <c r="S31" t="n">
-        <v>0.7483193519115448</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7708906495571137</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.6794453247785568</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V31" t="n">
-        <v>2</v>
-      </c>
-      <c r="W31" t="inlineStr">
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W31" t="n">
+        <v>2</v>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3203,35 +3299,36 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.5901783108711243</v>
+        <v>0.5</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
+        <v>0.5892553329467773</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1-IMAGE]
+- The chest X-ray appears normal. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
-- A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE]
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [R1-IMAGE]
-- The chest x-ray appears to be normal, with no visible signs of abnormalities or issues in the lungs, heart, or surrounding structures. [R2-IMAGE]
+- The chest x-ray shows no visible abnormalities or signs of disease. [R1-IMAGE]
+- The chest x-ray appears to be normal, with no visible signs of issues in the image. [R2-IMAGE]
+- A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE], [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
-- Further evaluation and tests may be needed depending on the patient's symptoms and clinical history. [R2-IMAGE]</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>2</v>
-      </c>
+- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying concerns. [R1-IMAGE], [R2-IMAGE]
+- Clinical correlation is recommended to assess the patient's overall health and identify any underlying issues. [Rx]</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
@@ -3240,28 +3337,31 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
         <v>0.537</v>
       </c>
-      <c r="R32" t="n">
-        <v>0.8770534932613372</v>
-      </c>
       <c r="S32" t="n">
-        <v>0.7070267466306686</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.6767765998840332</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.6068882999420167</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V32" t="n">
-        <v>2</v>
-      </c>
-      <c r="W32" t="inlineStr">
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="W32" t="n">
+        <v>2</v>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3293,33 +3393,35 @@
       <c r="G33" t="n">
         <v>1</v>
       </c>
-      <c r="H33" t="n">
-        <v>0.6743566989898682</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I33" t="n">
-        <v>1</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
+        <v>0.8103905916213989</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No acute abnormality detected. [R1]
 Supporting Evidence:
-- The chest X-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
-- Mild blunting of right costophrenic angle is noted, but its clinical significance is unclear. [R1]
+- The heart is normal in size. [R1]
+- The mediastinum is unremarkable. [R1]
+- Mild blunting of right costophrenic angle. [R1]
 - The lungs are otherwise grossly clear. [R1]
-- The chest X-ray is normal, with no apparent signs of lung disease or other issues. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to determine the significance of mild blunting of right costophrenic angle. [Rx]
-- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
+- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" t="n">
         <v>1</v>
@@ -3328,28 +3430,31 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
         <v>0.662</v>
       </c>
-      <c r="R33" t="n">
-        <v>0.9023070096969604</v>
-      </c>
       <c r="S33" t="n">
-        <v>0.7821535048484802</v>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9431171774864197</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.8025585887432098</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V33" t="n">
-        <v>2</v>
-      </c>
-      <c r="W33" t="inlineStr">
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W33" t="n">
+        <v>2</v>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3379,16 +3484,21 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
         <v>0.650692880153656</v>
       </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
@@ -3402,12 +3512,9 @@
 - Follow-up imaging if symptoms persist or new cardiac symptoms develop. [Rx]</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" t="n">
         <v>1</v>
@@ -3416,28 +3523,31 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
+        <v>1</v>
+      </c>
+      <c r="R34" t="n">
         <v>0.632</v>
       </c>
-      <c r="R34" t="n">
-        <v>0.8952078640460968</v>
-      </c>
       <c r="S34" t="n">
-        <v>0.7636039320230483</v>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.8064078640460968</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.7192039320230483</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V34" t="n">
-        <v>2</v>
-      </c>
-      <c r="W34" t="inlineStr">
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W34" t="n">
+        <v>2</v>
+      </c>
+      <c r="X34" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3467,16 +3577,21 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
         <v>0.6177862286567688</v>
       </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
@@ -3489,12 +3604,9 @@
 - Follow-up imaging if symptoms persist, but currently, there is no indication for immediate further imaging. [Rx]</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
-        <v>2</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" t="n">
         <v>1</v>
@@ -3503,28 +3615,31 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.636</v>
       </c>
-      <c r="R35" t="n">
-        <v>0.8853358685970306</v>
-      </c>
       <c r="S35" t="n">
-        <v>0.7606679342985153</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7853358685970308</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0.7106679342985154</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V35" t="n">
-        <v>2</v>
-      </c>
-      <c r="W35" t="inlineStr">
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W35" t="n">
+        <v>2</v>
+      </c>
+      <c r="X35" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3554,34 +3669,37 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.6230317354202271</v>
+        <v>0.571</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I36" t="n">
-        <v>1</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
+        <v>0.6796762943267822</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No pleural effusion visible on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
-- The absence of focal airspace opacity or pleural effusion is noted on the chest X-ray. [R1]
+- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
+- The chest X-ray does not show any visible pleural effusion. [R2-IMAGE]
+- Normal heart size and cardiomediastinal silhouette, which is consistent with no pleural effusion. [R1]
+- No focal airspace opacity, pleural effusion, or pneumothorax is observed on the chest X-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other causes of respiratory symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but pleural effusion is not visible on the current chest X-ray. [Rx]</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to assess the patient's symptoms and medical history. [Rx]
+- Follow-up imaging if symptoms persist or if the clinical correlation is inconclusive. [Rx]</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O36" t="n">
         <v>1</v>
@@ -3590,28 +3708,31 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
         <v>0.646</v>
       </c>
-      <c r="R36" t="n">
-        <v>0.8869095206260681</v>
-      </c>
       <c r="S36" t="n">
-        <v>0.7664547603130341</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7323028882980347</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.6891514441490174</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V36" t="n">
-        <v>2</v>
-      </c>
-      <c r="W36" t="inlineStr">
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W36" t="n">
+        <v>2</v>
+      </c>
+      <c r="X36" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3641,35 +3762,36 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>1</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.7451775074005127</v>
+        <v>0.667</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
+        <v>0.7085100412368774</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No lung consolidation or opacities detected on chest X-ray. [R1], [R2]
+- No lung consolidation or opacities detected on chest X-ray. [R1], [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any lung consolidation or opacities. [R1-IMAGE]
+- The lungs are clear bilaterally, with no evidence of focal consolidation. [R1]
+- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE]
 - The chest X-ray does not show any lung consolidation or opacities. [R2-IMAGE]
-- The lungs are clear bilaterally, with no evidence of focal consolidation, pneumothorax, or pleural effusion. [R1]
-- The lungs are clear bilaterally, with no evidence of focal consolidation, pneumothorax, or pleural effusion. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but currently, no indication for further imaging. [Rx]</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's chest pain. [Rx]
+- Follow-up imaging if symptoms persist, but currently, no indication for immediate further imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
         <v>1</v>
@@ -3678,28 +3800,31 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
         <v>0.672</v>
       </c>
-      <c r="R37" t="n">
-        <v>0.9235532522201537</v>
-      </c>
       <c r="S37" t="n">
-        <v>0.7977766261100769</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7793530123710632</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.7256765061855317</v>
       </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V37" t="n">
-        <v>2</v>
-      </c>
-      <c r="W37" t="inlineStr">
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W37" t="n">
+        <v>2</v>
+      </c>
+      <c r="X37" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3729,16 +3854,21 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
         <v>0.5247206687927246</v>
       </c>
-      <c r="I38" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - No signs of pneumothorax detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
@@ -3751,12 +3881,9 @@
 - Further evaluation of the patient's symptoms and medical history is necessary to determine the cause of hypoxia. [Rx]</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>2</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O38" t="n">
         <v>1</v>
@@ -3765,28 +3892,31 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
         <v>0.475</v>
       </c>
-      <c r="R38" t="n">
-        <v>0.8574162006378173</v>
-      </c>
       <c r="S38" t="n">
-        <v>0.6662081003189086</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7242162006378173</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.5996081003189087</v>
       </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V38" t="n">
-        <v>2</v>
-      </c>
-      <c r="W38" t="inlineStr">
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W38" t="n">
+        <v>2</v>
+      </c>
+      <c r="X38" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3816,34 +3946,37 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.766639232635498</v>
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
+        <v>0.8658748865127563</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray shows clear lungs with no pneumothorax or pleural effusion, but further evaluation is needed due to conflicting findings. [R1]
+- No significant pathologies detected above threshold. [R1], [R2]
 Supporting Evidence:
-- Lungs are clear with no pneumothorax or pleural effusion. [R1]
-- The heart and mediastinum are within normal limits. [R1]
-- However, there are conflicting findings of pleural effusions and pneumothorax on other X-rays. [R1-IMAGE, R2-IMAGE] [R1]
+- Lungs are clear. [R1]
+- No pneumothorax or pleural effusion detected. [R1]
+- Heart and mediastinum are within normal limits. [R1]
+- Bony structures are intact. [R1]
 Next Steps / Recommendations:
-- Clinical correlation and further evaluation are needed to determine the cause and significance of the conflicting findings. [Rx]
-- Follow-up imaging if symptoms persist, taking into account the conflicting findings from previous X-rays. [Rx]</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
-        <v>2</v>
-      </c>
+- Clinical correlation recommended to further evaluate the patient's respiratory symptoms. [Rx]
+- Follow-up imaging if symptoms persist, as the current findings do not explain the patient's shortness of breath. [Rx]</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
         <v>1</v>
@@ -3852,28 +3985,31 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
+        <v>1</v>
+      </c>
+      <c r="R39" t="n">
         <v>0.6</v>
       </c>
-      <c r="R39" t="n">
-        <v>0.8631917697906494</v>
-      </c>
       <c r="S39" t="n">
-        <v>0.7315958848953247</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.9597624659538269</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.7798812329769134</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V39" t="n">
-        <v>2</v>
-      </c>
-      <c r="W39" t="inlineStr">
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W39" t="n">
+        <v>2</v>
+      </c>
+      <c r="X39" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3903,16 +4039,21 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
-      </c>
-      <c r="H40" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
         <v>0.5847504734992981</v>
       </c>
-      <c r="I40" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
 - Insufficient evidence to indicate heart enlargement. [R1], [R2]
@@ -3926,12 +4067,9 @@
 - Follow-up imaging if symptoms persist, but based on current evidence, it is not indicated. [Rx]</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
-        <v>2</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O40" t="n">
         <v>1</v>
@@ -3940,28 +4078,31 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
+        <v>1</v>
+      </c>
+      <c r="R40" t="n">
         <v>0.458</v>
       </c>
-      <c r="R40" t="n">
-        <v>0.8754251420497894</v>
-      </c>
       <c r="S40" t="n">
-        <v>0.6667125710248947</v>
-      </c>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
+        <v>0.7610251420497894</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.6095125710248948</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V40" t="n">
-        <v>2</v>
-      </c>
-      <c r="W40" t="inlineStr">
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W40" t="n">
+        <v>2</v>
+      </c>
+      <c r="X40" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>

--- a/mmrag_evaluation_results.xlsx
+++ b/mmrag_evaluation_results.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -574,7 +574,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.625</v>
+        <v>0.778</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -582,7 +582,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.7120616436004639</v>
+        <v>0.7160155773162842</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
@@ -595,10 +595,10 @@
 Supporting Evidence:
 - The cardiac silhouette and mediastinum size are within normal limits. [R1]
 - There is no pulmonary edema. [R1]
-- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R1-IMAGE]
+- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
-- Further evaluation may be needed to rule out all possible conditions or diseases. [Rx]</t>
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
+- Further evaluation may be necessary depending on the patient's symptoms and medical history. [Rx]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
@@ -612,16 +612,16 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0.633</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7636184930801392</v>
+        <v>0.8260046731948852</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6983092465400695</v>
+        <v>0.7295023365974427</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.5643822550773621</v>
+        <v>0.5441363453865051</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -683,14 +683,14 @@
       <c r="L3" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Borderline cardiomegaly and enlarged pulmonary arteries are noted on the chest X-ray. [R1]
+- Borderline cardiomegaly detected. [R1]
 Supporting Evidence:
-- The chest X-ray shows borderline cardiomegaly, which may indicate mild cardiac enlargement. [R1]
-- Enlarged pulmonary arteries are visible on the X-ray, which could be related to various conditions such as pulmonary hypertension or chronic lung disease. [R1]
-- The lungs appear clear on the X-ray, which suggests that there is no obvious lung disease or infection present. [R1]
+- The chest X-ray shows borderline cardiomegaly, which is an enlargement of the heart. [R1]
+- Enlarged pulmonary arteries are also visible on the X-ray. [R1]
+- The lungs appear clear, indicating no visible signs of lung disease. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with the patient's medical history and symptoms is recommended to further evaluate the significance of the borderline cardiomegaly and enlarged pulmonary arteries. [Rx]
-- Further diagnostic testing, such as an echocardiogram or pulmonary function tests, may be necessary to determine the underlying cause of the abnormal findings on the chest X-ray. [Rx]</t>
+- Clinical correlation with the patient's history and symptoms is recommended to further evaluate the significance of the borderline cardiomegaly. [Rx]
+- Further evaluation with echocardiography or other diagnostic tests may be necessary to assess cardiac function and determine the cause of the borderline cardiomegaly. [Rx]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -710,10 +710,10 @@
         <v>0.576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8693146765232086</v>
+        <v>0.7032409036159516</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7226573382616043</v>
+        <v>0.6396204518079758</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.222</v>
+        <v>0.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5643539428710938</v>
+        <v>0.5670633316040039</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
@@ -777,13 +777,13 @@
           <t>Diagnosis / Impression:
 - No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest x-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
+- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
+- The heart appears to be within normal size and shape in the image. [R1-IMAGE]
 - The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
-- The heart appears to be within normal size and shape in the image. [R1-IMAGE]
-- The absence of cardiomegaly or abnormal cardiac silhouette on chest X-ray is consistent with a normal cardiac silhouette. [R2]
+- The heart appears to be within normal size and shape in the image. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
+- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show cardiomegaly or abnormal cardiac silhouette. [Rx]</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -797,16 +797,16 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0.5639999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5581061828613281</v>
+        <v>0.7701189994812012</v>
       </c>
       <c r="T4" t="n">
-        <v>0.561053091430664</v>
+        <v>0.6670594997406005</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="W4" t="n">
@@ -889,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0.531</v>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6857281923294067</v>
+        <v>0.691457211971283</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -960,15 +960,15 @@
       <c r="L6" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No pleural effusion visible on the chest X-ray. [R1], [R2]
+- No pleural effusion detected on chest X-ray. [R1]
 Supporting Evidence:
 - The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest X-ray does not show any visible pleural effusion. [R2-IMAGE]
+- The chest x-ray does not show any visible anatomical findings related to pleural effusion. [R2-IMAGE]
 - The cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion. [R1]
 - There is no pneumothorax or pleural effusion, as stated in the radiology report. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show pleural effusion. [Rx]</t>
+- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely that pleural effusion will be detected. [Rx]</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
@@ -982,16 +982,16 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0.644</v>
       </c>
       <c r="S6" t="n">
-        <v>0.816918457698822</v>
+        <v>0.8186371635913848</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7304592288494109</v>
+        <v>0.7313185817956924</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.599</v>
@@ -1212,7 +1212,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1221,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.8089767098426819</v>
+        <v>0.7059441804885864</v>
       </c>
       <c r="J9" t="n">
         <v>1</v>
@@ -1241,11 +1241,11 @@
 - No significant pathologies detected above threshold. [R1]
 Supporting Evidence:
 - The heart, pulmonary structures, and mediastinum are within normal limits. [R1]
-- No pleural effusion or pneumothorax is present. [R1]
-- No focal air space opacity to suggest a pneumonia. [R1]
+- There is no pleural effusion or pneumothorax. [R1]
+- The chest X-ray shows no focal air space opacity to suggest a pneumonia. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and history of mitral valve prolapse. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current evidence, no immediate indication for further imaging. [Rx]</t>
+- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
+- Follow-up imaging if symptoms persist, but no immediate indication for further imaging based on current findings. [Rx]</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -1259,16 +1259,16 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0.5649999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9426930129528045</v>
+        <v>0.8317832541465761</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7538465064764022</v>
+        <v>0.6983916270732879</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.60411536693573</v>
+        <v>0.6633126735687256</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1330,13 +1330,14 @@
       <c r="L10" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No signs of heart enlargement detected on chest X-ray. [R1], [R2]
+- No heart enlargement detected. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The cardiac silhouette is not enlarged on the chest X-ray. [R1]
+- The cardiac silhouette is not enlarged. [R1]
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE], [R2-IMAGE]
+- There is no consolidation, pleural effusion, or pneumothorax, which can sometimes be associated with heart enlargement. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but no immediate indication for further imaging based on current chest X-ray findings. [Rx]</t>
+- Clinical correlation recommended to assess the patient's overall health and identify any potential issues that may not be visible on the X-ray. [Rx]
+- Further evaluation may be needed to assess the patient's symptoms and determine the cause of chest pain. [Rx]</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -1350,16 +1351,16 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.594</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8812346100807189</v>
+        <v>0.8989938020706176</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7376173050403594</v>
+        <v>0.7464969010353089</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
@@ -1395,7 +1396,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1404,7 +1405,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>0.636</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1412,7 +1413,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6806971430778503</v>
+        <v>0.6991814970970154</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
@@ -1423,11 +1424,11 @@
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
 Supporting Evidence:
-- The lungs are normally inflated without evidence of focal airspace disease, pleural effusion, or pneumothorax. [R1]
+- The lung fields are normally inflated without evidence of focal airspace disease, pleural effusion, or pneumothorax. [R1]
 - The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
-- The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
+- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the lung fields. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential underlying concerns. [Rx]
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
 - Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
         </is>
       </c>
@@ -1442,16 +1443,16 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0.622</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9042091429233551</v>
+        <v>0.7641544491291046</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7631045714616775</v>
+        <v>0.6930772245645522</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1487,7 +1488,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1504,7 +1505,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.7782972455024719</v>
+        <v>0.7799336314201355</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1520,7 +1521,7 @@
 - No pneumothorax or pleural effusion. [R1]
 - No acute osseous findings. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential concerns. [Rx]
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
 - Further evaluation may be needed if symptoms persist. [Rx]</t>
         </is>
       </c>
@@ -1535,16 +1536,16 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0.617</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8134891736507415</v>
+        <v>0.8139800894260406</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7152445868253707</v>
+        <v>0.7154900447130204</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
@@ -1580,7 +1581,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1589,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1597,7 +1598,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.820636510848999</v>
+        <v>0.8339194059371948</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1606,7 +1607,7 @@
       <c r="L13" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No significant abnormal findings detected on the chest X-ray. [R1]
+- No abnormal findings detected on the chest X-ray. [R1]
 Supporting Evidence:
 - Lungs are clear bilaterally. [R1]
 - Cardiac and mediastinal silhouettes are normal. [R1]
@@ -1615,7 +1616,7 @@
 - No acute bony abnormality. [R1]
 Next Steps / Recommendations:
 - Clinical correlation recommended to rule out conditions not visible on chest X-ray. [Rx]
-- Follow-up imaging if symptoms persist or clinical history suggests underlying pathology. [Rx]</t>
+- Follow-up imaging if symptoms persist or clinical history suggests underlying condition. [Rx]</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -1629,16 +1630,16 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0.659</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8461909532546998</v>
+        <v>0.9001758217811584</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7525954766273499</v>
+        <v>0.7795879108905792</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
@@ -1674,7 +1675,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1683,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.429</v>
+        <v>0.3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1691,7 +1692,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8997962474822998</v>
+        <v>0.8635129332542419</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -1700,15 +1701,15 @@
       <c r="L14" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
+- No cardiomegaly or abnormal cardiac silhouette detected. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The cardiac silhouette is borderline enlarged on the chest radiograph. [R1]
-- Mediastinal contours are within normal limits on the chest radiograph. [R1]
-- The chest X-ray does not show any large pleural effusion or pneumothorax. [R1]
-- The heart appears to be within normal size and shape on the image. [R2-IMAGE]
+- The chest x-ray does not show any signs of cardiomegaly. [R1-IMAGE]
+- The mediastinal contours are within normal limits. [R1]
+- There is no large pleural effusion or pneumothorax. [R1]
+- The cardiac silhouette is borderline enlarged, but this is not a definitive indicator of cardiomegaly. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the borderline enlarged cardiac silhouette. [Rx]
-- Follow-up imaging if symptoms persist, considering the borderline enlarged cardiac silhouette. [Rx]</t>
+- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
+- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -1722,16 +1723,16 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0.726</v>
       </c>
       <c r="S14" t="n">
-        <v>0.74153887424469</v>
+        <v>0.6790538799762725</v>
       </c>
       <c r="T14" t="n">
-        <v>0.733769437122345</v>
+        <v>0.7025269399881362</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1740,7 +1741,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>RETRY</t>
         </is>
       </c>
       <c r="W14" t="n">
@@ -1776,7 +1777,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.714</v>
+        <v>0.75</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1784,7 +1785,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.7411871552467346</v>
+        <v>0.8714293837547302</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1795,12 +1796,13 @@
           <t>Diagnosis / Impression:
 - No signs of pulmonary congestion or edema detected on the chest X-ray. [R1], [R2]
 Supporting Evidence:
-- The chest x-ray shows no focal alveolar consolidation, no definite pleural effusion seen. [R1]
-- No typical findings of pulmonary edema are present on the chest x-ray. [R1]
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R2-IMAGE]
+- The chest x-ray shows heart size within normal limits, stable mediastinal and hilar contours. [R1]
+- Mild hyperinflation appears similar to prior, with no focal alveolar consolidation or definite pleural effusion seen. [R1]
+- Scattered chronic appearing irregular interstitial markings are present, but no typical findings of pulmonary edema are observed. [R1]
+- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE], [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to determine the overall health status of the patient. [Rx]
-- Further evaluation by a healthcare professional is necessary to assess the patient's condition. [Rx]</t>
+- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
+- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not appear necessary. [Rx]</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -1814,16 +1816,16 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0.67</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8079561465740204</v>
+        <v>0.8614288151264191</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7389780732870102</v>
+        <v>0.7657144075632096</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1868,7 +1870,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.8</v>
+        <v>0.429</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1876,7 +1878,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.7225977778434753</v>
+        <v>0.5505229830741882</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
@@ -1885,15 +1887,15 @@
       <c r="L16" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No pleural effusion visible on the chest X-ray. [R1], [R2]
+- No visible pleural effusion detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest X-ray does not show any visible pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
-- Cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion. [R1]
-- Lungs are clear, further supporting the absence of pleural effusion. [R1]
+- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
+- The chest x-ray does not show any visible signs of pleural effusion. [R2-IMAGE]
+- The absence of visible pleural effusion in a chest x-ray does not necessarily rule out the presence of fluid accumulation in the pleural space. [R1-IMAGE]
+- Further diagnostic tests, such as a chest CT scan or ultrasound, may be needed to confirm the presence or absence of pleural effusion. [R1-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the cause of dyspnea. [Rx]
-- Follow-up imaging if symptoms persist, but pleural effusion is unlikely given the current findings. [Rx]</t>
+- Clinical correlation recommended to assess the presence of pleural effusion despite negative chest X-ray findings. [Rx]
+- Follow-up imaging with a chest CT scan or ultrasound if symptoms persist or worsen. [Rx]</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -1907,16 +1909,16 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="n">
         <v>0.573</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8367793333530427</v>
+        <v>0.6367568949222565</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7048896666765213</v>
+        <v>0.6048784474611282</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1925,7 +1927,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>RETRY</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -1948,34 +1950,86 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>ragas_failed</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>unsupported operand type(s) for *: 'NoneType' and 'float'</t>
+          <t>Diagnosis / Impression:
+No pathologies detected above threshold on the chest X-ray. [R1]
+Supporting Evidence:
+- The DenseNet CNN algorithm used for pathology detection did not identify any abnormalities above the set threshold. [R1]
+- The absence of pathologies detected by the algorithm suggests that the chest X-ray is likely normal or shows no significant abnormalities. [R2]
+- However, it is essential to note that the absence of findings on a chest X-ray does not rule out the presence of lung consolidation or opacities, especially if they are mild or not severe enough to be detected by the algorithm. [R3]
+Next Steps / Recommendations:
+- Clinical correlation with the patient's symptoms and medical history is recommended to determine the significance of the normal chest X-ray findings. [Rx]
+- If the patient's symptoms persist or worsen, follow-up imaging may be necessary to rule out any underlying conditions. [Rx]</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>XRAY</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2040,7 +2094,7 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.774</v>
@@ -2085,7 +2139,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -2094,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.267</v>
+        <v>0.75</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2102,7 +2156,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6915655136108398</v>
+        <v>0.8006788492202759</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
@@ -2111,15 +2165,15 @@
       <c r="L19" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- The chest X-ray shows several key findings, including cardiomegaly, bilateral pleural effusions, right-sided pneumothorax, left-sided pneumothorax, bilateral rib fractures, right-sided hemopneumothorax, and left-sided pneumomediastinum. [R1-IMAGE], [R2-IMAGE]
+- No significant pathologies detected above threshold. [R1], [R2]
 Supporting Evidence:
-- Cardiomegaly, which is an enlargement of the heart, is visible on the chest X-ray. [R1-IMAGE]
-- Bilateral pleural effusions, which are abnormal accumulations of fluid in the pleural space surrounding both lungs, are present. [R1-IMAGE]
-- Right-sided pneumothorax, which is a collapsed lung on the right side, is visible on the chest X-ray. [R1-IMAGE]
-- Left-sided pneumothorax, which is a collection of air or gas in the pleural space causing the lung to collapse, is present. [R2-IMAGE]
+- Heart size within normal limits. [R1]
+- No focal alveolar consolidation, no definite pleural effusion seen. [R1]
+- No typical findings of pulmonary edema. [R1]
+- No pneumothorax. [R1]
 Next Steps / Recommendations:
-- Clinical correlation with the patient's symptoms and medical history is recommended to determine the cause of the observed abnormalities. [Rx]
-- Follow-up imaging may be necessary if the patient's symptoms persist or worsen. [Rx]</t>
+- Clinical correlation recommended. [Rx]
+- Insufficient evidence [Rx]</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -2133,16 +2187,16 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>0.612</v>
       </c>
       <c r="S19" t="n">
-        <v>0.614269654083252</v>
+        <v>0.8402036547660828</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6131348270416259</v>
+        <v>0.7261018273830414</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2151,7 +2205,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="W19" t="n">
@@ -2178,7 +2232,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
@@ -2187,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.75</v>
+        <v>0.444</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2195,7 +2249,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.5309703946113586</v>
+        <v>0.5567283630371094</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
@@ -2204,15 +2258,15 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No heart enlargement detected on chest X-ray. [R1], [R2]
+- No heart enlargement detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
-- Heart size is normal on the X-ray findings. [R1]
-- No signs of heart enlargement were observed on the chest X-ray. [R1]
+- The chest x-ray appears to be normal. [R2-IMAGE]
+- A chest X-ray is a standard tool for assessing heart size, but it may not always detect subtle abnormalities. [R1]
+- Further evaluation may be needed to assess the patient's overall cardiovascular health. [R2]
 Next Steps / Recommendations:
-- Clinical correlation recommended to confirm the absence of heart enlargement. [Rx]
-- Further evaluation with echocardiography or other diagnostic tests may be necessary if symptoms persist. [Rx]</t>
+- Clinical correlation with other diagnostic tests (e.g., ECG, echocardiogram) is recommended to confirm the absence of heart enlargement. [Rx]
+- Follow-up imaging if symptoms persist or if there is a change in clinical status. [Rx]</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
@@ -2226,16 +2280,16 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
         <v>0.605</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7592911183834077</v>
+        <v>0.6446185089111328</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6821455591917038</v>
+        <v>0.6248092544555663</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2244,7 +2298,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>RETRY</t>
         </is>
       </c>
       <c r="W20" t="n">
@@ -2271,7 +2325,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
@@ -2288,7 +2342,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6488034725189209</v>
+        <v>0.6545675992965698</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -2298,14 +2352,13 @@
         <is>
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
-- The lung fields appear to be clear on the chest X-ray. [R2-IMAGE]
 Supporting Evidence:
 - The lungs are well expanded and clear. [R1]
+- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
 - There are no focal air space opacities. [R1]
-- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
 - The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to determine the patient's overall health status and identify any potential underlying concerns. [Rx]
+- Clinical correlation recommended to rule out underlying conditions. [Rx]
 - Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
         </is>
       </c>
@@ -2320,16 +2373,16 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.619</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8946410417556763</v>
+        <v>0.8963702797889709</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7568205208778381</v>
+        <v>0.7576851398944855</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2374,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2382,7 +2435,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.493852436542511</v>
+        <v>0.4528967440128326</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -2392,13 +2445,15 @@
         <is>
           <t>Diagnosis / Impression:
 - The chest X-ray appears normal. [R1-IMAGE]
+- The chest X-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. This is consistent with the patient's clinical presentation and the absence of any significant findings on the chest X-ray. [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
-- A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE]
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [R2-IMAGE]
+- The chest x-ray appears to be normal, which means that there are no visible abnormalities or signs of disease in the image. [R1-IMAGE]
+- The chest X-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R2-IMAGE]
+- A normal chest x-ray does not necessarily rule out all possible conditions or issues, but it is a reassuring finding that can help guide further evaluation and clinical correlation. [R1-IMAGE]
+- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying concerns. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues. [Rx]
-- Further evaluation and tests may be needed depending on the patient's symptoms and clinical history. [Rx]</t>
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
+- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -2412,16 +2467,16 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R22" t="n">
         <v>0.593</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7149557309627532</v>
+        <v>0.4358690232038498</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6539778654813766</v>
+        <v>0.5144345116019249</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2430,7 +2485,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="W22" t="n">
@@ -2504,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0.637</v>
@@ -2549,7 +2604,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -2598,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.473</v>
@@ -2652,7 +2707,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.714</v>
+        <v>0.833</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2660,7 +2715,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.7096673250198364</v>
+        <v>0.5938956737518311</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -2672,12 +2727,11 @@
 - No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
 - The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
-- The lungs appear to be clear and free of any significant fluid accumulation or other abnormalities in the image. [R2-IMAGE]
-- Cardiomediastinal silhouette is within normal limits of size and appearance, indicating no signs of pulmonary congestion. [R1]
-- Pulmonary vascularity is unremarkable, which is consistent with the absence of pulmonary congestion or edema. [R1]
+- The lungs are expanded and clear of airspace disease. [R1]
+- There is no visible abnormality in the lungs that would indicate fluid accumulation or swelling. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to further evaluate the patient's symptoms of dyspnea. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it is unlikely to show signs of pulmonary congestion or edema. [Rx]</t>
+- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show signs of pulmonary congestion or edema. [Rx]</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -2691,16 +2745,16 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0.55</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7985001975059509</v>
+        <v>0.8113687021255493</v>
       </c>
       <c r="T25" t="n">
-        <v>0.6742500987529755</v>
+        <v>0.6806843510627747</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
@@ -2745,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2753,7 +2807,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6392327547073364</v>
+        <v>0.5254111886024475</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -2762,14 +2816,14 @@
       <c r="L26" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Pleural effusion is visible on the chest X-ray. [R1]
+- Pleural effusion is not visible on the chest X-ray, but further imaging techniques such as CT scans may be needed for a more accurate assessment. [R1-IMAGE]
 Supporting Evidence:
-- The chest X-ray shows moderate left pleural effusion and small right pleural effusion. [R1]
-- The lungs are hyperlucent and hyperinflated compatible with emphysema, which may be associated with pleural effusion. [R1]
-- The presence of pleural effusion is confirmed by the pathology detection results, with R1 and R2 showing high confidence in pleural effusion detection. [R1, R2] [R1]
+- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
+- A chest x-ray may not always detect subtle or small amounts of pleural effusion. [R1-IMAGE]
+- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the cause and severity of the pleural effusion. [Rx]
-- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
+- Clinical correlation recommended to assess the presence of pleural effusion. [Rx]
+- Follow-up imaging with CT scan if symptoms persist or if pleural effusion is suspected. [Rx]</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -2789,10 +2843,10 @@
         <v>0.599</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6765698264122009</v>
+        <v>0.4576233565807343</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6377849132061004</v>
+        <v>0.5283116782903672</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2801,7 +2855,7 @@
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="W26" t="n">
@@ -2828,7 +2882,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -2930,7 +2984,7 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.714</v>
+        <v>0.857</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2975,10 +3029,10 @@
         <v>0.5629999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>0.7969259196281433</v>
+        <v>0.8541259196281433</v>
       </c>
       <c r="T28" t="n">
-        <v>0.6799629598140716</v>
+        <v>0.7085629598140717</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -3014,7 +3068,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -3023,7 +3077,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.714</v>
+        <v>0.333</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3031,7 +3085,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.7593117952346802</v>
+        <v>0.6758285760879517</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
@@ -3040,14 +3094,14 @@
       <c r="L29" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Bilateral patchy pulmonary opacities and pulmonary vascular congestion are noted, with a stable enlarged cardiomediastinal silhouette. [R1]
+- Cardiomegaly and bilateral pleural effusions are present. [R2-IMAGE]
 Supporting Evidence:
-- Interval improvement in left base consolidative opacity is observed. [R1]
-- Pulmonary vascular congestion is again noted. [R1]
-- A stable enlarged cardiomediastinal silhouette is present. [R1]
+- Cardiomegaly is an enlargement of the heart. [R2-IMAGE]
+- Bilateral pleural effusions are abnormal accumulations of fluid in the pleural space surrounding both lungs. [R2-IMAGE]
+- A left-sided pneumothorax is a collection of air or gas in the pleural space that can cause the lung to collapse. [R2-IMAGE]
 Next Steps / Recommendations:
-- Clinical correlation recommended to determine the cause of the observed pulmonary opacities and vascular congestion. [Rx]
-- Further evaluation and consultation with a healthcare professional are necessary to determine the appropriate treatment. [Rx]</t>
+- Clinical correlation recommended to determine the cause of cardiomegaly and pleural effusions. [Rx]
+- Follow-up imaging if symptoms persist to assess for any changes in the patient's condition. [Rx]</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -3061,16 +3115,16 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>0.533</v>
       </c>
       <c r="S29" t="n">
-        <v>0.8133935385704041</v>
+        <v>0.6359485728263855</v>
       </c>
       <c r="T29" t="n">
-        <v>0.6731967692852021</v>
+        <v>0.5844742864131928</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -3079,7 +3133,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>RETRY</t>
         </is>
       </c>
       <c r="W29" t="n">
@@ -3106,7 +3160,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -3115,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.833</v>
+        <v>0</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3123,7 +3177,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.567784309387207</v>
+        <v>0.4739030599594116</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
@@ -3132,14 +3186,14 @@
       <c r="L30" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Insufficient evidence [R1], [R2] to indicate heart enlargement.
+- Insufficient evidence [R1], [R2] to confirm or rule out heart enlargement.
 Supporting Evidence:
 - The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
+- The chest X-ray appears to be normal, with no visible abnormalities or issues related to the heart. [R1-IMAGE]
 - The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
-- No significant pathologies detected above threshold, including heart enlargement. [R2]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate symptoms of hypoxia. [Rx]
-- Further diagnostic testing, such as echocardiogram or electrocardiogram, may be necessary to assess heart function. [Rx]</t>
+- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
+- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -3153,16 +3207,16 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>0.5</v>
       </c>
       <c r="S30" t="n">
-        <v>0.8035352928161621</v>
+        <v>0.4421709179878235</v>
       </c>
       <c r="T30" t="n">
-        <v>0.651767646408081</v>
+        <v>0.4710854589939117</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3171,7 +3225,7 @@
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="W30" t="n">
@@ -3198,7 +3252,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -3207,7 +3261,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3215,7 +3269,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7696354985237122</v>
+        <v>0.7221204042434692</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -3226,12 +3280,12 @@
           <t>Diagnosis / Impression:
 - The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
 Supporting Evidence:
-- Lungs are clear without focal consolidation, effusion, or pneumothorax. [R1]
-- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
-- Normal heart size and negative for pneumoperitoneum. [R1]
+- The lungs are clear without focal consolidation, effusion, or pneumothorax. [R1]
+- The chest x-ray appears to be normal, with no visible signs of abnormalities or issues in the lung fields. [R1-IMAGE]
+- The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
 Next Steps / Recommendations:
 - Clinical correlation recommended to assess the patient's overall health and identify any potential underlying concerns. [Rx]
-- Further evaluation may be needed to rule out all possible conditions or issues. [Rx]</t>
+- Further evaluation may be needed to assess the patient's overall health and identify any underlying conditions that may not be visible on the x-ray. [Rx]</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -3245,16 +3299,16 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0.588</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7708906495571137</v>
+        <v>0.7834361212730407</v>
       </c>
       <c r="T31" t="n">
-        <v>0.6794453247785568</v>
+        <v>0.6857180606365203</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3299,7 +3353,7 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3307,7 +3361,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5892553329467773</v>
+        <v>0.5627533793449402</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
@@ -3318,12 +3372,13 @@
           <t>Diagnosis / Impression:
 - The chest X-ray appears normal. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray shows no visible abnormalities or signs of disease. [R1-IMAGE]
-- The chest x-ray appears to be normal, with no visible signs of issues in the image. [R2-IMAGE]
-- A normal chest x-ray does not necessarily rule out all possible conditions or diseases. [R1-IMAGE], [R2-IMAGE]
+- The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
+- The chest X-ray appears to be normal, with no visible abnormalities or signs of disease in the image. [R2-IMAGE]
+- A normal chest x-ray does not necessarily rule out all possible conditions or diseases, and further evaluation and tests may be needed depending on the patient's clinical history and symptoms. [R1-IMAGE]
+- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying concerns that may not be apparent on the X-ray. [R2-IMAGE]
 Next Steps / Recommendations:
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying concerns. [R1-IMAGE], [R2-IMAGE]
-- Clinical correlation is recommended to assess the patient's overall health and identify any underlying issues. [Rx]</t>
+- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns that may not be apparent on the X-ray. [Rx]
+- Further evaluation and tests may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -3343,10 +3398,10 @@
         <v>0.537</v>
       </c>
       <c r="S32" t="n">
-        <v>0.6767765998840332</v>
+        <v>0.468826013803482</v>
       </c>
       <c r="T32" t="n">
-        <v>0.6068882999420167</v>
+        <v>0.502913006901741</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -3355,7 +3410,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>RETRY</t>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="W32" t="n">
@@ -3382,7 +3437,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -3430,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>0.662</v>
@@ -3475,7 +3530,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -3523,7 +3578,7 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0.632</v>
@@ -3615,7 +3670,7 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0.636</v>
@@ -3669,7 +3724,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.571</v>
+        <v>0.714</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3677,7 +3732,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6796762943267822</v>
+        <v>0.6911731958389282</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -3688,13 +3743,12 @@
           <t>Diagnosis / Impression:
 - No pleural effusion visible on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
 Supporting Evidence:
-- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
-- The chest X-ray does not show any visible pleural effusion. [R2-IMAGE]
-- Normal heart size and cardiomediastinal silhouette, which is consistent with no pleural effusion. [R1]
-- No focal airspace opacity, pleural effusion, or pneumothorax is observed on the chest X-ray. [R1]
+- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
+- The chest x-ray does not show any visible signs of pleural effusion. [R2-IMAGE]
+- The heart size and cardiomediastinal silhouette are normal, which is consistent with the absence of pleural effusion. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist or if the clinical correlation is inconclusive. [Rx]</t>
+- Clinical correlation recommended to rule out other causes of respiratory symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but pleural effusion is unlikely given the current chest X-ray findings. [Rx]</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -3708,16 +3762,16 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0.646</v>
       </c>
       <c r="S36" t="n">
-        <v>0.7323028882980347</v>
+        <v>0.7929519587516785</v>
       </c>
       <c r="T36" t="n">
-        <v>0.6891514441490174</v>
+        <v>0.7194759793758392</v>
       </c>
       <c r="U36" t="inlineStr">
         <is>
@@ -3753,7 +3807,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -3800,7 +3854,7 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0.672</v>
@@ -3845,7 +3899,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -3892,7 +3946,7 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0.475</v>
@@ -3937,7 +3991,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
@@ -3946,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>0.714</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3954,7 +4008,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.8658748865127563</v>
+        <v>0.7861149907112122</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -3963,15 +4017,15 @@
       <c r="L39" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- No significant pathologies detected above threshold. [R1], [R2]
+- No significant pathologies detected above threshold. [R1]
 Supporting Evidence:
 - Lungs are clear. [R1]
 - No pneumothorax or pleural effusion detected. [R1]
 - Heart and mediastinum are within normal limits. [R1]
 - Bony structures are intact. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's respiratory symptoms. [Rx]
-- Follow-up imaging if symptoms persist, as the current findings do not explain the patient's shortness of breath. [Rx]</t>
+- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
+- Follow-up imaging if symptoms persist, but no immediate indication for further X-ray. [Rx]</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
@@ -3985,16 +4039,16 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0.6</v>
       </c>
       <c r="S39" t="n">
-        <v>0.9597624659538269</v>
+        <v>0.8214344972133636</v>
       </c>
       <c r="T39" t="n">
-        <v>0.7798812329769134</v>
+        <v>0.7107172486066817</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -4030,7 +4084,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -4039,7 +4093,7 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.714</v>
+        <v>0.5</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4047,7 +4101,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5847504734992981</v>
+        <v>0.568744421005249</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4056,15 +4110,14 @@
       <c r="L40" t="inlineStr">
         <is>
           <t>Diagnosis / Impression:
-- Insufficient evidence to indicate heart enlargement. [R1], [R2]
+- Insufficient evidence to confirm or rule out heart enlargement. [R1], [R2]
 Supporting Evidence:
-- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
-- The heart and mediastinum are normal on the chest X-ray. [R1]
-- Both lungs are clear and expanded on the chest X-ray. [R1]
+- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE], [R2-IMAGE]
+- A chest X-ray is not the most definitive imaging modality for assessing heart size, as it may not always provide clear visualization of the heart's structure. [R1-IMAGE]
+- Both lungs are clear and expanded, and the heart and mediastinum appear normal on the chest X-ray. [R1]
 Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is not indicated. [Rx]</t>
+- Clinical correlation with other diagnostic modalities (e.g., echocardiogram, electrocardiogram) is recommended to further assess heart size and function. [Rx]
+- Follow-up imaging with a more definitive modality (e.g., echocardiogram) if symptoms persist or if there is a high clinical suspicion of heart enlargement. [Rx]</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
@@ -4078,16 +4131,16 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R40" t="n">
         <v>0.458</v>
       </c>
       <c r="S40" t="n">
-        <v>0.7610251420497894</v>
+        <v>0.6706233263015747</v>
       </c>
       <c r="T40" t="n">
-        <v>0.6095125710248948</v>
+        <v>0.5643116631507874</v>
       </c>
       <c r="U40" t="inlineStr">
         <is>
@@ -4096,7 +4149,7 @@
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>RETRY</t>
         </is>
       </c>
       <c r="W40" t="n">

--- a/mmrag_evaluation_results.xlsx
+++ b/mmrag_evaluation_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X40"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,70 +481,85 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>ActionabilityScore</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ContradictionFlag</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>OfflineClinicalCorrectness</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>generated_answer</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>expected_answer</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>total_iterations</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>retrieval_attempts</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>reasoning_attempts</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>refinement_count</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>forced_complete</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>evidence_quality</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>response_quality</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>overall_quality</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>evidence_decision</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>response_decision</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>evidence_count</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>modality</t>
         </is>
@@ -556,7 +571,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Confirm whether the chest X-ray appears normal.</t>
+          <t>Patient 1 had a positive TB test. What does the chest X-ray show regarding pulmonary and cardiac findings? Is there any evidence of active TB infection?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -574,7 +589,7 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.778</v>
+        <v>0.667</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -582,61 +597,69 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>0.7160155773162842</v>
+        <v>0.4392675757408142</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1-IMAGE]
-Supporting Evidence:
-- The cardiac silhouette and mediastinum size are within normal limits. [R1]
-- There is no pulmonary edema. [R1]
-- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
-- Further evaluation may be necessary depending on the patient's symptoms and medical history. [Rx]</t>
-        </is>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6</v>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="n">
-        <v>2</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray shows no evidence of active TB infection, with normal lung fields, cardiac silhouette, and no signs of pleural effusion or pneumothorax [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The cardiac silhouette and mediastinum size are within normal limits, with no pulmonary edema, focal consolidation, or pleural effusion [R1].
+- The chest X-ray shows normal lung fields, a normal cardiac silhouette, and no evidence of active TB infection, with clear pleura, sharp costophrenic angles, and no mediastinal widening or diaphragmatic elevation [R1-IMAGE].
+Differential Considerations:
+- Primary: TB infection is unlikely given the normal chest X-ray findings and negative text report evidence [R1].
+- Alternative: Other pulmonary or cardiac conditions could be considered, but the evidence does not support this at this time [R2].</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>0.633</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8260046731948852</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.7295023365974427</v>
-      </c>
-      <c r="U2" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5479535151481629</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6524767575740815</v>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W2" t="n">
-        <v>2</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -648,7 +671,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Identify any abnormal findings on the chest X-ray.</t>
+          <t>Patient 2 is a preoperative bariatric surgery candidate. What cardiac and vascular findings are present on the chest X-ray, and are there any acute pulmonary abnormalities?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -666,69 +689,77 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>0.534568727016449</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
         <v>0.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ragas</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>0.5441363453865051</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- Borderline cardiomegaly detected. [R1]
-Supporting Evidence:
-- The chest X-ray shows borderline cardiomegaly, which is an enlargement of the heart. [R1]
-- Enlarged pulmonary arteries are also visible on the X-ray. [R1]
-- The lungs appear clear, indicating no visible signs of lung disease. [R1]
-Next Steps / Recommendations:
-- Clinical correlation with the patient's history and symptoms is recommended to further evaluate the significance of the borderline cardiomegaly. [Rx]
-- Further evaluation with echocardiography or other diagnostic tests may be necessary to assess cardiac function and determine the cause of the borderline cardiomegaly. [Rx]</t>
-        </is>
-      </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="n">
-        <v>2</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Borderline cardiomegaly is present on the chest X-ray, but no acute pulmonary abnormalities are visible [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Borderline cardiomegaly is noted on the chest X-ray, which is a common finding in preoperative bariatric surgery candidates [R1].
+- No acute pulmonary abnormalities are visible on the chest X-ray, which is consistent with the imaging findings [R1-IMAGE].
+Differential Considerations:
+- Primary: Cardiac enlargement due to obesity, which is a common finding in preoperative bariatric surgery candidates [R1].
+- Alternative: Pulmonary embolism or other acute pulmonary conditions are less likely given the absence of acute pulmonary abnormalities on the chest X-ray [R2].</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>0.576</v>
+        <v>1</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7032409036159516</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.6396204518079758</v>
-      </c>
-      <c r="U3" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T3" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5169137454032897</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.6474568727016449</v>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -740,7 +771,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show cardiomegaly or abnormal cardiac silhouette?</t>
+          <t>Patient 3 presented with right-sided rib pain after a fall. Does the chest X-ray show any rib fractures, pneumothorax, or pleural effusion?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -749,7 +780,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.6</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -758,7 +789,7 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -766,62 +797,69 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5670633316040039</v>
+        <v>0.7376003265380859</v>
       </c>
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1], [R2]
-Supporting Evidence:
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
-- The heart appears to be within normal size and shape in the image. [R1-IMAGE]
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
-- The heart appears to be within normal size and shape in the image. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show cardiomegaly or abnormal cardiac silhouette. [Rx]</t>
-        </is>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6</v>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="n">
-        <v>2</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any rib fractures, pneumothorax, or pleural effusion [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The patient's chest X-ray appears to be normal, with no visible rib fractures, pneumothorax, or pleural effusion [R1].
+- The lung fields, cardiac silhouette, pleura, costophrenic angles, mediastinum, and diaphragm all appear to be within normal limits on both chest X-rays [R1-IMAGE].
+Differential Considerations:
+- Primary: Rib contusion or strain given the patient's history of a fall and right-sided rib pain [R1].
+- Alternative: Pulmonary embolism or other pulmonary conditions are less likely given the normal chest X-ray findings [R2].</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5639999999999999</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7701189994812012</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.6670594997406005</v>
-      </c>
-      <c r="U4" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T4" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.7075200653076172</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.7627600326538087</v>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="W4" t="n">
-        <v>2</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="Z4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -833,7 +871,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Are there signs of pulmonary congestion or edema on the chest X-ray?</t>
+          <t>Patient 4 has a history of COPD. What does the chest X-ray reveal about the extent of emphysematous and fibrotic changes?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -851,7 +889,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.833</v>
+        <v>0.211</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -859,61 +897,69 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.7382009029388428</v>
+        <v>0.5017662048339844</v>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pulmonary congestion or edema detected. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R2-IMAGE]
-- The cardiomediastinal silhouette is normal in size and contour, which is consistent with no pulmonary congestion or edema. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess for other potential causes of symptoms. [Rx]
-- Further evaluation of the left lung apex for a cavitary lesion is recommended. [Rx]</t>
-        </is>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6</v>
       </c>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The patient has extensive emphysematous and fibrotic changes in both lung fields, consistent with chronic obstructive lung disease, [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The chest X-ray reveals diffuse bilateral interstitial and alveolar opacities consistent with chronic obstructive lung disease and bullous emphysema. [R1]
+- The chest X-ray shows extensive emphysematous and fibrotic changes in the patient's lungs, affecting the cardiac silhouette, pleura, costophrenic angles, mediastinum, diaphragm, and the entire lung parenchyma. [R1-IMAGE]
+Differential Considerations:
+- Primary: Chronic obstructive pulmonary disease (COPD) due to the presence of diffuse bilateral interstitial and alveolar opacities, emphysematous and fibrotic changes, and the patient's history of COPD. [R1]
+- Alternative: Pneumonia or other pulmonary infections could be considered, but the lack of mention of acute findings such as consolidation or cavitation in the text report and the presence of chronic changes on imaging make this less likely. [R2]</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
-        <v>0.531</v>
+        <v>1</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8546602708816529</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.6928301354408264</v>
-      </c>
-      <c r="U5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T5" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4236532409667969</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4918266204833984</v>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -925,7 +971,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Is pleural effusion visible on the chest X-ray?</t>
+          <t>Patient 5 presents with chest and nasal congestion. Is there any acute cardiopulmonary abnormality on the chest X-ray? Are there any chronic skeletal changes?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -934,7 +980,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -943,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.778</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -951,62 +997,69 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.691457211971283</v>
+        <v>0.638244092464447</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No pleural effusion detected on chest X-ray. [R1]
-Supporting Evidence:
-- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible anatomical findings related to pleural effusion. [R2-IMAGE]
-- The cardiomediastinal silhouette and pulmonary vasculature are within normal limits, which is consistent with the absence of pleural effusion. [R1]
-- There is no pneumothorax or pleural effusion, as stated in the radiology report. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely that pleural effusion will be detected. [Rx]</t>
-        </is>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6</v>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="n">
-        <v>2</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+There is no acute cardiopulmonary abnormality on the chest X-ray, but there is evidence of mild hyperexpansion of the lungs and biapical pleural thickening, which is unchanged from prior. [HIGH CONFIDENCE — supported by text report]
+Evidence Synthesis:
+- The cardiomediastinal silhouette and pulmonary vasculature are within normal limits, and there is no pneumothorax or pleural effusion. [R1]
+- The chest x-ray appears to be normal, with no acute cardiopulmonary abnormalities or chronic skeletal changes visible in the image. [R1-IMAGE]
+Differential Considerations:
+- Primary: Mild hyperexpansion of the lungs and biapical pleural thickening, likely due to chronic respiratory issues. [R1]
+- Alternative: Acute respiratory infection, but the lack of focal areas of consolidation and normal pulmonary vasculature makes this less likely. [R2]</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
-        <v>0.644</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8186371635913848</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.7313185817956924</v>
-      </c>
-      <c r="U6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T6" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.662</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.6276488184928894</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6448244092464448</v>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W6" t="n">
-        <v>2</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1018,7 +1071,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show lung consolidation or opacities?</t>
+          <t>Patient 6 is being evaluated for possible infection. Does the chest X-ray show any evidence of consolidation, pneumonia, or other acute cardiopulmonary findings?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1036,7 +1089,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.75</v>
+        <v>0.821</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1044,62 +1097,69 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6997577548027039</v>
+        <v>0.6876677870750427</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No lung consolidation or opacities detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE]
-- The chest X-ray does not show any lung consolidation or opacities. [R2-IMAGE]
-- Heart size and mediastinal contour are within normal limits on the chest X-ray. [R1]
-- Mild degenerative change of the thoracic spine is noted on the chest X-ray. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess for other potential causes of symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show lung consolidation or opacities. [Rx]</t>
-        </is>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.6</v>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any evidence of consolidation, pneumonia, or other acute cardiopulmonary findings. [HIGH CONFIDENCE — supported by text report]
+Evidence Synthesis:
+- Heart size and mediastinal contour are within normal limits, with no focal airspace consolidation or suspicious pulmonary opacity. [R1]
+- The chest x-ray appears to be normal, with no signs of infection or other abnormalities in the patient's lungs, heart, pleura, costophrenic angles, mediastinum, or diaphragm. [R1-IMAGE]
+Differential Considerations:
+- Primary: No acute cardiopulmonary findings are present, making an infectious process less likely. [R1]
+- Alternative: Although the chest X-ray is normal, it is essential to compare with prior chest films from [date] to assess interval change in cardiac silhouette size, as mild degenerative change of the thoracic spine was noted. [R1]</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>0.599</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8099273264408112</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.7044636632204055</v>
-      </c>
-      <c r="U7" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T7" t="b">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6438335574150085</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.6699167787075042</v>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W7" t="n">
-        <v>2</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1111,7 +1171,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Are there signs of pneumothorax on the chest X-ray?</t>
+          <t>Patient 7 is a preoperative lumbar surgery candidate. What does the chest X-ray show regarding lung fields and any incidental findings?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1129,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.625</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1137,61 +1197,69 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.4138781428337097</v>
+        <v>0.3132930994033813</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pneumothorax detected. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
-- The lungs are clear. [R1]
-- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended. [Rx]
-- Follow-up imaging if symptoms persist. [Rx]</t>
-        </is>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6</v>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="n">
-        <v>2</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The lungs appear to be clear and free of any visible abnormalities, with normal cardiac silhouette and no incidental findings, [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The lungs are clear with no visible abnormalities, as stated in the text report. [R1]
+- The chest x-ray shows normal lung fields with no incidental findings, as observed in the image. [R1-IMAGE]
+Differential Considerations:
+- Primary: Pulmonary Atelectasis is less likely given the clear lung fields on the chest x-ray and normal cardiac silhouette, as stated in the text report [R1].
+- Alternative: Pleural Effusion is less likely given the normal lung fields and no mention of fluid accumulation in the text report [R1].</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>0.468</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6909634428501129</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.5794817214250565</v>
-      </c>
-      <c r="U8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T8" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5101586198806762</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.5445793099403381</v>
+      </c>
+      <c r="X8" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>RETRY</t>
-        </is>
-      </c>
-      <c r="W8" t="n">
-        <v>2</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1203,7 +1271,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Summarize the key findings from the chest X-ray.</t>
+          <t>Patient 8 has a history of mitral valve prolapse and presents with dyspnea. Does the chest X-ray show any cardiomegaly, pulmonary edema, or pleural effusion?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1212,78 +1280,86 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>0.4549850821495056</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
         <v>0.6</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ragas</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>0.7059441804885864</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No significant pathologies detected above threshold. [R1]
-Supporting Evidence:
-- The heart, pulmonary structures, and mediastinum are within normal limits. [R1]
-- There is no pleural effusion or pneumothorax. [R1]
-- The chest X-ray shows no focal air space opacity to suggest a pneumonia. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
-- Follow-up imaging if symptoms persist, but no immediate indication for further imaging based on current findings. [Rx]</t>
-        </is>
-      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any cardiomegaly, pulmonary edema, or pleural effusion [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The heart, pulmonary fields, and mediastinum are within normal limits on the chest X-ray [R1].
+- The lung fields appear to be clear, the cardiac silhouette is normal, and there are no abnormalities in the pleura, costophrenic angles, mediastinum, or diaphragm on imaging [R1-IMAGE].
+Differential Considerations:
+- Primary: Mitral valve prolapse with no evidence of cardiac decompensation or pulmonary edema on chest X-ray [R1].
+- Alternative: Pulmonary embolism or other respiratory conditions that may cause dyspnea, but the chest X-ray does not support these diagnoses [R2].</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5649999999999999</v>
+        <v>1</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8317832541465761</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.6983916270732879</v>
-      </c>
-      <c r="U9" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T9" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5759970164299011</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6644985082149506</v>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1295,7 +1371,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Does the chest X-ray indicate heart enlargement?</t>
+          <t>Patient 9 presents with chest pain and a history of stent placement. What does the chest X-ray show, and what is the significance of the left cardiophrenic angle density?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1313,7 +1389,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1321,61 +1397,70 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6633126735687256</v>
+        <v>0.6667966842651367</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No heart enlargement detected. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The cardiac silhouette is not enlarged. [R1]
-- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE], [R2-IMAGE]
-- There is no consolidation, pleural effusion, or pneumothorax, which can sometimes be associated with heart enlargement. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential issues that may not be visible on the X-ray. [Rx]
-- Further evaluation may be needed to assess the patient's symptoms and determine the cause of chest pain. [Rx]</t>
-        </is>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray shows a calcified granuloma in the right upper lobe, and the left cardiophrenic angle density appears to be increased, which may indicate an issue or abnormality in that area. [HIGH CONFIDENCE — supported by text report]
+Evidence Synthesis:
+- The chest X-ray shows a calcified granuloma in the right upper lobe. [R1]
+- The left cardiophrenic angle density appears to be increased, which may indicate an issue or abnormality in that area. [R1-IMAGE]
+- Discordance Note: CNN detected Granuloma: 51.3% but text report states Calcified granuloma is again seen in the right upper lobe. [R1, R1-IMAGE]
+Differential Considerations:
+- Primary: Calcified granuloma in the right upper lobe, which is consistent with the patient's history and the chest X-ray findings. [R1]
+- Alternative: Left cardiophrenic angle density increase, which may be related to a variety of conditions, including pleural effusion or pneumothorax, but the chest X-ray does not show any consolidation, pleural effusion, or pneumothorax. [R2]</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>0.594</v>
+        <v>1</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8989938020706176</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.7464969010353089</v>
-      </c>
-      <c r="U10" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T10" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.5458593368530273</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6324296684265136</v>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W10" t="n">
-        <v>2</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1387,7 +1472,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Are the lung fields clear on the chest X-ray?</t>
+          <t>Patient 10 is a male presenting with chest pain. Does the chest X-ray show any acute cardiopulmonary process or significant pathology?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1396,7 +1481,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
@@ -1405,7 +1490,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>0.636</v>
+        <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1413,61 +1498,70 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6991814970970154</v>
+        <v>0.6422308087348938</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
-Supporting Evidence:
-- The lung fields are normally inflated without evidence of focal airspace disease, pleural effusion, or pneumothorax. [R1]
-- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
-- The chest x-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the lung fields. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying issues that may not be visible on the x-ray. [Rx]
-- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
-        </is>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6</v>
       </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1</v>
-      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any acute cardiopulmonary process or significant pathology [HIGH CONFIDENCE — supported by text report].
+- Alternative: Pulmonary embolism is less likely given the normal lung fields and absence of focal airspace disease on the chest X-ray [R2].
+Evidence Synthesis:
+- The cardiomediastinal silhouette is within normal limits for size and contour, and the lungs are normally inflated without evidence of focal airspace disease, pleural effusion, or pneumothorax [R1].
+- The chest x-ray appears to be normal, with no acute cardiopulmonary process or significant pathology visible in the lung fields, cardiac silhouette, pleura, costophrenic angles, mediastinum, and diaphragm [R1-IMAGE].
+Differential Considerations:
+- Primary: No acute abnormality identified based on available evidence. [R1]
+- Alternative: Insufficient evidence to exclude other diagnoses without additional imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>0.622</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7641544491291046</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.6930772245645522</v>
-      </c>
-      <c r="U11" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T11" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.6884461617469788</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6777230808734894</v>
+      </c>
+      <c r="X11" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W11" t="n">
-        <v>2</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1479,7 +1573,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Confirm whether the chest X-ray appears normal.</t>
+          <t>Patient 11 presents with fatigue, weakness, and anterior chest pain. What are the findings on the chest X-ray?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1488,7 +1582,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
@@ -1497,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>0.333</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1505,62 +1599,70 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.7799336314201355</v>
+        <v>0.3905929327011108</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1]
-Supporting Evidence:
-- Cardiomediastinal silhouette and pulmonary vasculature are within normal limits. [R1]
-- Lungs are clear. [R1]
-- No pneumothorax or pleural effusion. [R1]
-- No acute osseous findings. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
-- Further evaluation may be needed if symptoms persist. [Rx]</t>
-        </is>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The patient's chest X-ray shows an enlarged cardiac silhouette, bilateral diffuse reticular opacities in the lung fields, pleural [redacted], blunting of both costophrenic angles, and a widened mediastinum, which may be indicative of various conditions or abnormalities [MODERATE CONFIDENCE — partial text support, supplemented by imaging].
+Evidence Synthesis:
+- The chest X-ray shows clear lungs, a normal cardiac silhouette, and no pleural [redacted] or abnormalities in the costophrenic angles, which are consistent with the patient's clinical presentation of fatigue, weakness, and anterior chest pain [R2].
+- Based on imaging only (limited confidence): The chest x-ray shows several findings, including bilateral diffuse reticular opacities in the lung fields, an enlarged cardiac silhouette, pleural [redacted], blunting of both costophrenic angles, and a widened mediastinum [R1-IMAGE].
+- Discordance Note: CNN detected no pathologies above threshold but text report suggests several abnormalities, including pleural [redacted] and blunting of costophrenic angles [R1, R1-IMAGE].
+Differential Considerations:
+- Primary: Cardiomyopathy or congestive heart failure given the enlarged cardiac silhouette and bilateral diffuse reticular opacities in the lung fields [R1].
+- Alternative: Pulmonary embolism or pneumonia could be considered, but the clear lungs on the second X-ray and lack of CNN detection make this less likely [R2].</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>0.617</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8139800894260406</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.7154900447130204</v>
-      </c>
-      <c r="U12" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T12" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.4780185865402222</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.5705092932701111</v>
+      </c>
+      <c r="X12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W12" t="n">
-        <v>2</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1572,7 +1674,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Identify any abnormal findings on the chest X-ray.</t>
+          <t>Patient 12 had a chest X-ray performed. Are there any abnormal findings in the lungs, heart, or mediastinum?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1581,7 +1683,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1590,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.875</v>
+        <v>0.846</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1598,63 +1700,70 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8339194059371948</v>
+        <v>0.5029357075691223</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No abnormal findings detected on the chest X-ray. [R1]
-Supporting Evidence:
-- Lungs are clear bilaterally. [R1]
-- Cardiac and mediastinal silhouettes are normal. [R1]
-- Pulmonary vasculature is normal. [R1]
-- No pneumothorax or pleural effusion. [R1]
-- No acute bony abnormality. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to rule out conditions not visible on chest X-ray. [Rx]
-- Follow-up imaging if symptoms persist or clinical history suggests underlying condition. [Rx]</t>
-        </is>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="n">
-        <v>2</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The lungs, heart, and mediastinum appear normal on chest X-ray, with no visible abnormalities [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Lungs are clear bilaterally, and pulmonary vasculature is normal [R1].
+- Cardiac and mediastinal silhouettes are normal, with no pneumothorax or pleural effusion [R1].
+- Discordance Note: CNN detected no pathologies above threshold, but imaging suggests a normal chest X-ray [R1, R1-IMAGE].
+Differential Considerations:
+- Primary: Normal chest X-ray, with no acute bony abnormality or other concerning features [R1].
+- Alternative: Pneumonia or other pulmonary pathology could be present, but evidence does not support this at this time [R2].</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>0.659</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9001758217811584</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0.7795879108905792</v>
-      </c>
-      <c r="U13" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T13" t="b">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.6543871415138244</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.6666935707569122</v>
+      </c>
+      <c r="X13" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W13" t="n">
-        <v>2</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1666,7 +1775,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show cardiomegaly or abnormal cardiac silhouette?</t>
+          <t>Patient 13 presents with chest pain. Is there any cardiomegaly or acute pulmonary disease on the chest X-ray?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1675,7 +1784,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
@@ -1684,7 +1793,7 @@
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3</v>
+        <v>0.286</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1692,62 +1801,70 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8635129332542419</v>
+        <v>0.4162360429763794</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No cardiomegaly or abnormal cardiac silhouette detected. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any signs of cardiomegaly. [R1-IMAGE]
-- The mediastinal contours are within normal limits. [R1]
-- There is no large pleural effusion or pneumothorax. [R1]
-- The cardiac silhouette is borderline enlarged, but this is not a definitive indicator of cardiomegaly. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
-        </is>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>2</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Cardiomegaly is ABSENT [HIGH CONFIDENCE — supported by text report]. [R1]
+Evidence Synthesis:
+- The cardiac silhouette is borderline enlarged, but no focal opacity is noted, and mediastinal contours are within normal limits [R1].
+- The chest x-ray does not show any signs of cardiomegaly or acute pulmonary disease, with clear lung fields and normal costophrenic angles [R1-IMAGE].
+- Discordance Note: CNN detected Emphysema at 49.1% but text report states no acute pulmonary disease [R2, R1-IMAGE].
+Differential Considerations:
+- Primary: Acute pulmonary disease is unlikely given the clear lung fields and normal costophrenic angles on the chest x-ray [R1].
+- Alternative: Cardiomegaly could be considered if the patient's symptoms persist, but the borderline enlarged cardiac silhouette on the chest radiograph is not definitive evidence [R1].</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>0.726</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6790538799762725</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.7025269399881362</v>
-      </c>
-      <c r="U14" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T14" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.4690472085952759</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.5260236042976379</v>
+      </c>
+      <c r="X14" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>RETRY</t>
-        </is>
-      </c>
-      <c r="W14" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1759,7 +1876,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Are there signs of pulmonary congestion or edema on the chest X-ray?</t>
+          <t>Patient 14 is a female presenting with chest pain. Are there signs of pulmonary edema, hyperinflation, or acute findings on the chest X-ray?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1768,7 +1885,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
@@ -1777,7 +1894,7 @@
         <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0.75</v>
+        <v>0.917</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1785,62 +1902,70 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8714293837547302</v>
+        <v>0.385119765996933</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pulmonary congestion or edema detected on the chest X-ray. [R1], [R2]
-Supporting Evidence:
-- The chest x-ray shows heart size within normal limits, stable mediastinal and hilar contours. [R1]
-- Mild hyperinflation appears similar to prior, with no focal alveolar consolidation or definite pleural effusion seen. [R1]
-- Scattered chronic appearing irregular interstitial markings are present, but no typical findings of pulmonary edema are observed. [R1]
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE], [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current chest X-ray findings, it does not appear necessary. [Rx]</t>
-        </is>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6</v>
       </c>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Pulmonary edema is ABSENT [HIGH CONFIDENCE — supported by text report].
+- Alternative: Pulmonary embolism is less likely given the absence of focal alveolar consolidation or pleural effusion, and the normal cardiac silhouette [R2].
+Evidence Synthesis:
+- Mild hyperinflation appears similar to prior, with no focal alveolar consolidation or definite pleural effusion seen [R1].
+- The chest x-ray shows no signs of pulmonary edema, hyperinflation, or acute findings, with normal lung fields and no visible abnormalities [R1-IMAGE].
+Differential Considerations:
+- Primary: No acute abnormality identified based on available evidence. [R1]
+- Alternative: Insufficient evidence to exclude other diagnoses without additional imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8614288151264191</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0.7657144075632096</v>
-      </c>
-      <c r="U15" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T15" t="b">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.756</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6121239531993867</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6840619765996934</v>
+      </c>
+      <c r="X15" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W15" t="n">
-        <v>2</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1852,7 +1977,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Is pleural effusion visible on the chest X-ray?</t>
+          <t>Patient 15 presents with dyspnea. Is there any pleural effusion, consolidation, or evidence of granulomatous disease on the chest X-ray?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1861,7 +1986,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1870,7 +1995,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.429</v>
+        <v>0.5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1878,62 +2003,69 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.5505229830741882</v>
+        <v>0.4324659109115601</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No visible pleural effusion detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible signs of pleural effusion. [R2-IMAGE]
-- The absence of visible pleural effusion in a chest x-ray does not necessarily rule out the presence of fluid accumulation in the pleural space. [R1-IMAGE]
-- Further diagnostic tests, such as a chest CT scan or ultrasound, may be needed to confirm the presence or absence of pleural effusion. [R1-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the presence of pleural effusion despite negative chest X-ray findings. [Rx]
-- Follow-up imaging with a chest CT scan or ultrasound if symptoms persist or worsen. [Rx]</t>
-        </is>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6</v>
       </c>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="n">
-        <v>2</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+There is no pleural effusion, consolidation, or evidence of granulomatous disease on the chest X-ray [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The chest X-ray shows no pleural effusion, consolidation, or evidence of granulomatous disease [R1].
+- The lung fields appear to be clear, and there is no cardiac silhouette enlargement, with sharp costophrenic angles and a normal mediastinum [R1-IMAGE].
+Differential Considerations:
+- Primary: Pulmonary granulomatosis is less likely given the absence of granulomatous disease on the chest X-ray [R1].
+- Alternative: Other causes of dyspnea such as asthma or chronic obstructive pulmonary disease (COPD) could be considered, but the chest X-ray does not support these diagnoses [R2].</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
         <v>2</v>
       </c>
       <c r="R16" t="n">
-        <v>0.573</v>
+        <v>1</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6367568949222565</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.6048784474611282</v>
-      </c>
-      <c r="U16" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T16" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.496493182182312</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.566246591091156</v>
+      </c>
+      <c r="X16" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>RETRY</t>
-        </is>
-      </c>
-      <c r="W16" t="n">
-        <v>2</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -1945,7 +2077,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show lung consolidation or opacities?</t>
+          <t>Patient 16 has limited clinical information available. What can be determined from the available imaging and dataset records?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1976,56 +2108,63 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-No pathologies detected above threshold on the chest X-ray. [R1]
-Supporting Evidence:
-- The DenseNet CNN algorithm used for pathology detection did not identify any abnormalities above the set threshold. [R1]
-- The absence of pathologies detected by the algorithm suggests that the chest X-ray is likely normal or shows no significant abnormalities. [R2]
-- However, it is essential to note that the absence of findings on a chest X-ray does not rule out the presence of lung consolidation or opacities, especially if they are mild or not severe enough to be detected by the algorithm. [R3]
-Next Steps / Recommendations:
-- Clinical correlation with the patient's symptoms and medical history is recommended to determine the significance of the normal chest X-ray findings. [Rx]
-- If the patient's symptoms persist or worsen, follow-up imaging may be necessary to rule out any underlying conditions. [Rx]</t>
-        </is>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.7</v>
       </c>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2</v>
-      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+No pathologies detected in the lungs above threshold by CNN, but the text report is limited [LOW CONFIDENCE].
+Evidence Synthesis:
+- No mention of any pathologies in the text report [R1].
+- Based on imaging only (limited confidence): No pathologies detected in the lungs above threshold by CNN [R1-IMAGE].
+Differential Considerations:
+- Primary: Pulmonary embolism is unlikely given the lack of text report findings and CNN results [R1].</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="U17" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="X17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2037,7 +2176,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Are there signs of pneumothorax on the chest X-ray?</t>
+          <t>Patient 17 is a female presenting with chest pain. Does the chest X-ray demonstrate any pulmonary opacities, pleural effusion, or cardiomegaly?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2055,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>0.917</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2063,62 +2202,69 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7941926717758179</v>
+        <v>0.501488208770752</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pneumothorax detected on the chest X-ray. [R1], [R2]
-Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
-- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
-- No focal areas of consolidation or suspicious pulmonary opacities were observed on the chest X-ray. [R1]
-- Heart size and osseous structures are within normal limits on the chest X-ray. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but no immediate indication for further imaging at this time. [Rx]</t>
-        </is>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6</v>
       </c>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="n">
-        <v>2</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
-      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not demonstrate any pulmonary opacities, pleural effusion, or cardiomegaly [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- No focal areas of consolidation or suspicious pulmonary opacities are present on the chest X-ray, as per the text report [R1].
+- The chest X-ray appears to be normal, with no visible pulmonary opacities, pleural effusions, or cardiomegaly, as per imaging [R1-IMAGE].
+Differential Considerations:
+- Primary: The patient's chest pain is likely due to a non-cardiac cause, given the absence of any abnormalities on the chest X-ray [R1].
+- Alternative: The patient's chest pain could be related to a musculoskeletal issue, given the lack of any radiographic evidence of cardiac or pulmonary pathology [R2].</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>0.774</v>
+        <v>1</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9382578015327453</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0.8561289007663726</v>
-      </c>
-      <c r="U18" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.6353976417541505</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.7071988208770752</v>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W18" t="n">
-        <v>2</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2130,7 +2276,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Summarize the key findings from the chest X-ray.</t>
+          <t>Patient 18 is a male presenting with pain. Is there any evidence of pleural effusion or acute cardiopulmonary pathology on the chest X-ray?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2139,7 +2285,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
@@ -2148,7 +2294,7 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0.75</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2156,62 +2302,69 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8006788492202759</v>
+        <v>0.7006397247314453</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No significant pathologies detected above threshold. [R1], [R2]
-Supporting Evidence:
-- Heart size within normal limits. [R1]
-- No focal alveolar consolidation, no definite pleural effusion seen. [R1]
-- No typical findings of pulmonary edema. [R1]
-- No pneumothorax. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended. [Rx]
-- Insufficient evidence [Rx]</t>
-        </is>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.6</v>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>2</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+There is no evidence of pleural effusion or acute cardiopulmonary pathology on the chest X-ray. [HIGH CONFIDENCE — supported by text report]
+Evidence Synthesis:
+- The chest X-ray shows no focal alveolar consolidation, no definite pleural effusion, and no typical findings of pulmonary edema. [R1]
+- The chest x-ray appears to be normal, with no evidence of pleural [redacted] or acute cardiopulmonary pathology. [R1-IMAGE]
+Differential Considerations:
+- Primary: Normal chest X-ray findings are consistent with the patient's presentation of pain, and there is no indication of underlying cardiopulmonary pathology. [R1]
+- Alternative: Although the patient presents with pain, the absence of any abnormal findings on the chest X-ray makes other diagnoses such as pleural effusion or acute cardiopulmonary pathology less likely. [R2]</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>0.612</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8402036547660828</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0.7261018273830414</v>
-      </c>
-      <c r="U19" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.6077279449462891</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.6923639724731445</v>
+      </c>
+      <c r="X19" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>2</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2223,7 +2376,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Does the chest X-ray indicate heart enlargement?</t>
+          <t>Patient 19 is a preoperative candidate for abdominal aortic aneurysm repair. What does the chest X-ray show about the thoracic aorta and lung fields?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2232,79 +2385,86 @@
         </is>
       </c>
       <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0.3653049468994141</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
         <v>0.6</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ragas</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>0.5567283630371094</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No heart enlargement detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest x-ray appears to be normal. [R2-IMAGE]
-- A chest X-ray is a standard tool for assessing heart size, but it may not always detect subtle abnormalities. [R1]
-- Further evaluation may be needed to assess the patient's overall cardiovascular health. [R2]
-Next Steps / Recommendations:
-- Clinical correlation with other diagnostic tests (e.g., ECG, echocardiogram) is recommended to confirm the absence of heart enlargement. [Rx]
-- Follow-up imaging if symptoms persist or if there is a change in clinical status. [Rx]</t>
-        </is>
-      </c>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1</v>
-      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The thoracic aorta shows tortuosity, which is stable compared to prior, and there is no focal airspace disease or effusion, but the lung fields appear normal [HIGH CONFIDENCE — supported by text report]. [R1]
+Evidence Synthesis:
+- The chest X-ray shows normal lung fields, a normal cardiac silhouette, and no pleural abnormalities or abnormalities in the costophrenic angles, with a normal mediastinum and no diaphragmatic hernia visible [R1-IMAGE].
+- Insufficient evidence to determine the presence of pleural effusions or pneumothoraces [Rx].
+Differential Considerations:
+- Primary: Stable thoracic aorta tortuosity, which is consistent with the patient's preoperative status for abdominal aortic aneurysm repair, and normal lung fields [R1].
+- Alternative: Pulmonary embolism or other acute respiratory conditions are less likely given the normal lung fields and absence of focal airspace disease or effusion on the chest X-ray [R2].</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q20" t="n">
         <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>0.605</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6446185089111328</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0.6248092544555663</v>
-      </c>
-      <c r="U20" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.5016609893798829</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.6013304946899414</v>
+      </c>
+      <c r="X20" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>RETRY</t>
-        </is>
-      </c>
-      <c r="W20" t="n">
-        <v>2</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2316,7 +2476,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Are the lung fields clear on the chest X-ray?</t>
+          <t>Patient 20 is a female who had a chest X-ray. Are the cardiac and mediastinal silhouettes normal and are the lung fields clear?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2334,7 +2494,7 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2342,62 +2502,69 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6545675992965698</v>
+        <v>0.5420539379119873</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
-Supporting Evidence:
-- The lungs are well expanded and clear. [R1]
-- The lung fields appear to be clear on the chest x-ray. [R1-IMAGE]
-- There are no focal air space opacities. [R1]
-- The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to rule out underlying conditions. [Rx]
-- Further evaluation may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
-        </is>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6</v>
       </c>
       <c r="M21" t="inlineStr"/>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>1</v>
-      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The cardiac and mediastinal silhouettes are unremarkable and the lung fields are clear [HIGH CONFIDENCE — supported by text report] [R1].
+Evidence Synthesis:
+- The lungs are well expanded and clear, with no focal air space opacities, pneumothorax, or effusion [R1].
+- The cardiac and mediastinal silhouettes are unremarkable on imaging [R1-IMAGE].
+Differential Considerations:
+- Primary: Normal chest radiograph findings, consistent with the patient's clinical presentation [R1].
+- Alternative: Pneumonia or other pulmonary pathology could be considered if symptoms persist or worsen, but the current evidence does not support this [R2].</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>0.619</v>
+        <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8963702797889709</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.7576851398944855</v>
-      </c>
-      <c r="U21" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.6183107875823974</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.7136553937911987</v>
+      </c>
+      <c r="X21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W21" t="n">
-        <v>2</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2409,7 +2576,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Confirm whether the chest X-ray appears normal.</t>
+          <t>Patient 21 presented with confusion and possible head injury. What does the chest X-ray show incidentally regarding cardiac, lung, and bony findings?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2418,7 +2585,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
@@ -2427,7 +2594,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.364</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2435,63 +2602,69 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4528967440128326</v>
+        <v>0.6048868894577026</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1-IMAGE]
-- The chest X-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. This is consistent with the patient's clinical presentation and the absence of any significant findings on the chest X-ray. [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray appears to be normal, which means that there are no visible abnormalities or signs of disease in the image. [R1-IMAGE]
-- The chest X-ray appears to be normal, which means that there are no visible signs of abnormalities or issues in the image. [R2-IMAGE]
-- A normal chest x-ray does not necessarily rule out all possible conditions or issues, but it is a reassuring finding that can help guide further evaluation and clinical correlation. [R1-IMAGE]
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying concerns. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
-        </is>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.6</v>
       </c>
       <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1</v>
-      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray shows normal cardiac silhouette, lung fields, and no abnormalities in the pleura or costophrenic angles, with a normal mediastinum and no evidence of diaphragmatic hernia [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The chest X-ray shows normal lung fields, a normal cardiac silhouette, and no abnormalities in the pleura or costophrenic angles, with a normal mediastinum and no evidence of diaphragmatic hernia [R1].
+- The chest X-ray findings are considered incidental, meaning they were discovered during the imaging process but may not be directly related to the patient's presenting symptoms or condition [R1-IMAGE].
+Differential Considerations:
+- Primary: The patient's confusion and possible head injury are the primary concern, and the chest X-ray findings are incidental [R1].
+- Alternative: The patient's chest X-ray findings do not suggest any alternative diagnoses that would explain the patient's symptoms [NO TEXT REPORT AVAILABLE]. [R1]</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
         <v>2</v>
       </c>
       <c r="R22" t="n">
-        <v>0.593</v>
+        <v>1</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4358690232038498</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0.5144345116019249</v>
-      </c>
-      <c r="U22" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.4901773778915405</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.5670886889457702</v>
+      </c>
+      <c r="X22" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="W22" t="n">
-        <v>2</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="Z22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2503,7 +2676,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Identify any abnormal findings on the chest X-ray.</t>
+          <t>Patient 22 is a woman with symptoms lasting 3 weeks. Does the chest X-ray show any pulmonary or cardiac abnormality?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2521,7 +2694,7 @@
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.667</v>
+        <v>0.733</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2529,61 +2702,69 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.76126629114151</v>
+        <v>0.576751708984375</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No abnormal findings detected on the chest X-ray. [R1]
-Supporting Evidence:
-- The lungs are clear, and without focal air space opacity. [R1]
-- The cardiomediastinal silhouette is normal in size and contour, and stable. [R1]
-- The chest X-ray appears to be normal, with no visible abnormalities. [R1-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
-- Follow-up imaging if symptoms persist, but currently, there is no indication for further imaging. [Rx]</t>
-        </is>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.6</v>
       </c>
       <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>2</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1</v>
-      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any pulmonary or cardiac abnormality [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The lungs are clear, and without focal air space opacity, according to the text report [R1].
+- The chest x-ray appears to be normal, with no visible pulmonary or cardiac abnormalities in the lung fields, cardiac silhouette, pleura, costophrenic angles, mediastinum, and diaphragm [R1-IMAGE].
+Differential Considerations:
+- Primary: Normal chest X-ray, consistent with the patient's symptoms being non-specific or due to a non-respiratory cause [R1].
+- Alternative: Pulmonary or cardiac abnormality not visible on the chest X-ray, but could be present and not detected by imaging [R2].</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>0.637</v>
+        <v>1</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7951798873424529</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.7160899436712265</v>
-      </c>
-      <c r="U23" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.5952503417968751</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.6331251708984376</v>
+      </c>
+      <c r="X23" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W23" t="n">
-        <v>2</v>
-      </c>
-      <c r="X23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2595,7 +2776,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show cardiomegaly or abnormal cardiac silhouette?</t>
+          <t>Patient 23 presents with nausea, vomiting, and is a preoperative candidate. Is there any active pulmonary disease on the chest X-ray?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2604,7 +2785,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
@@ -2613,7 +2794,7 @@
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2621,63 +2802,68 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.632602334022522</v>
+        <v>0.5068638324737549</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE]
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R2-IMAGE]
-Supporting Evidence:
-- The heart size appears within normal limits on the chest x-ray. [R1]
-- The lungs are free of focal airspace disease, indicating no acute abnormality. [R1]
-- The chest x-ray does not show any signs of pleural effusion or pneumothorax. [R1]
-- The pulmonary vascularity appears within normal limits on the chest x-ray. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but based on the current chest X-ray, no immediate indication for further imaging. [Rx]</t>
-        </is>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6</v>
       </c>
       <c r="M24" t="inlineStr"/>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Active pulmonary disease is ABSENT [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The heart size and pulmonary vascularity appear within normal limits, and the lungs are free of focal airspace disease [R1].
+- The chest x-ray appears to be normal, with no active pulmonary disease visible in the image [R1-IMAGE].
+Differential Considerations:
+- Primary: Pulmonary disease is unlikely given the normal chest x-ray findings and absence of symptoms suggestive of active pulmonary disease [R1].</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R24" t="n">
-        <v>0.473</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7897807002067567</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.6313903501033784</v>
-      </c>
-      <c r="U24" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.6613727664947511</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.6466863832473755</v>
+      </c>
+      <c r="X24" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W24" t="n">
-        <v>2</v>
-      </c>
-      <c r="X24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2689,7 +2875,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Are there signs of pulmonary congestion or edema on the chest X-ray?</t>
+          <t>Patient 24 presents with dyspnea. Does the chest X-ray show pulmonary edema, consolidation, or any acute cardiopulmonary abnormality?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2698,7 +2884,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
@@ -2707,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.833</v>
+        <v>0.909</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2715,61 +2901,69 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5938956737518311</v>
+        <v>0.3969992995262146</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
-- The lungs are expanded and clear of airspace disease. [R1]
-- There is no visible abnormality in the lungs that would indicate fluid accumulation or swelling. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms of dyspnea. [Rx]
-- Follow-up imaging if symptoms persist, but based on current evidence, it is unlikely to show signs of pulmonary congestion or edema. [Rx]</t>
-        </is>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6</v>
       </c>
       <c r="M25" t="inlineStr"/>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
-      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Pulmonary edema is ABSENT [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Cardiomediastinal silhouette is within normal limits of size and appearance, and lungs are expanded and clear of airspace disease [R1].
+- The chest X-ray does not show any acute cardiopulmonary abnormalities such as pulmonary edema, consolidation, or any other signs of acute respiratory distress syndrome (ARDS) [R1-IMAGE].
+Differential Considerations:
+- Primary: Dyspnea due to possible respiratory muscle fatigue or other non-cardiopulmonary causes [R1].
+- Alternative: Acute respiratory distress syndrome (ARDS) is less likely given the normal lung fields and clear airspace disease on the chest X-ray [R1].</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R25" t="n">
-        <v>0.55</v>
+        <v>1</v>
       </c>
       <c r="S25" t="n">
-        <v>0.8113687021255493</v>
-      </c>
-      <c r="T25" t="n">
-        <v>0.6806843510627747</v>
-      </c>
-      <c r="U25" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.612099859905243</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.6175499299526215</v>
+      </c>
+      <c r="X25" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W25" t="n">
-        <v>2</v>
-      </c>
-      <c r="X25" t="inlineStr">
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2781,7 +2975,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Is pleural effusion visible on the chest X-ray?</t>
+          <t>Patient 25 is an oxygen-dependent smoker with pulmonary emphysema. What does the chest X-ray show regarding emphysema severity, pleural effusions, and airspace disease?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2799,7 +2993,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.545</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2807,61 +3001,70 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5254111886024475</v>
+        <v>0.6279433965682983</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- Pleural effusion is not visible on the chest X-ray, but further imaging techniques such as CT scans may be needed for a more accurate assessment. [R1-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any visible pleural effusion. [R1-IMAGE]
-- A chest x-ray may not always detect subtle or small amounts of pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible pleural effusion. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the presence of pleural effusion. [Rx]
-- Follow-up imaging with CT scan if symptoms persist or if pleural effusion is suspected. [Rx]</t>
-        </is>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
       </c>
       <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>2</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Pleural effusions are present, and airspace disease is present, but emphysema severity is difficult to assess due to hyperinflation of the lungs [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Moderate left pleural effusion and small right pleural effusion are present, as indicated by the text report. [R1]
+- Airspace disease is not evident in the chest X-ray image, but pleural effusions are visible. [R1-IMAGE]
+- Discordance Note: CNN detected Pulmonary Atelectasis at 48.2% but text report does not mention it. [R1, R1-IMAGE]
+Differential Considerations:
+- Primary: Pulmonary emphysema with pleural effusions and airspace disease, as suggested by the combination of clinical history, imaging findings, and text report. [R1]
+- Alternative: Pneumonia or other infectious process, which could be considered less likely given the lack of mention of atelectasis in the text report and the presence of airspace disease. [R2]</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
         <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>0.599</v>
+        <v>1</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4576233565807343</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0.5283116782903672</v>
-      </c>
-      <c r="U26" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.5890886793136597</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.6420443396568298</v>
+      </c>
+      <c r="X26" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="W26" t="n">
-        <v>2</v>
-      </c>
-      <c r="X26" t="inlineStr">
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2873,7 +3076,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show lung consolidation or opacities?</t>
+          <t>Patient 26 had a chest X-ray. Are there any acute pulmonary or cardiac findings? Are there any skeletal abnormalities?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2882,79 +3085,86 @@
         </is>
       </c>
       <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
         <v>0.8</v>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.444</v>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>ragas</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6798410415649414</v>
+        <v>0.5567870736122131</v>
       </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No lung consolidation or opacities detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE]
-- The chest X-ray does not show any lung consolidation or opacities. [R2-IMAGE]
-- The lungs are clear on the X-ray. [R1]
-- The cardiac contours are normal, and thoracic spondylosis is present, but these findings are not relevant to the question of lung consolidation or opacities. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the presence of symptoms or other clinical findings that may be related to thoracic spondylosis. [Rx]
-- No further imaging is recommended at this time, but follow-up imaging may be necessary if symptoms persist or worsen. [Rx]</t>
-        </is>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.6</v>
       </c>
       <c r="M27" t="inlineStr"/>
-      <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1</v>
-      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+No acute pulmonary or cardiac findings are present [HIGH CONFIDENCE — supported by text report]. [R1]
+Evidence Synthesis:
+- The cardiac contours are normal, and the lungs are clear, indicating no acute pulmonary or cardiac findings. [R1]
+- Thoracic spondylosis is noted on the chest X-ray, suggesting a skeletal abnormality. [R1]
+Differential Considerations:
+- Primary: Thoracic spondylosis, as it is directly supported by the chest X-ray findings. [R1]
+- Alternative: Pulmonary embolism or cardiac disease, but these are less likely given the normal cardiac contours and clear lungs on the chest X-ray. [R2]</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q27" t="n">
         <v>2</v>
       </c>
       <c r="R27" t="n">
-        <v>0.541</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6815523124694824</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0.6112761562347413</v>
-      </c>
-      <c r="U27" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.6113574147224425</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.6291787073612213</v>
+      </c>
+      <c r="X27" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr">
+      <c r="Y27" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="W27" t="n">
-        <v>2</v>
-      </c>
-      <c r="X27" t="inlineStr">
+      <c r="Z27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -2966,7 +3176,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Are there signs of pneumothorax on the chest X-ray?</t>
+          <t>Patient 27 has a chronic pulmonary condition. What does the chest X-ray show about the degree of hyperexpansion and diaphragmatic changes?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2992,62 +3202,69 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.704419732093811</v>
+        <v>0.6098130941390991</v>
       </c>
       <c r="J28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pneumothorax detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
-- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
-- Lungs are overall hyperexpanded with flattening of the diaphragms, which is consistent with chronic obstructive pulmonary disease (COPD) but does not indicate pneumothorax. [R1]
-- No focal consolidation, pleural effusions, or pneumothoraces are present on the chest x-ray. [R1]
-Next Steps / Recommendations:
-- Clinical correlation with patient symptoms and medical history is recommended. [Rx]
-- Follow-up imaging if symptoms persist or worsen. [Rx]</t>
-        </is>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.6</v>
       </c>
       <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>2</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1</v>
-      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The patient has chronic pulmonary hyperexpansion and diaphragmatic changes, which are consistent with their chronic pulmonary condition [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The lungs are overall hyperexpanded with flattening of the diaphragms, indicating chronic pulmonary hyperexpansion [R1].
+- The chest X-ray shows clear lung fields with no visible signs of infection or other abnormalities, and the cardiac silhouette is normal [R1-IMAGE].
+Differential Considerations:
+- Primary: Chronic obstructive pulmonary disease (COPD) given the patient's history of chronic pulmonary condition and radiographic evidence of hyperexpansion and diaphragmatic changes [R1].
+- Alternative: Pneumonia or other acute respiratory conditions are less likely given the clear lung fields and absence of focal consolidation on the chest X-ray [R2].</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5629999999999999</v>
+        <v>1</v>
       </c>
       <c r="S28" t="n">
-        <v>0.8541259196281433</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0.7085629598140717</v>
-      </c>
-      <c r="U28" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.704</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.6390626188278199</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.6715313094139099</v>
+      </c>
+      <c r="X28" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W28" t="n">
-        <v>2</v>
-      </c>
-      <c r="X28" t="inlineStr">
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3059,7 +3276,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Summarize the key findings from the chest X-ray.</t>
+          <t>Patient 28 presents with shortness of breath and has bilateral pulmonary opacities. What is the current status and has there been any interval change compared to prior?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3068,7 +3285,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -3077,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.333</v>
+        <v>0.556</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3085,61 +3302,70 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6758285760879517</v>
+        <v>0.5651587247848511</v>
       </c>
       <c r="J29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- Cardiomegaly and bilateral pleural effusions are present. [R2-IMAGE]
-Supporting Evidence:
-- Cardiomegaly is an enlargement of the heart. [R2-IMAGE]
-- Bilateral pleural effusions are abnormal accumulations of fluid in the pleural space surrounding both lungs. [R2-IMAGE]
-- A left-sided pneumothorax is a collection of air or gas in the pleural space that can cause the lung to collapse. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to determine the cause of cardiomegaly and pleural effusions. [Rx]
-- Follow-up imaging if symptoms persist to assess for any changes in the patient's condition. [Rx]</t>
-        </is>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
       </c>
       <c r="M29" t="inlineStr"/>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The patient has bilateral pulmonary opacities, which are consistent with the symptoms of shortness of breath, but there has been no interval change compared to prior imaging [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Bilateral patchy pulmonary opacities noted, consistent with patient's symptoms of shortness of breath [R1].
+- No interval change in bilateral pulmonary opacities compared to prior imaging [R1-IMAGE].
+- Discordance Note: CNN detected Pleural Effusion at 71.3% but text report states "No large pleural effusions" [R1, R1-IMAGE].
+Differential Considerations:
+- Primary: Bilateral pulmonary opacities, likely due to pulmonary congestion and vascular congestion noted in the text report [R1].
+- Alternative: Pneumothorax is less likely given the absence of this finding in the text report [R2].</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q29" t="n">
         <v>2</v>
       </c>
       <c r="R29" t="n">
-        <v>0.533</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
-        <v>0.6359485728263855</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0.5844742864131928</v>
-      </c>
-      <c r="U29" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.5798317449569702</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.5999158724784851</v>
+      </c>
+      <c r="X29" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr">
+      <c r="Y29" t="inlineStr">
         <is>
           <t>RETRY</t>
         </is>
       </c>
-      <c r="W29" t="n">
-        <v>2</v>
-      </c>
-      <c r="X29" t="inlineStr">
+      <c r="Z29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA29" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3151,7 +3377,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Does the chest X-ray indicate heart enlargement?</t>
+          <t>Patient 29 presents with hypoxia and has a tracheostomy in situ. What does the chest X-ray show regarding cardiac size, diaphragm, and lung fields?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3160,7 +3386,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
@@ -3169,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.556</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3177,61 +3403,69 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.4739030599594116</v>
+        <v>0.5332908034324646</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- Insufficient evidence [R1], [R2] to confirm or rule out heart enlargement.
-Supporting Evidence:
-- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE]
-- The chest X-ray appears to be normal, with no visible abnormalities or issues related to the heart. [R1-IMAGE]
-- The chest X-ray does not show any signs of heart enlargement. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and medical history. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
-        </is>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.6</v>
       </c>
       <c r="M30" t="inlineStr"/>
-      <c r="N30" t="n">
-        <v>2</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
-      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The cardiac silhouette is normal in size, and there is no evidence of diaphragmatic hernia or other abnormalities [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The chest X-ray shows normal lung fields, a normal cardiac silhouette, and normal pleura [R1].
+- The chest X-ray also shows normal lung fields, a normal cardiac silhouette, and no pleural abnormalities or costophrenic angle abnormalities [R1-IMAGE].
+Differential Considerations:
+- Primary: Pulmonary Atelectasis is less likely given the normal lung fields on chest X-ray [R1].
+- Alternative: Pleural Effusion is less likely given the normal pleura on chest X-ray [R1].</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q30" t="n">
         <v>2</v>
       </c>
       <c r="R30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S30" t="n">
-        <v>0.4421709179878235</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0.4710854589939117</v>
-      </c>
-      <c r="U30" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.533458160686493</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.5992290803432465</v>
+      </c>
+      <c r="X30" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr">
+      <c r="Y30" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="W30" t="n">
-        <v>2</v>
-      </c>
-      <c r="X30" t="inlineStr">
+      <c r="Z30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3243,7 +3477,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Are the lung fields clear on the chest X-ray?</t>
+          <t>Patient 30 is a male presenting with chest pain. Does the chest X-ray show any consolidation, effusion, pneumothorax, or pneumoperitoneum?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3252,7 +3486,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
@@ -3261,7 +3495,7 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.667</v>
+        <v>0.9</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3269,61 +3503,69 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7221204042434692</v>
+        <v>0.3382844924926758</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The lung fields appear to be clear on the chest X-ray. [R1-IMAGE]
-Supporting Evidence:
-- The lungs are clear without focal consolidation, effusion, or pneumothorax. [R1]
-- The chest x-ray appears to be normal, with no visible signs of abnormalities or issues in the lung fields. [R1-IMAGE]
-- The lung fields appear to be clear on the chest x-ray. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any potential underlying concerns. [Rx]
-- Further evaluation may be needed to assess the patient's overall health and identify any underlying conditions that may not be visible on the x-ray. [Rx]</t>
-        </is>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.6</v>
       </c>
       <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>2</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any consolidation, effusion, pneumothorax, or pneumoperitoneum [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Lungs are clear without focal consolidation, effusion, or pneumothorax, and the heart size is normal [R1].
+- The chest X-ray appears to be normal, with no visible consolidation, pneumothorax, or pneumoperitoneum [R1-IMAGE].
+Differential Considerations:
+- Primary: Acute chest pain is likely due to musculoskeletal strain given the normal chest X-ray findings [R1].
+- Alternative: Pneumonia or pulmonary embolism are less likely given the clear lung fields and absence of other concerning features on the chest X-ray [R2].</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
-        <v>0.588</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>0.7834361212730407</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0.6857180606365203</v>
-      </c>
-      <c r="U31" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T31" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.5976568984985351</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0.6668284492492675</v>
+      </c>
+      <c r="X31" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W31" t="n">
-        <v>2</v>
-      </c>
-      <c r="X31" t="inlineStr">
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA31" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3335,7 +3577,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Confirm whether the chest X-ray appears normal.</t>
+          <t>Patient 31 presents with dyspnea. Are there any interstitial changes or acute pulmonary findings on the chest X-ray?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3344,7 +3586,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -3353,7 +3595,7 @@
         <v>1</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3361,62 +3603,68 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5627533793449402</v>
+        <v>0.4710338115692139</v>
       </c>
       <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- The chest X-ray appears normal. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray shows no visible signs of abnormalities or issues in the image. [R1-IMAGE]
-- The chest X-ray appears to be normal, with no visible abnormalities or signs of disease in the image. [R2-IMAGE]
-- A normal chest x-ray does not necessarily rule out all possible conditions or diseases, and further evaluation and tests may be needed depending on the patient's clinical history and symptoms. [R1-IMAGE]
-- Further evaluation and clinical correlation may be needed to assess the patient's overall health and identify any underlying concerns that may not be apparent on the X-ray. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to assess the patient's overall health and identify any underlying concerns that may not be apparent on the X-ray. [Rx]
-- Further evaluation and tests may be needed depending on the patient's clinical history and symptoms. [Rx]</t>
-        </is>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.6</v>
       </c>
       <c r="M32" t="inlineStr"/>
-      <c r="N32" t="n">
-        <v>2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1</v>
-      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+No interstitial changes or acute pulmonary findings are present on the chest X-ray. [HIGH CONFIDENCE — supported by text report]
+Evidence Synthesis:
+- The chest x-ray shows no interstitial changes or acute pulmonary findings. [R1-IMAGE]
+- Insufficient evidence to determine the presence of interstitial changes or acute pulmonary findings based on text reports. [R1]
+Differential Considerations:
+- Primary: Pulmonary embolism is less likely given the absence of interstitial changes or acute pulmonary findings on the chest X-ray. [R1]</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q32" t="n">
         <v>2</v>
       </c>
       <c r="R32" t="n">
-        <v>0.537</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>0.468826013803482</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0.502913006901741</v>
-      </c>
-      <c r="U32" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T32" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.4541067623138428</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0.5345533811569214</v>
+      </c>
+      <c r="X32" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr">
+      <c r="Y32" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="W32" t="n">
-        <v>2</v>
-      </c>
-      <c r="X32" t="inlineStr">
+      <c r="Z32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA32" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3428,7 +3676,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Identify any abnormal findings on the chest X-ray.</t>
+          <t>Patient 32 has a history of muscle weakness and pulmonary nodules. What does the chest X-ray show? Is there blunting of the costophrenic angles?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3437,7 +3685,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -3446,7 +3694,7 @@
         <v>1</v>
       </c>
       <c r="G33" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3454,62 +3702,69 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.8103905916213989</v>
+        <v>0.3492819666862488</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No acute abnormality detected. [R1]
-Supporting Evidence:
-- The heart is normal in size. [R1]
-- The mediastinum is unremarkable. [R1]
-- Mild blunting of right costophrenic angle. [R1]
-- The lungs are otherwise grossly clear. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms and history. [Rx]
-- Follow-up imaging if symptoms persist or new symptoms develop. [Rx]</t>
-        </is>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.6</v>
       </c>
       <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray shows no significant abnormalities, including no blunting of the costophrenic angles, with HIGH CONFIDENCE [R1].
+Evidence Synthesis:
+- The heart is normal in size, and the mediastinum is unremarkable, as per the text report. [R1]
+- The chest x-ray shows normal lung fields, a normal cardiac silhouette, and no pleural abnormalities or blunting of the costophrenic angles, as per imaging findings. [R1-IMAGE]
+Differential Considerations:
+- Primary: Normal chest X-ray, given the absence of any significant abnormalities on imaging and the text report's description of the heart and mediastinum as normal. [R1]
+- Alternative: Pulmonary nodules or muscle weakness-related changes might be present but are not visible on the chest X-ray, given the normal findings. [R2]</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R33" t="n">
-        <v>0.662</v>
+        <v>1</v>
       </c>
       <c r="S33" t="n">
-        <v>0.9431171774864197</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0.8025585887432098</v>
-      </c>
-      <c r="U33" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T33" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.4498563933372497</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0.5754281966686249</v>
+      </c>
+      <c r="X33" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W33" t="n">
-        <v>2</v>
-      </c>
-      <c r="X33" t="inlineStr">
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3521,7 +3776,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show cardiomegaly or abnormal cardiac silhouette?</t>
+          <t>Patient 33 has six months of symptoms and prior surgery. What does the chest X-ray reveal about the lungs and are there any surgical hardware findings?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3530,7 +3785,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
@@ -3539,7 +3794,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.778</v>
+        <v>0.308</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3547,62 +3802,70 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.650692880153656</v>
+        <v>0.4141548871994019</v>
       </c>
       <c r="J34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of cardiomegaly or abnormal cardiac silhouette detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- Cardiac and mediastinal contours are within normal limits on the chest X-ray. [R1]
-- The lungs are clear on the chest X-ray. [R1]
-- Bony structures are intact on the chest X-ray. [R1]
-- The chest X-ray does not show any signs of cardiomegaly or an abnormal cardiac silhouette. [R1-IMAGE], [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's cardiac status. [Rx]
-- Follow-up imaging if symptoms persist or new cardiac symptoms develop. [Rx]</t>
-        </is>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1</v>
       </c>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="n">
-        <v>2</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1</v>
-      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The lungs appear to be clear and free of any visible abnormalities, with no evidence of surgical hardware findings, but there is a small amount of pleural fluid present [MODERATE CONFIDENCE — partial text support, supplemented by imaging].
+Evidence Synthesis:
+- Cardiac and mediastinal contours are within normal limits, and the lungs are clear, as per text report [R1].
+- The chest x-ray shows normal lung fields, with no surgical hardware findings visible, but there is a small amount of pleural fluid present [R1-IMAGE].
+- Discordance Note: CNN did not detect any pathologies above threshold, but text report and imaging findings suggest a small amount of pleural fluid [R1, R1-IMAGE].
+Differential Considerations:
+- Primary: Pleural effusion due to the presence of a small amount of pleural fluid, as suggested by imaging findings [R1].
+- Alternative: Pulmonary embolism or other lung pathology, but evidence does not support this, and CNN did not detect any pathologies above threshold [R2].</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>0.632</v>
+        <v>1</v>
       </c>
       <c r="S34" t="n">
-        <v>0.8064078640460968</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0.7192039320230483</v>
-      </c>
-      <c r="U34" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T34" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.4752309774398804</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0.5931154887199401</v>
+      </c>
+      <c r="X34" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W34" t="n">
-        <v>2</v>
-      </c>
-      <c r="X34" t="inlineStr">
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3614,7 +3877,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Are there signs of pulmonary congestion or edema on the chest X-ray?</t>
+          <t>Patient 34 is a patient with chest pain. Does the chest X-ray show any infiltrate, pneumothorax, or cardiac abnormality?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3632,7 +3895,7 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.75</v>
+        <v>0.857</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3640,61 +3903,69 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.6177862286567688</v>
+        <v>0.4388651847839355</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pulmonary congestion or edema detected on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R1-IMAGE]
-- The lungs are clear, without evidence of infiltrate. [R1]
-- The chest x-ray does not show any signs of pulmonary congestion or edema. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but currently, there is no indication for immediate further imaging. [Rx]</t>
-        </is>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.6</v>
       </c>
       <c r="M35" t="inlineStr"/>
-      <c r="N35" t="n">
-        <v>2</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1</v>
-      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any infiltrate, pneumothorax, or cardiac abnormality [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The heart is normal in size and contour, and the lungs are clear without evidence of infiltrate [R1].
+- The chest X-ray appears to be normal, with no visible infiltrate, pneumothorax, or cardiac abnormality [R1-IMAGE].
+Differential Considerations:
+- Primary: Pulmonary embolism is unlikely given the normal chest X-ray findings [R1].
+- Alternative: Pneumonia could be considered, but the lack of infiltrate on the chest X-ray makes it less likely [R2].</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>0.636</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
-        <v>0.7853358685970308</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0.7106679342985154</v>
-      </c>
-      <c r="U35" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T35" t="b">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0.779</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0.6048730369567872</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0.6919365184783937</v>
+      </c>
+      <c r="X35" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W35" t="n">
-        <v>2</v>
-      </c>
-      <c r="X35" t="inlineStr">
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA35" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3706,7 +3977,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Is pleural effusion visible on the chest X-ray?</t>
+          <t>Patient 35 is a female with a breast mass and smoking history. What does the chest X-ray show about emphysematous changes and are there any acute findings?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3724,7 +3995,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.714</v>
+        <v>0.474</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3732,61 +4003,69 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6911731958389282</v>
+        <v>0.6568161249160767</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No pleural effusion visible on the chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any visible signs of pleural effusion. [R1-IMAGE]
-- The chest x-ray does not show any visible signs of pleural effusion. [R2-IMAGE]
-- The heart size and cardiomediastinal silhouette are normal, which is consistent with the absence of pleural effusion. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other causes of respiratory symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but pleural effusion is unlikely given the current chest X-ray findings. [Rx]</t>
-        </is>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.6</v>
       </c>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="n">
-        <v>2</v>
-      </c>
-      <c r="O36" t="n">
-        <v>1</v>
-      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray shows no emphysematous changes and no acute findings in the lung fields, cardiac silhouette, pleura, costophrenic angles, mediastinum, or diaphragm [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The heart size and cardiomediastinal silhouette are normal, with no focal airspace opacity, pleural effusion, or pneumothorax [R1].
+- The chest X-ray shows no emphysematous changes and no acute findings in the lung fields, cardiac silhouette, pleura, costophrenic angles, mediastinum, or diaphragm [R1-IMAGE].
+Differential Considerations:
+- Primary: Normal chest X-ray findings in a 35-year-old female with a breast mass and smoking history, with no evidence of emphysema or acute lung injury [R1].
+- Alternative: Although the patient has a smoking history, the chest X-ray does not show any signs of emphysema, making other respiratory conditions less likely [R2].</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
-        <v>0.646</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
-        <v>0.7929519587516785</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0.7194759793758392</v>
-      </c>
-      <c r="U36" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T36" t="b">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.729</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.5335632249832154</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0.6312816124916076</v>
+      </c>
+      <c r="X36" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W36" t="n">
-        <v>2</v>
-      </c>
-      <c r="X36" t="inlineStr">
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA36" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3798,7 +4077,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Does the chest X-ray show lung consolidation or opacities?</t>
+          <t>Patient 36 is a female presenting with chest pain and suspected pneumonia. Does the chest X-ray confirm or rule out pneumonia, pleural effusion, or pneumothorax?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3816,7 +4095,7 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.667</v>
+        <v>0.867</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3824,61 +4103,69 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.7085100412368774</v>
+        <v>0.3591641485691071</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No lung consolidation or opacities detected on chest X-ray. [R1], [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The lungs are clear bilaterally, with no evidence of focal consolidation. [R1]
-- The chest X-ray does not show any lung consolidation or opacities. [R1-IMAGE]
-- The chest X-ray does not show any lung consolidation or opacities. [R2-IMAGE]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's chest pain. [Rx]
-- Follow-up imaging if symptoms persist, but currently, no indication for immediate further imaging. [Rx]</t>
-        </is>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.6</v>
       </c>
       <c r="M37" t="inlineStr"/>
-      <c r="N37" t="n">
-        <v>2</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1</v>
-      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Pneumonia is ABSENT [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- The lungs are clear bilaterally, with no evidence of focal consolidation, pneumothorax, or pleural effusion [R1].
+- The chest X-ray shows normal lung fields, a normal cardiac silhouette, and no pleural effusion or pneumothorax [R1-IMAGE].
+Differential Considerations:
+- Primary: Pulmonary embolism or musculoskeletal chest pain given the patient's symptoms and normal chest X-ray findings [R1].
+- Alternative: Pneumonia or other pulmonary conditions that may not be visible on a chest X-ray, such as bronchitis or asthma, are less likely given the clear lung fields and normal cardiac silhouette [R2].</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.672</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
-        <v>0.7793530123710632</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0.7256765061855317</v>
-      </c>
-      <c r="U37" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T37" t="b">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.5919328297138213</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0.6634664148569107</v>
+      </c>
+      <c r="X37" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W37" t="n">
-        <v>2</v>
-      </c>
-      <c r="X37" t="inlineStr">
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA37" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3890,7 +4177,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Are there signs of pneumothorax on the chest X-ray?</t>
+          <t>Patient 37 presents with hypoxia. What does the chest X-ray show in the right middle lobe? Is there any acute disease?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3899,7 +4186,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
@@ -3908,7 +4195,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3916,61 +4203,70 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.5247206687927246</v>
+        <v>0.1141817718744278</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No signs of pneumothorax detected on chest X-ray. [R1-IMAGE], [R2-IMAGE]
-Supporting Evidence:
-- The chest x-ray does not show any signs of pneumothorax. [R1-IMAGE]
-- The chest x-ray does not show any signs of pneumothorax. [R2-IMAGE]
-- The lungs are otherwise grossly clear, which is consistent with no pneumothorax. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to rule out other causes of hypoxia. [Rx]
-- Further evaluation of the patient's symptoms and medical history is necessary to determine the cause of hypoxia. [Rx]</t>
-        </is>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.7</v>
       </c>
       <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>2</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1</v>
-      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The opacity in the right middle lobe of the lung is present [HIGH CONFIDENCE — supported by text report].
+- Alternative: Other lung abnormalities such as atelectasis or lung cancer could also be considered, but the evidence points away from these diagnoses as there is no mention of a history of cancer or recent respiratory symptoms. [R2]
+Evidence Synthesis:
+- The chest x-ray shows an opacity in the right middle lobe of the lung, which could be due to various reasons such as infection, inflammation, or other lung abnormalities. [R1]
+- Based on imaging only (limited confidence): The chest x-ray shows an opacity in the right middle lobe of the lung. [R2-IMAGE]
+Differential Considerations:
+- Primary: No acute abnormality identified based on available evidence. [R1]
+- Alternative: Insufficient evidence to exclude other diagnoses without additional imaging. [Rx]</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>0.475</v>
+        <v>1</v>
       </c>
       <c r="S38" t="n">
-        <v>0.7242162006378173</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0.5996081003189087</v>
-      </c>
-      <c r="U38" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T38" t="b">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.4428363543748856</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.5434181771874428</v>
+      </c>
+      <c r="X38" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W38" t="n">
-        <v>2</v>
-      </c>
-      <c r="X38" t="inlineStr">
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA38" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -3982,7 +4278,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Summarize the key findings from the chest X-ray.</t>
+          <t>Patient 38 presents with shortness of breath for 3 days. Does the chest X-ray show any pleural effusion, pneumothorax, or airspace disease?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3991,79 +4287,86 @@
         </is>
       </c>
       <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.769</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>ragas</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.3699504733085632</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>0.6</v>
       </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>ragas</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>0.7861149907112122</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- No significant pathologies detected above threshold. [R1]
-Supporting Evidence:
-- Lungs are clear. [R1]
-- No pneumothorax or pleural effusion detected. [R1]
-- Heart and mediastinum are within normal limits. [R1]
-- Bony structures are intact. [R1]
-Next Steps / Recommendations:
-- Clinical correlation recommended to further evaluate the patient's symptoms. [Rx]
-- Follow-up imaging if symptoms persist, but no immediate indication for further X-ray. [Rx]</t>
-        </is>
-      </c>
       <c r="M39" t="inlineStr"/>
-      <c r="N39" t="n">
-        <v>2</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+The chest X-ray does not show any pleural effusion, pneumothorax, or airspace disease [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Lungs are clear with no pneumothorax or pleural effusion as per text report [R1].
+- The chest X-ray appears to be normal with no visible anatomical findings such as pleural effusion, pneumothorax, or airspace disease [R1-IMAGE].
+Differential Considerations:
+- Primary: Acute respiratory distress syndrome (ARDS) is unlikely given the clear lung fields on chest X-ray [R1].
+- Alternative: Pulmonary embolism could be considered, but the normal chest X-ray makes it less likely [R2].</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0.8214344972133636</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0.7107172486066817</v>
-      </c>
-      <c r="U39" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T39" t="b">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.5646900946617126</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0.6703450473308563</v>
+      </c>
+      <c r="X39" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="W39" t="n">
-        <v>2</v>
-      </c>
-      <c r="X39" t="inlineStr">
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>RETRY</t>
+        </is>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
@@ -4075,7 +4378,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Does the chest X-ray indicate heart enlargement?</t>
+          <t>Patient 39 presents with diminished breath sounds throughout. What do the chest X-ray findings show and is there any active disease?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4084,7 +4387,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
@@ -4101,61 +4404,69 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.568744421005249</v>
+        <v>0.1067323982715607</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Diagnosis / Impression:
-- Insufficient evidence to confirm or rule out heart enlargement. [R1], [R2]
-Supporting Evidence:
-- The chest X-ray does not show any signs of heart enlargement. [R1-IMAGE], [R2-IMAGE]
-- A chest X-ray is not the most definitive imaging modality for assessing heart size, as it may not always provide clear visualization of the heart's structure. [R1-IMAGE]
-- Both lungs are clear and expanded, and the heart and mediastinum appear normal on the chest X-ray. [R1]
-Next Steps / Recommendations:
-- Clinical correlation with other diagnostic modalities (e.g., echocardiogram, electrocardiogram) is recommended to further assess heart size and function. [Rx]
-- Follow-up imaging with a more definitive modality (e.g., echocardiogram) if symptoms persist or if there is a high clinical suspicion of heart enlargement. [Rx]</t>
-        </is>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.6</v>
       </c>
       <c r="M40" t="inlineStr"/>
-      <c r="N40" t="n">
-        <v>2</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Clinical Impression:
+Diminished breath sounds throughout are present [HIGH CONFIDENCE — supported by text report].
+Evidence Synthesis:
+- Diminished breath sounds throughout are noted on physical examination, consistent with respiratory symptoms [R1].
+- The chest x-ray shows normal lung fields, a normal cardiac silhouette, and no active disease [R1-IMAGE].
+Differential Considerations:
+- Primary: Pneumonia is less likely given the normal lung fields on chest x-ray and absence of active disease [R1].
+- Alternative: Pulmonary edema could be considered, but the normal cardiac silhouette and clear costophrenic angles on chest x-ray make this less likely [R2].</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
       </c>
       <c r="R40" t="n">
-        <v>0.458</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0.6706233263015747</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0.5643116631507874</v>
-      </c>
-      <c r="U40" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="T40" t="b">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.696</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.4313464796543121</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.563673239827156</v>
+      </c>
+      <c r="X40" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>RETRY</t>
-        </is>
-      </c>
-      <c r="W40" t="n">
-        <v>2</v>
-      </c>
-      <c r="X40" t="inlineStr">
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="Z40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>XRAY</t>
         </is>
